--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,6 +83,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -542,40 +543,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>EGH International Berhad</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.04</v>
+        <v>0.145</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>12300100</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.69</v>
-      </c>
+        <v>53301700</v>
+      </c>
+      <c r="G2" s="5" t="n"/>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.043</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
     </row>
@@ -587,39 +579,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>-0.0235</v>
+        <v>0.18</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6087800</v>
+        <v>20493900</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.378</v>
+        <v>0.191</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.27</v>
+        <v>0.185</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -632,28 +624,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.065</v>
+        <v>0.04</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5783500</v>
+        <v>13427100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.01</v>
+        <v>21.32</v>
       </c>
       <c r="H4" t="n">
-        <v>24.19</v>
+        <v>46.69</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -661,10 +653,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.132</v>
+        <v>0.041</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.334</v>
+        <v>0.043</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -677,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3372700</v>
+        <v>13410900</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>66.34999999999999</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.17</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3</v>
+        <v>0.161</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.255</v>
+        <v>0.138</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -722,45 +714,2727 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.0074</v>
+        <v>0.06</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2793800</v>
+        <v>11988400</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.11</v>
+        <v>219.79</v>
       </c>
       <c r="H6" t="n">
-        <v>75.19</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>57.82</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.61</v>
+        <v>0.057</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.526</v>
+        <v>0.062</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8966</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TECHBASE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>11732400</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10825800</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>9519300</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0207</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MESTRON</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>8334200</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0096</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NEXGRAM</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7740200</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.07690000000000001</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7603500</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7096700</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6668900</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6502400</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H15" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>5958700</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>5661800</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>5370500</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H18" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>7.556</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>4567200</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3606500</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3533800</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3385200</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H22" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3090100</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2532500</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H24" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2482700</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H25" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2464000</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H26" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2190000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7217</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMETALL</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2019500</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H28" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1880600</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H29" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1821100</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1719500</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H31" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1609600</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H32" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>5.544</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>5.435</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1589500</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H33" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1523200</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H34" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1341900</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1316600</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1257800</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H37" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1229100</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H38" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0328</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3REN</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1218100</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H39" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1197500</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1190500</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1166500</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>4.856</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1073400</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1059500</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.05769999999999999</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1057800</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H45" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BFIELD</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1014900</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H46" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.0251</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1011600</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H47" t="n">
+        <v>29</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>7.311</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1004900</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>4.913</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>4.721</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>980800</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H49" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>2.798</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>948800</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2.648</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>876900</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>868500</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H52" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>817000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H53" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>813400</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>2.164</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>773200</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>720200</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H56" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>682100</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H57" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>3.664</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>675000</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H58" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>648500</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H59" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>627800</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>624100</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H61" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>582800</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H62" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>568100</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H63" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>541400</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H64" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H65" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>6.134</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>5.893</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>523700</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H66" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,9 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.145</v>
+        <v>0.135</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>53301700</v>
+        <v>60611000</v>
       </c>
       <c r="G2" s="5" t="n"/>
       <c r="I2" s="6" t="inlineStr">
@@ -579,39 +579,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>20493900</v>
+        <v>22900500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.23</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.191</v>
+        <v>0.823</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.185</v>
+        <v>0.732</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -624,28 +624,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>13427100</v>
+        <v>20493900</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>21.32</v>
+        <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>46.69</v>
+        <v>42.99</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.041</v>
+        <v>0.191</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.043</v>
+        <v>0.185</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -669,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.145</v>
+        <v>0.335</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.0333</v>
+        <v>0.0152</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>13410900</v>
+        <v>15360300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.54000000000001</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.161</v>
+        <v>0.301</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.138</v>
+        <v>0.255</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.055</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11988400</v>
+        <v>15107400</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>219.79</v>
+        <v>6.48</v>
       </c>
       <c r="H6" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+        <v>69.25</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.062</v>
+        <v>0.047</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11732400</v>
+        <v>14157100</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>10.9</v>
+        <v>22.48</v>
       </c>
       <c r="H7" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.059</v>
+        <v>0.041</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.057</v>
+        <v>0.043</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10825800</v>
+        <v>13929900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.14</v>
+        <v>255.38</v>
       </c>
       <c r="H8" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+        <v>57.82</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.301</v>
+        <v>0.057</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.255</v>
+        <v>0.062</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,39 +849,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.145</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9519300</v>
+        <v>13835400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H9" t="n">
-        <v>66.79000000000001</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.17</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.821</v>
+        <v>0.161</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.731</v>
+        <v>0.138</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,39 +894,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0417</v>
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8334200</v>
+        <v>13211600</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3.08</v>
+        <v>0.37</v>
       </c>
       <c r="H10" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.092</v>
+        <v>0.378</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.092</v>
+        <v>0.27</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -939,39 +939,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7740200</v>
+        <v>13146800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3.32</v>
+        <v>12.21</v>
       </c>
       <c r="H11" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
+        <v>68.44</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.675</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7603500</v>
+        <v>12084100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.02</v>
+        <v>0.48</v>
       </c>
       <c r="H12" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.131</v>
+        <v>0.611</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.334</v>
+        <v>0.526</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>7.37</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7096700</v>
+        <v>9695300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="H13" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
+        <v>39.4</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.611</v>
+        <v>7.558</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.526</v>
+        <v>7.701</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>-0.0118</v>
+        <v>0.115</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6668900</v>
+        <v>8718700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.19</v>
+        <v>3.22</v>
       </c>
       <c r="H14" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
+        <v>69.55</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.378</v>
+        <v>0.092</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.27</v>
+        <v>0.092</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,40 +1119,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6502400</v>
+        <v>8118100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H15" t="n">
-        <v>38.13</v>
+        <v>0.31</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.482</v>
-      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1164,33 +1157,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>-0.0196</v>
+        <v>0.06</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5958700</v>
+        <v>7603500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+        <v>0.02</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.334</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.053</v>
+        <v>0.79</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.0464</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5661800</v>
+        <v>7164700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7.35</v>
+        <v>0.45</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>-0.0174</v>
+        <v>0.0112</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5370500</v>
+        <v>6861700</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="H18" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.556</v>
+        <v>0.482</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>7.7</v>
+        <v>0.482</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1294,27 +1294,27 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.005</v>
+        <v>2.03</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.015</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4567200</v>
+        <v>5853600</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H19" t="n">
-        <v>58.91</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
+        <v>59.85</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.919</v>
+        <v>1.921</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1.727</v>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.295</v>
+        <v>0.82</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.0061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3606500</v>
+        <v>4942000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.44</v>
+        <v>0.31</v>
       </c>
       <c r="H20" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.12</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.299</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-0.0222</v>
+        <v>0.1</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3533800</v>
+        <v>4784900</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.17</v>
+        <v>1.21</v>
       </c>
       <c r="H21" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.28</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.223</v>
+        <v>0.097</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.239</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,39 +1420,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.455</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0341</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3385200</v>
+        <v>4640300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.47</v>
+        <v>0.23</v>
       </c>
       <c r="H22" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
+        <v>60.99</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.371</v>
+        <v>0.423</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.385</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3090100</v>
+        <v>4305000</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
+        <v>63.48</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.422</v>
+        <v>0.371</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.364</v>
+        <v>0.369</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.295</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2532500</v>
+        <v>4166300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H24" t="n">
-        <v>49.14</v>
+        <v>50.32</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.347</v>
+        <v>0.299</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.333</v>
+        <v>0.28</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,39 +1555,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.028</v>
+        <v>0.44</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2482700</v>
+        <v>3934000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.12</v>
+        <v>4.41</v>
       </c>
       <c r="H25" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.33</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.575</v>
+        <v>0.439</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.538</v>
+        <v>0.439</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,40 +1600,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.36</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.0746</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2464000</v>
+        <v>3924500</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.15</v>
+        <v>0.71</v>
       </c>
       <c r="H26" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
+        <v>63.39</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>0.314</v>
+      </c>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1645,39 +1643,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.31</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2190000</v>
+        <v>3879700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H27" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.309</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.776</v>
+        <v>0.299</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,39 +1688,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.44</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2019500</v>
+        <v>3814100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.27</v>
+        <v>0.25</v>
       </c>
       <c r="H28" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
+        <v>50.17</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.439</v>
+        <v>0.775</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.439</v>
+        <v>0.776</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,39 +1733,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.0367</v>
+        <v>0.225</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1880600</v>
+        <v>3583200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.48</v>
+        <v>0.17</v>
       </c>
       <c r="H29" t="n">
-        <v>75.38</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+        <v>48.67</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.829</v>
+        <v>0.224</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.239</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,28 +1778,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1821100</v>
+        <v>3405700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H30" t="n">
-        <v>33.84</v>
+        <v>38.01</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1809,10 +1807,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.397</v>
+        <v>5.544</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.407</v>
+        <v>5.435</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1823,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.0238</v>
+        <v>0.165</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1719500</v>
+        <v>3398000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.21</v>
+        <v>0.48</v>
       </c>
       <c r="H31" t="n">
-        <v>21.73</v>
+        <v>34.49</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1852,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.537</v>
+        <v>0.179</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.619</v>
+        <v>0.197</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,28 +1868,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.25</v>
+        <v>0.335</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.0152</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1609600</v>
+        <v>3371600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H32" t="n">
-        <v>38.01</v>
+        <v>47.25</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1899,10 +1897,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.544</v>
+        <v>0.346</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5.435</v>
+        <v>0.332</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1913,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.0053</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1589500</v>
+        <v>3268100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H33" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.919</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.874</v>
+        <v>0.869</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,38 +1958,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.0746</v>
+        <v>0.18</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1523200</v>
+        <v>3027200</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
+        <v>62.97</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="K34" s="2" t="n"/>
+        <v>0.164</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.165</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2003,28 +2003,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.555</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1341900</v>
+        <v>2959900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="H35" t="n">
-        <v>46.04</v>
+        <v>47.94</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.055</v>
+        <v>0.576</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.953</v>
+        <v>0.538</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,28 +2048,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0.0471</v>
+        <v>6.95</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0307</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1316600</v>
+        <v>2621300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="H36" t="n">
-        <v>45.75</v>
+        <v>27.89</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>7.307</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.844</v>
+        <v>7.647</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2093,28 +2093,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0.0373</v>
+        <v>1.46</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1257800</v>
+        <v>2482400</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H37" t="n">
-        <v>53.8</v>
+        <v>23.66</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.825</v>
+        <v>1.72</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.777</v>
+        <v>1.958</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2138,28 +2138,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1229100</v>
+        <v>2481800</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H38" t="n">
-        <v>41.25</v>
+        <v>51.22</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.773</v>
+        <v>0.388</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.772</v>
+        <v>0.377</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2183,39 +2183,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.415</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1218100</v>
+        <v>2451600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.13</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.388</v>
+        <v>0.538</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.391</v>
+        <v>0.619</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,39 +2228,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.375</v>
+        <v>1.13</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-0.0132</v>
+        <v>0.0367</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1197500</v>
+        <v>2440300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="H40" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+        <v>75.38</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.387</v>
+        <v>0.829</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.377</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.0227</v>
+        <v>4.77</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1190500</v>
+        <v>2373200</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H41" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.44</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.237</v>
+        <v>4.725</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.289</v>
+        <v>4.855</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,39 +2318,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1166500</v>
+        <v>2208300</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H42" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.726</v>
+        <v>0.918</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.856</v>
+        <v>0.873</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,28 +2363,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.0092</v>
+        <v>0.39</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1073400</v>
+        <v>2128400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H43" t="n">
-        <v>54.23</v>
+        <v>33.84</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.077</v>
+        <v>0.397</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.043</v>
+        <v>0.407</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2417,19 +2417,19 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.455</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1059500</v>
+        <v>2049200</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H44" t="n">
-        <v>28.37</v>
+        <v>27.74</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2453,28 +2453,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.895</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.0529</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1057800</v>
+        <v>1924100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H45" t="n">
-        <v>58.07</v>
+        <v>46.48</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.048</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.904</v>
+        <v>0.844</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,38 +2498,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>-0.023</v>
+        <v>0.625</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1014900</v>
+        <v>1907400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H46" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K46" s="2" t="n"/>
+        <v>0.616</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.614</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
     </row>
@@ -2541,28 +2543,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6.99</v>
+        <v>1.01</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.0251</v>
+        <v>0.0306</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1011600</v>
+        <v>1892000</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H47" t="n">
-        <v>29</v>
+        <v>46.04</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2570,10 +2572,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.311</v>
+        <v>1.055</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>7.648</v>
+        <v>0.953</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2586,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.0021</v>
+        <v>0.295</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1004900</v>
+        <v>1859000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.04</v>
+        <v>0.6</v>
       </c>
       <c r="H48" t="n">
-        <v>47.9</v>
+        <v>49.15</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2615,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4.913</v>
+        <v>0.295</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4.721</v>
+        <v>0.295</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2631,40 +2633,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.046</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>980800</v>
+        <v>1736500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H49" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>16.79</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.798</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>2.405</v>
-      </c>
+        <v>0.463</v>
+      </c>
+      <c r="K49" s="2" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2676,39 +2676,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>0.0272</v>
+        <v>1.15</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.1058</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>948800</v>
+        <v>1651300</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
       <c r="H50" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.54</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.648</v>
+        <v>1.053</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.549</v>
+        <v>0.905</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2721,28 +2721,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>0.0192</v>
+        <v>1.03</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0457</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>876900</v>
+        <v>1651100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.06</v>
+        <v>1.15</v>
       </c>
       <c r="H51" t="n">
-        <v>54.35</v>
+        <v>42.32</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.521</v>
+        <v>1.083</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.458</v>
+        <v>1.095</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2766,39 +2766,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0.028</v>
+        <v>0.845</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.04969999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>868500</v>
+        <v>1621900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H52" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.569</v>
+        <v>0.826</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.613</v>
+        <v>0.777</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2811,28 +2811,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>4.84</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>817000</v>
+        <v>1597700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H53" t="n">
-        <v>46.73</v>
+        <v>47.9</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.307</v>
+        <v>4.913</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.314</v>
+        <v>4.721</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2856,39 +2856,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0.0148</v>
+        <v>2.64</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.0272</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>813400</v>
+        <v>1579900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H54" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.98</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.164</v>
+        <v>2.648</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.232</v>
+        <v>2.549</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2901,39 +2901,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>773200</v>
+        <v>1575400</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H55" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.49</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.616</v>
+        <v>2.163</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.614</v>
+        <v>2.232</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2946,39 +2946,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>0.0133</v>
+        <v>1.12</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>720200</v>
+        <v>1574700</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>11.81</v>
+        <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.65</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.736</v>
+        <v>1.078</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.741</v>
+        <v>1.044</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2991,28 +2991,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0.0546</v>
+        <v>0.745</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>682100</v>
+        <v>1520100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H57" t="n">
-        <v>52.15</v>
+        <v>41.25</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3.853</v>
+        <v>0.773</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>3.664</v>
+        <v>0.772</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3036,28 +3036,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.22</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>675000</v>
+        <v>1508800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>52.61</v>
+        <v>33.7</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.764</v>
+        <v>0.237</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.289</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3081,39 +3081,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>0.0191</v>
+        <v>0.705</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>648500</v>
+        <v>1400500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.11</v>
+        <v>0.55</v>
       </c>
       <c r="H59" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.7</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.791</v>
+        <v>0.647</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.77</v>
+        <v>0.553</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3126,39 +3126,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E60" s="9" t="n">
-        <v>0.0037</v>
+        <v>0.395</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>627800</v>
+        <v>1351200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.05</v>
+        <v>0.57</v>
       </c>
       <c r="H60" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.778</v>
+        <v>0.388</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.735</v>
+        <v>0.391</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3171,39 +3171,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.49</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>624100</v>
+        <v>1343300</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H61" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.646</v>
+        <v>0.511</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.552</v>
+        <v>0.526</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3216,28 +3216,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>582800</v>
+        <v>1328600</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="H62" t="n">
-        <v>50.91</v>
+        <v>42.59</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.637</v>
+        <v>2.045</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.621</v>
+        <v>2.073</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3261,28 +3261,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.825</v>
+        <v>0.53</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.006</v>
+        <v>0.0192</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>568100</v>
+        <v>1309000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="H63" t="n">
-        <v>36.21</v>
+        <v>54.35</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.848</v>
+        <v>0.521</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.862</v>
+        <v>0.458</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3306,28 +3306,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.9</v>
+        <v>2.71</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>541400</v>
+        <v>1304100</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>49.12</v>
+        <v>44.87</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.914</v>
+        <v>2.778</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.869</v>
+        <v>2.735</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3351,39 +3351,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>0.0125</v>
+        <v>1.2</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>538300</v>
+        <v>1299900</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H65" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.134</v>
+        <v>1.171</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>5.893</v>
+        <v>1.133</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3396,28 +3396,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>0.0069</v>
+        <v>0.8</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>523700</v>
+        <v>1290900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H66" t="n">
-        <v>23.66</v>
+        <v>58.44</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3425,16 +3425,1456 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.72</v>
+        <v>0.791</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.958</v>
+        <v>0.77</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1280400</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H67" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>1140300</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>3.664</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>1072100</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H69" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1042800</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H70" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1024100</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>10.016</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>10.161</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1018500</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H72" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1015200</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H73" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>932500</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>917300</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H75" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>846100</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H76" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>3.636</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>803300</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H77" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>WELLCHIP</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>771300</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>744000</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>7.482</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>7.978</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>732100</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>723600</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H81" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>720200</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H82" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>709300</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H83" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>706000</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H84" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>688100</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H85" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>6.133</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>5.893</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>672300</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H86" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>2.771</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>663600</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H87" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>6.068</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>636800</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>626500</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H89" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>607400</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H90" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>582800</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H91" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>562900</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H92" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>559800</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>548900</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H94" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>548400</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H95" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>515600</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H96" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>510300</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>506800</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H98" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M66"/>
+  <autoFilter ref="A1:M98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
@@ -78,13 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,31 +543,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EGH International Berhad</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.135</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.2308</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>60611000</v>
-      </c>
-      <c r="G2" s="5" t="n"/>
+        <v>115145800</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22.65</v>
+      </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.334</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
     </row>
@@ -579,40 +588,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>EGH International Berhad</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.135</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0222</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>22900500</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H3" t="n">
-        <v>68.23</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.732</v>
-      </c>
+        <v>60834700</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
     </row>
@@ -624,39 +624,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20493900</v>
+        <v>27296500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.28</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.191</v>
+        <v>0.822</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.185</v>
+        <v>0.732</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -669,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.175</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15360300</v>
+        <v>20543300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.36</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.301</v>
+        <v>0.19</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.255</v>
+        <v>0.185</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15107400</v>
+        <v>17725100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>6.48</v>
+        <v>0.23</v>
       </c>
       <c r="H6" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.045</v>
+        <v>0.301</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.047</v>
+        <v>0.255</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E7" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14157100</v>
+        <v>17249800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>22.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.041</v>
+        <v>0.611</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.043</v>
+        <v>0.526</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13929900</v>
+        <v>17162100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>255.38</v>
+        <v>27.25</v>
       </c>
       <c r="H8" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.057</v>
+        <v>0.041</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.062</v>
+        <v>0.043</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,39 +849,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0333</v>
+        <v>7.35</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13835400</v>
+        <v>16417000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.19</v>
+        <v>1.11</v>
       </c>
       <c r="H9" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.72</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.161</v>
+        <v>7.556</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.138</v>
+        <v>7.7</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,39 +894,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13211600</v>
+        <v>15187500</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.37</v>
+        <v>6.52</v>
       </c>
       <c r="H10" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>69.25</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.378</v>
+        <v>0.045</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.27</v>
+        <v>0.047</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -939,39 +939,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.145</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13146800</v>
+        <v>14215100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>12.21</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.17</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.059</v>
+        <v>0.161</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.057</v>
+        <v>0.138</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.1818</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12084100</v>
+        <v>14080100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.48</v>
+        <v>258.14</v>
       </c>
       <c r="H12" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>69.25</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.611</v>
+        <v>0.057</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.526</v>
+        <v>0.063</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0147</v>
+        <v>0.075</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9695300</v>
+        <v>13466500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.65</v>
+        <v>12.51</v>
       </c>
       <c r="H13" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+        <v>68.44</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.558</v>
+        <v>0.059</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>7.701</v>
+        <v>0.057</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0417</v>
+        <v>0.42</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8718700</v>
+        <v>13260100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3.22</v>
+        <v>0.37</v>
       </c>
       <c r="H14" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.092</v>
+        <v>0.378</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.092</v>
+        <v>0.27</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1130,14 +1130,14 @@
       <c r="D15" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="3" t="n">
         <v>-0.0196</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8118100</v>
+        <v>11001800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1157,28 +1157,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.45</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7603500</v>
+        <v>10425300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="H16" t="n">
-        <v>23.66</v>
+        <v>40</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.131</v>
+        <v>0.482</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.334</v>
+        <v>0.482</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1202,33 +1202,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.0464</v>
+        <v>0.115</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7164700</v>
+        <v>8841700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+        <v>3.27</v>
+      </c>
+      <c r="H17" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="J17" s="2" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.092</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1240,40 +1247,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.0112</v>
+        <v>0.795</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>0.053</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6861700</v>
+        <v>7703900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H18" t="n">
-        <v>40</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.482</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1285,39 +1285,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.015</v>
+        <v>0.455</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.0341</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5853600</v>
+        <v>7090300</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
+        <v>60.99</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.921</v>
+        <v>0.423</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.727</v>
+        <v>0.364</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1341,19 +1341,19 @@
       <c r="D20" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>0.0061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4942000</v>
+        <v>6869300</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="H20" t="n">
         <v>57.12</v>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>2.03</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.015</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4784900</v>
+        <v>6868500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.21</v>
+        <v>0.23</v>
       </c>
       <c r="H21" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.85</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.097</v>
+        <v>1.921</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.727</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,40 +1420,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.0341</v>
+        <v>0.375</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.1194</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4640300</v>
+        <v>6669000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.23</v>
+        <v>1.21</v>
       </c>
       <c r="H22" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
+        <v>66.2</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0.364</v>
-      </c>
+        <v>0.315</v>
+      </c>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1465,39 +1463,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.385</v>
+        <v>0.31</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.0267</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4305000</v>
+        <v>6405600</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="H23" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.371</v>
+        <v>0.309</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.369</v>
+        <v>0.299</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1508,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.02</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4166300</v>
+        <v>5857100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.51</v>
+        <v>29.8</v>
       </c>
       <c r="H24" t="n">
-        <v>50.32</v>
+        <v>43.23</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1539,10 +1537,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.299</v>
+        <v>0.023</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.28</v>
+        <v>0.024</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,39 +1553,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3934000</v>
+        <v>5571700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4.41</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+        <v>63.48</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.439</v>
+        <v>0.371</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.439</v>
+        <v>0.369</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,38 +1598,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.0746</v>
+        <v>6.79</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.053</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3924500</v>
+        <v>5263000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H26" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.21</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="K26" s="2" t="n"/>
+        <v>7.292</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>7.644</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1643,39 +1643,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E27" s="3" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3879700</v>
+        <v>4984100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
+        <v>50.17</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.309</v>
+        <v>0.775</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.299</v>
+        <v>0.776</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1688,39 +1688,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3814100</v>
+        <v>4935200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="H28" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.775</v>
+        <v>0.347</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.776</v>
+        <v>0.333</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1733,39 +1733,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.225</v>
+        <v>0.865</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3583200</v>
+        <v>4358800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H29" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+        <v>45.57</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.224</v>
+        <v>0.868</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.239</v>
+        <v>0.869</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,28 +1778,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3405700</v>
+        <v>4212300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H30" t="n">
-        <v>38.01</v>
+        <v>50.32</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5.544</v>
+        <v>0.299</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>5.435</v>
+        <v>0.28</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1823,28 +1823,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.0395</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3398000</v>
+        <v>4094700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>34.49</v>
+        <v>52.58</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.179</v>
+        <v>0.389</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.197</v>
+        <v>0.377</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1868,28 +1868,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.0152</v>
+        <v>5.24</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3371600</v>
+        <v>3952200</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="H32" t="n">
-        <v>47.25</v>
+        <v>37.71</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.346</v>
+        <v>5.543</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.332</v>
+        <v>5.435</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.44</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3268100</v>
+        <v>3934000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.16</v>
+        <v>4.41</v>
       </c>
       <c r="H33" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+        <v>54.33</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.868</v>
+        <v>0.439</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.869</v>
+        <v>0.439</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.295</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.0286</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3027200</v>
+        <v>3703000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="H34" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.164</v>
+        <v>0.295</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.165</v>
+        <v>0.295</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2003,39 +2003,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.555</v>
+        <v>0.225</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.0374</v>
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2959900</v>
+        <v>3607800</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H35" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.67</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.576</v>
+        <v>0.224</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.538</v>
+        <v>0.239</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,39 +2048,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0307</v>
+        <v>0.625</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2621300</v>
+        <v>3587300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H36" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.307</v>
+        <v>0.616</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>7.647</v>
+        <v>0.614</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2093,28 +2093,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.555</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2482400</v>
+        <v>3477200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H37" t="n">
-        <v>23.66</v>
+        <v>47.94</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.72</v>
+        <v>0.576</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.958</v>
+        <v>0.538</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2138,28 +2138,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.39</v>
+        <v>0.165</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2481800</v>
+        <v>3398000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="H38" t="n">
-        <v>51.22</v>
+        <v>34.49</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.388</v>
+        <v>0.179</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.377</v>
+        <v>0.197</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2183,39 +2183,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0119</v>
+        <v>4.79</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2451600</v>
+        <v>3380400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.23</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.538</v>
+        <v>4.727</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.619</v>
+        <v>4.856</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,39 +2228,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.455</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2440300</v>
+        <v>3256700</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="H40" t="n">
-        <v>75.38</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.74</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.829</v>
+        <v>0.513</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0063</v>
+        <v>1.46</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2373200</v>
+        <v>3235200</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="H41" t="n">
-        <v>52.44</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.66</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.725</v>
+        <v>1.72</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4.855</v>
+        <v>1.958</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,39 +2318,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.0106</v>
+        <v>10</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2208300</v>
+        <v>3224400</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H42" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.918</v>
+        <v>10.013</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.873</v>
+        <v>10.16</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2128400</v>
+        <v>3088500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="H43" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31999999999999</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.397</v>
+        <v>0.165</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.407</v>
+        <v>0.166</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0215</v>
+        <v>0.13</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2049200</v>
+        <v>3005600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="H44" t="n">
-        <v>27.74</v>
+        <v>57.1</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.513</v>
+        <v>0.126</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2462,19 +2462,19 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>0.0529</v>
+        <v>0.885</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1924100</v>
+        <v>2943000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H45" t="n">
-        <v>46.48</v>
+        <v>45.01</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1907400</v>
+        <v>2930400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H46" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.73</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.616</v>
+        <v>1.307</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.614</v>
+        <v>1.314</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0306</v>
+        <v>1.08</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.0964</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1892000</v>
+        <v>2721800</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.23</v>
+        <v>1.89</v>
       </c>
       <c r="H47" t="n">
-        <v>46.04</v>
+        <v>48.91</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.055</v>
+        <v>1.088</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.953</v>
+        <v>1.096</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.295</v>
+        <v>0.415</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>-0.0119</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1859000</v>
+        <v>2682100</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="H48" t="n">
-        <v>49.15</v>
+        <v>22.13</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.295</v>
+        <v>0.538</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.295</v>
+        <v>0.619</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,38 +2633,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.046</v>
+        <v>1.14</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0.0459</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1736500</v>
+        <v>2518100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="H49" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.69</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="K49" s="2" t="n"/>
+        <v>0.83</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2676,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.1058</v>
+        <v>1.11</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1651300</v>
+        <v>2325800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H50" t="n">
-        <v>61.54</v>
+        <v>55.47</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2705,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.053</v>
+        <v>1.078</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.905</v>
+        <v>1.044</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2721,28 +2723,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.03</v>
+        <v>0.745</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.0457</v>
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1651100</v>
+        <v>2275100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1.15</v>
+        <v>0.27</v>
       </c>
       <c r="H51" t="n">
-        <v>42.32</v>
+        <v>41.25</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2750,10 +2752,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.083</v>
+        <v>0.773</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.095</v>
+        <v>0.772</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2766,28 +2768,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1621900</v>
+        <v>2250100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="H52" t="n">
-        <v>55.37</v>
+        <v>59.85</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2795,10 +2797,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.826</v>
+        <v>0.918</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.777</v>
+        <v>0.874</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2811,28 +2813,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0021</v>
+        <v>1.01</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.0306</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1597700</v>
+        <v>2232200</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>47.9</v>
+        <v>46.04</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2840,10 +2842,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.913</v>
+        <v>1.055</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.721</v>
+        <v>0.953</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2856,39 +2858,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2.64</v>
+        <v>0.39</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.0272</v>
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1579900</v>
+        <v>2217300</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H54" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.84</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.648</v>
+        <v>0.397</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.549</v>
+        <v>0.407</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2901,39 +2903,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.705</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1575400</v>
+        <v>2205600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.11</v>
+        <v>0.87</v>
       </c>
       <c r="H55" t="n">
-        <v>36.49</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.7</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.163</v>
+        <v>0.647</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.232</v>
+        <v>0.553</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2946,28 +2948,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.29</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1574700</v>
+        <v>2182400</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H56" t="n">
-        <v>56.65</v>
+        <v>25.38</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2975,10 +2977,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.078</v>
+        <v>0.339</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.044</v>
+        <v>0.374</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2991,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1520100</v>
+        <v>2180400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H57" t="n">
-        <v>41.25</v>
+        <v>40.08</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3020,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.773</v>
+        <v>0.511</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.772</v>
+        <v>0.526</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3036,28 +3038,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0673</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1508800</v>
+        <v>2176000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H58" t="n">
-        <v>33.7</v>
+        <v>58.81</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3065,10 +3067,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.237</v>
+        <v>1.049</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.289</v>
+        <v>0.905</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3081,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.625</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1400500</v>
+        <v>2114400</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="H59" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.647</v>
+        <v>0.616</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.553</v>
+        <v>0.604</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3126,39 +3128,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.85</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0.0559</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1351200</v>
+        <v>2111400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.12</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.388</v>
+        <v>0.826</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.391</v>
+        <v>0.777</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3171,39 +3173,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.0208</v>
+        <v>2.65</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1343300</v>
+        <v>2071600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H61" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.56</v>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.511</v>
+        <v>2.649</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.526</v>
+        <v>2.55</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3216,39 +3218,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0147</v>
+        <v>1.68</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.006</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1328600</v>
+        <v>2059900</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.57</v>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.045</v>
+        <v>1.625</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.073</v>
+        <v>1.699</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3261,28 +3263,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0.0192</v>
+        <v>1.21</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1309000</v>
+        <v>1851500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>54.35</v>
+        <v>55.6</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3290,10 +3292,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.521</v>
+        <v>1.172</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.458</v>
+        <v>1.134</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3306,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2.71</v>
+        <v>0.42</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>-0.0345</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1304100</v>
+        <v>1849700</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>44.87</v>
+        <v>17.96</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3335,11 +3337,9 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.778</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>2.735</v>
-      </c>
+        <v>0.464</v>
+      </c>
+      <c r="K64" s="2" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3351,28 +3351,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0.0169</v>
+        <v>4.83</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1299900</v>
+        <v>1773600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>54.56</v>
+        <v>47.37</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.171</v>
+        <v>4.912</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.133</v>
+        <v>4.721</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3396,28 +3396,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.0191</v>
+        <v>2.04</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1290900</v>
+        <v>1766900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H66" t="n">
-        <v>58.44</v>
+        <v>35.23</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.791</v>
+        <v>2.162</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.77</v>
+        <v>2.232</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3441,28 +3441,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>-0.0098</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1280400</v>
+        <v>1689300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="H67" t="n">
-        <v>45.07</v>
+        <v>44.04</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.306</v>
+        <v>2.046</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.314</v>
+        <v>2.073</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3486,28 +3486,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>3.87</v>
+        <v>0.22</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.0574</v>
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1140300</v>
+        <v>1598200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="H68" t="n">
-        <v>52.56</v>
+        <v>33.7</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.854</v>
+        <v>0.237</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>3.664</v>
+        <v>0.289</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3531,28 +3531,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>3.87</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0.0574</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1072100</v>
+        <v>1593700</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>24.06</v>
+        <v>52.56</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.278</v>
+        <v>3.854</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.302</v>
+        <v>3.664</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3576,39 +3576,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.395</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1042800</v>
+        <v>1562000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="H70" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.732</v>
+        <v>0.388</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.745</v>
+        <v>0.391</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3621,39 +3621,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>-0.004</v>
+        <v>0.525</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1024100</v>
+        <v>1513300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H71" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.48</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10.016</v>
+        <v>0.52</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>10.161</v>
+        <v>0.457</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3666,39 +3666,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.0374</v>
+        <v>2.72</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1018500</v>
+        <v>1470600</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.89</v>
+        <v>0.11</v>
       </c>
       <c r="H72" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.79</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.57</v>
+        <v>2.778</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.613</v>
+        <v>2.735</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3711,39 +3711,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.0033</v>
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1015200</v>
+        <v>1446200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.799</v>
+        <v>0.791</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.405</v>
+        <v>0.77</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3756,39 +3756,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.68</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>932500</v>
+        <v>1339100</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.75</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.616</v>
+        <v>0.732</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.604</v>
+        <v>0.745</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3801,39 +3801,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>3.11</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>0.013</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>917300</v>
+        <v>1337500</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="H75" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.64</v>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.914</v>
+        <v>2.802</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.869</v>
+        <v>2.406</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3857,14 +3857,14 @@
       <c r="D76" s="2" t="n">
         <v>3.76</v>
       </c>
-      <c r="E76" s="8" t="n">
+      <c r="E76" s="9" t="n">
         <v>0.0108</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>846100</v>
+        <v>1329400</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H76" t="n">
         <v>56.82</v>
@@ -3891,28 +3891,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>803300</v>
+        <v>1257900</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H77" t="n">
-        <v>52.56</v>
+        <v>30.1</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.79</v>
+        <v>0.278</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.655</v>
+        <v>0.302</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3936,39 +3936,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0.0374</v>
+        <v>6.37</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>771300</v>
+        <v>1240200</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.4</v>
+        <v>0.19</v>
       </c>
       <c r="H78" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.1</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.11</v>
+        <v>6.414</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.128</v>
+        <v>6.776</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3981,39 +3981,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0.0069</v>
+        <v>1.26</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>744000</v>
+        <v>1215500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.57</v>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7.482</v>
+        <v>1.188</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>7.978</v>
+        <v>1.183</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4026,28 +4026,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0.0053</v>
+        <v>2.82</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>732100</v>
+        <v>1163200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H80" t="n">
-        <v>45.92</v>
+        <v>53.62</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3.945</v>
+        <v>2.792</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.535</v>
+        <v>2.656</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4071,28 +4071,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0185</v>
+        <v>1.29</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0.032</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>723600</v>
+        <v>1145300</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.33</v>
+        <v>0.49</v>
       </c>
       <c r="H81" t="n">
-        <v>16.07</v>
+        <v>56.29</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.954</v>
+        <v>1.251</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.085</v>
+        <v>1.169</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4116,39 +4116,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.265</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>720200</v>
+        <v>1094200</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>11.81</v>
+        <v>0.14</v>
       </c>
       <c r="H82" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.736</v>
+        <v>0.275</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.741</v>
+        <v>0.296</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4161,28 +4161,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
+        <v>7.29</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>709300</v>
+        <v>1079100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>27.28</v>
+        <v>33.18</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.412</v>
+        <v>7.478</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.571</v>
+        <v>7.977</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.41</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>0.038</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>706000</v>
+        <v>1077600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H84" t="n">
-        <v>52.61</v>
+        <v>47.49</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.764</v>
+        <v>0.423</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.415</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.011</v>
+        <v>0.915</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>688100</v>
+        <v>1057100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.12</v>
+        <v>0.66</v>
       </c>
       <c r="H85" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.31</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>6.133</v>
+        <v>0.915</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>5.893</v>
+        <v>0.869</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4296,28 +4296,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0.0289</v>
+        <v>3.81</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>672300</v>
+        <v>1032300</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H86" t="n">
-        <v>57.91</v>
+        <v>47.71</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.771</v>
+        <v>3.95</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2.185</v>
+        <v>3.536</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4341,39 +4341,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.535</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.049</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>663600</v>
+        <v>1021000</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H87" t="n">
-        <v>32.16</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.68</v>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>6.068</v>
+        <v>0.497</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>6.333</v>
+        <v>0.463</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4397,14 +4397,14 @@
       <c r="D88" s="2" t="n">
         <v>0.605</v>
       </c>
-      <c r="E88" s="8" t="n">
+      <c r="E88" s="9" t="n">
         <v>0.0254</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>636800</v>
+        <v>1018900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H88" t="n">
         <v>41.82</v>
@@ -4431,39 +4431,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.0086</v>
+        <v>0.555</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>626500</v>
+        <v>1018500</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.14</v>
+        <v>0.89</v>
       </c>
       <c r="H89" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.94</v>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.598</v>
+        <v>0.57</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.585</v>
+        <v>0.613</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,28 +4476,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0181</v>
+        <v>2.86</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>0.0325</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>607400</v>
+        <v>1011100</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H90" t="n">
-        <v>33.02</v>
+        <v>58.22</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.847</v>
+        <v>2.772</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.862</v>
+        <v>2.185</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4521,28 +4521,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>2.58</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>582800</v>
+        <v>970800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H91" t="n">
-        <v>50.91</v>
+        <v>47.56</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.637</v>
+        <v>2.617</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.621</v>
+        <v>2.605</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4566,39 +4566,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.54</v>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>0.0251</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>562900</v>
+        <v>964700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H92" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
+        <v>57.58</v>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.624</v>
+        <v>6.142</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.699</v>
+        <v>5.895</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4611,39 +4611,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>0.0234</v>
+        <v>1.12</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>559800</v>
+        <v>936300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.06</v>
+        <v>1.7</v>
       </c>
       <c r="H93" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.7</v>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.111</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.128</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4656,28 +4656,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.27</v>
+        <v>0.72</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>548900</v>
+        <v>926000</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="H94" t="n">
-        <v>54.58</v>
+        <v>45.72</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.25</v>
+        <v>0.733</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.169</v>
+        <v>0.728</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4701,28 +4701,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>0.021</v>
+        <v>0.79</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>548400</v>
+        <v>870300</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="H95" t="n">
-        <v>50.8</v>
+        <v>15.81</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.74</v>
+        <v>0.953</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.673</v>
+        <v>1.085</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4746,39 +4746,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>0.0242</v>
+        <v>5.86</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>515600</v>
+        <v>860600</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H96" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.57</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.189</v>
+        <v>6.069</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1.184</v>
+        <v>6.333</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4791,28 +4791,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0.0177</v>
+        <v>5.11</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>510300</v>
+        <v>847600</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H97" t="n">
-        <v>56.23</v>
+        <v>53.51</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>5.07</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.513</v>
+        <v>5.062</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4836,28 +4836,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.59</v>
+        <v>1.28</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0.0157</v>
+        <v>0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>506800</v>
+        <v>817700</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H98" t="n">
-        <v>48.35</v>
+        <v>27.28</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4865,16 +4865,1411 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.618</v>
+        <v>1.412</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.605</v>
+        <v>1.571</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>779500</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H99" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>763300</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H100" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>743500</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H101" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>720200</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H102" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>718500</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H103" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>710600</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H104" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>5.398</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>692300</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H105" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>672800</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H106" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>660500</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H107" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>645800</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H108" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>640200</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H109" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>623600</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H110" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>2.158</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>612700</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H111" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>610700</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>600400</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H113" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>10.414</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>9.731</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H114" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>582800</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H115" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>580900</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H116" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>567500</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H117" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>565900</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H118" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>556600</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>555800</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H120" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>550400</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H121" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="E122" s="9" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>545500</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H122" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>7.368</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>6.884</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>539600</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H123" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>536500</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H124" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>536100</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>535100</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H126" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>503500</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H127" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>502100</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>0.04480000000000001</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>501800</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H129" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>2.209</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M98"/>
+  <autoFilter ref="A1:M129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.2308</v>
+        <v>-0.1538</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>115145800</v>
+        <v>141070300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H2" t="n">
-        <v>22.65</v>
+        <v>23.14</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.334</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>60834700</v>
+        <v>61950000</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.91</v>
+        <v>0.915</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.0111</v>
+        <v>0.0167</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>27296500</v>
+        <v>31660300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H4" t="n">
-        <v>67.28</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
@@ -669,28 +669,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-0.0278</v>
+        <v>0.04</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20543300</v>
+        <v>21206400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.88</v>
+        <v>33.68</v>
       </c>
       <c r="H5" t="n">
-        <v>40.36</v>
+        <v>46.69</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.19</v>
+        <v>0.041</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.185</v>
+        <v>0.043</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.175</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17725100</v>
+        <v>20634400</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.23</v>
+        <v>0.89</v>
       </c>
       <c r="H6" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.36</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.301</v>
+        <v>0.19</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.255</v>
+        <v>0.185</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,28 +759,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17249800</v>
+        <v>19339400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>77.59999999999999</v>
+        <v>68.66</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.611</v>
+        <v>0.301</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.526</v>
+        <v>0.255</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>7.36</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17162100</v>
+        <v>17363100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>27.25</v>
+        <v>1.17</v>
       </c>
       <c r="H8" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.06</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.041</v>
+        <v>7.557</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.043</v>
+        <v>7.7</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,28 +849,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.0174</v>
+        <v>0.675</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16417000</v>
+        <v>17249800</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>38.72</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.556</v>
+        <v>0.611</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>7.7</v>
+        <v>0.526</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>15187500</v>
+        <v>16747200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6.52</v>
+        <v>7.18</v>
       </c>
       <c r="H10" t="n">
-        <v>69.25</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.047</v>
@@ -939,39 +939,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.145</v>
+        <v>0.42</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.0118</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14215100</v>
+        <v>14988500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H11" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.161</v>
+        <v>0.378</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.138</v>
+        <v>0.27</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.1818</v>
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14080100</v>
+        <v>14543000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>258.14</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.057</v>
+        <v>0.161</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.063</v>
+        <v>0.138</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,28 +1029,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>13466500</v>
+        <v>14297700</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>12.51</v>
+        <v>262.13</v>
       </c>
       <c r="H13" t="n">
-        <v>68.44</v>
+        <v>57.82</v>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,28 +1074,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.0118</v>
+        <v>0.075</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>13260100</v>
+        <v>13654300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.37</v>
+        <v>12.68</v>
       </c>
       <c r="H14" t="n">
-        <v>74.48999999999999</v>
+        <v>68.44</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.378</v>
+        <v>0.059</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.27</v>
+        <v>0.057</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         <v>-0.0196</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11001800</v>
+        <v>11556900</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.45</v>
+        <v>0.455</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.0112</v>
+        <v>0.0225</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10425300</v>
+        <v>11258400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>41.76</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0417</v>
+        <v>0.82</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8841700</v>
+        <v>10091300</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.27</v>
+        <v>0.63</v>
       </c>
       <c r="H17" t="n">
-        <v>69.55</v>
+        <v>57.12</v>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.092</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.092</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1247,33 +1247,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.795</v>
+        <v>2.01</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.053</v>
+        <v>0.005</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7703900</v>
+        <v>9668900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>58.91</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="J18" s="2" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1.727</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1285,28 +1292,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.0341</v>
+        <v>0.115</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7090300</v>
+        <v>8896800</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.35</v>
+        <v>3.29</v>
       </c>
       <c r="H19" t="n">
-        <v>60.99</v>
+        <v>69.55</v>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
@@ -1314,10 +1321,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.423</v>
+        <v>0.092</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.364</v>
+        <v>0.092</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1330,40 +1337,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.0464</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6869300</v>
+        <v>8691500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H20" t="n">
-        <v>57.12</v>
+        <v>0.08</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
     </row>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.015</v>
+        <v>6.78</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0544</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6868500</v>
+        <v>8669100</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.23</v>
+        <v>1.12</v>
       </c>
       <c r="H21" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.01</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.921</v>
+        <v>7.291</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.727</v>
+        <v>7.644</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1194</v>
+        <v>0.1343</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6669000</v>
+        <v>8611200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="H22" t="n">
-        <v>66.2</v>
+        <v>67.05</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6405600</v>
+        <v>7921700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H23" t="n">
         <v>54.55</v>
@@ -1523,10 +1523,10 @@
         <v>-0.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5857100</v>
+        <v>7799200</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>29.8</v>
+        <v>39.69</v>
       </c>
       <c r="H24" t="n">
         <v>43.23</v>
@@ -1568,10 +1568,10 @@
         <v>0.0267</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5571700</v>
+        <v>7518800</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.78</v>
+        <v>1.05</v>
       </c>
       <c r="H25" t="n">
         <v>63.48</v>
@@ -1598,39 +1598,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.053</v>
+        <v>0.45</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5263000</v>
+        <v>7367000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="H26" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.06</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7.292</v>
+        <v>0.422</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>7.644</v>
+        <v>0.364</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4984100</v>
+        <v>6634100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H27" t="n">
         <v>50.17</v>
@@ -1688,28 +1688,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.295</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4935200</v>
+        <v>6621900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>49.14</v>
+        <v>50.32</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.347</v>
+        <v>0.299</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.333</v>
+        <v>0.28</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1733,39 +1733,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.865</v>
+        <v>0.46</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4358800</v>
+        <v>6116500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H29" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.37</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.868</v>
+        <v>0.513</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.869</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.295</v>
+        <v>0.865</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0167</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4212300</v>
+        <v>6100800</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="H30" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.299</v>
+        <v>0.868</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.28</v>
+        <v>0.869</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.0395</v>
+        <v>0.215</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4094700</v>
+        <v>5655900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.22</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.389</v>
+        <v>0.223</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.377</v>
+        <v>0.239</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1868,28 +1868,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-0.0076</v>
+        <v>0.34</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3952200</v>
+        <v>5543300</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H32" t="n">
-        <v>37.71</v>
+        <v>49.14</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.543</v>
+        <v>0.347</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5.435</v>
+        <v>0.333</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3934000</v>
+        <v>5244800</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>4.41</v>
+        <v>0.42</v>
       </c>
       <c r="H33" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.22</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.439</v>
+        <v>0.388</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.439</v>
+        <v>0.377</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1958,28 +1958,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
+        <v>5.27</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.0019</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3703000</v>
+        <v>4608600</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.19</v>
+        <v>0.32</v>
       </c>
       <c r="H34" t="n">
-        <v>49.15</v>
+        <v>38.63</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.295</v>
+        <v>5.546</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.295</v>
+        <v>5.435</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2003,28 +2003,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0</v>
+        <v>4.78</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3607800</v>
+        <v>4281900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H35" t="n">
-        <v>48.67</v>
+        <v>53.35</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.224</v>
+        <v>4.726</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.239</v>
+        <v>4.856</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,28 +2048,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.625</v>
+        <v>0.44</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3587300</v>
+        <v>4183100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.33</v>
+        <v>4.69</v>
       </c>
       <c r="H36" t="n">
-        <v>56.82</v>
+        <v>54.33</v>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.616</v>
+        <v>0.439</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.614</v>
+        <v>0.439</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2093,28 +2093,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.555</v>
+        <v>1.46</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.0069</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3477200</v>
+        <v>4046900</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H37" t="n">
-        <v>47.94</v>
+        <v>23.66</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.576</v>
+        <v>1.72</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.538</v>
+        <v>1.958</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2138,28 +2138,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.165</v>
+        <v>0.48</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3398000</v>
+        <v>3963700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H38" t="n">
-        <v>34.49</v>
+        <v>38.06</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.179</v>
+        <v>0.51</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.197</v>
+        <v>0.526</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2183,28 +2183,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.625</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3380400</v>
+        <v>3885600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H39" t="n">
-        <v>54.23</v>
+        <v>56.82</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.727</v>
+        <v>0.616</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.856</v>
+        <v>0.614</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,28 +2228,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.0215</v>
+        <v>0.555</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3256700</v>
+        <v>3737700</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>27.74</v>
+        <v>47.94</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.513</v>
+        <v>0.576</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.0069</v>
+        <v>0.295</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3235200</v>
+        <v>3703000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.29</v>
+        <v>1.19</v>
       </c>
       <c r="H41" t="n">
-        <v>23.66</v>
+        <v>49.15</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.72</v>
+        <v>0.295</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.958</v>
+        <v>0.295</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3224400</v>
+        <v>3560500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H42" t="n">
         <v>46.97</v>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.165</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3088500</v>
+        <v>3411500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.165</v>
+        <v>0.179</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.166</v>
+        <v>0.197</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-0.07139999999999999</v>
+        <v>0.1</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3005600</v>
+        <v>3404200</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="H44" t="n">
-        <v>57.1</v>
+        <v>36.27</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.1</v>
+        <v>0.121</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,28 +2453,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0.0412</v>
+        <v>0.13</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2943000</v>
+        <v>3295900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>45.01</v>
+        <v>57.1</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.843</v>
+        <v>0.1</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.66</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2930400</v>
+        <v>3197400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="H46" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.01</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.307</v>
+        <v>1.623</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.314</v>
+        <v>1.699</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,39 +2543,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.08</v>
+        <v>0.18</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>0.0964</v>
+        <v>0.0286</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2721800</v>
+        <v>3175900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.89</v>
+        <v>0.59</v>
       </c>
       <c r="H47" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.97</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.088</v>
+        <v>0.164</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1.096</v>
+        <v>0.165</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.0119</v>
+        <v>1.28</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2682100</v>
+        <v>3157700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H48" t="n">
-        <v>22.13</v>
+        <v>45.07</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.538</v>
+        <v>1.306</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.619</v>
+        <v>1.314</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,39 +2633,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>0.0459</v>
+        <v>0.1066</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2518100</v>
+        <v>3116800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.64</v>
+        <v>2.16</v>
       </c>
       <c r="H49" t="n">
-        <v>75.69</v>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.05</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.83</v>
+        <v>1.089</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.096</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0471</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2325800</v>
+        <v>3106900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>55.47</v>
+        <v>45.75</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.078</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.044</v>
+        <v>0.844</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,39 +2723,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2275100</v>
+        <v>3089400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="H51" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.56</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.773</v>
+        <v>2.649</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.772</v>
+        <v>2.55</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,28 +2768,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0053</v>
+        <v>0.745</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2250100</v>
+        <v>2921700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H52" t="n">
-        <v>59.85</v>
+        <v>41.25</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.918</v>
+        <v>0.773</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.874</v>
+        <v>0.772</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,28 +2813,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.42</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2232200</v>
+        <v>2920700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H53" t="n">
-        <v>46.04</v>
+        <v>22.54</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.055</v>
+        <v>0.538</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.953</v>
+        <v>0.619</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,28 +2858,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0</v>
+        <v>3.84</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2217300</v>
+        <v>2828000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="H54" t="n">
-        <v>33.84</v>
+        <v>58.58</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.397</v>
+        <v>3.644</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.407</v>
+        <v>2.964</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,39 +2903,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E55" s="9" t="n">
-        <v>0.0444</v>
+        <v>4.81</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2205600</v>
+        <v>2782200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="H55" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.36</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.647</v>
+        <v>4.91</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.553</v>
+        <v>4.721</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,39 +2948,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>0.0357</v>
+        <v>1.09</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2182400</v>
+        <v>2736400</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.05</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.339</v>
+        <v>0.825</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.374</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0.0104</v>
+        <v>1.73</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2180400</v>
+        <v>2715500</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.26</v>
+        <v>0.84</v>
       </c>
       <c r="H57" t="n">
-        <v>40.08</v>
+        <v>27.95</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.511</v>
+        <v>1.832</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.526</v>
+        <v>1.971</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,39 +3038,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0673</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2176000</v>
+        <v>2492900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.51</v>
+        <v>0.99</v>
       </c>
       <c r="H58" t="n">
-        <v>58.81</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.049</v>
+        <v>0.646</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.905</v>
+        <v>0.552</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.625</v>
+        <v>1.1</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2114400</v>
+        <v>2485200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H59" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.616</v>
+        <v>1.048</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.604</v>
+        <v>0.904</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,28 +3128,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.0559</v>
+        <v>0.0183</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2111400</v>
+        <v>2398700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>56.12</v>
+        <v>55.47</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.826</v>
+        <v>1.078</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.777</v>
+        <v>1.044</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,39 +3173,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2.65</v>
+        <v>1.01</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0306</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2071600</v>
+        <v>2378000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="H61" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.04</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.649</v>
+        <v>1.055</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.55</v>
+        <v>0.953</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,39 +3218,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.68</v>
+        <v>0.29</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>0.006</v>
+        <v>0.0357</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2059900</v>
+        <v>2365500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H62" t="n">
-        <v>55.57</v>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.38</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.625</v>
+        <v>0.339</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.699</v>
+        <v>0.374</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,28 +3263,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.39</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1851500</v>
+        <v>2317300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>55.6</v>
+        <v>33.84</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.172</v>
+        <v>0.397</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.134</v>
+        <v>0.407</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.0053</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1849700</v>
+        <v>2289400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="H64" t="n">
-        <v>17.96</v>
+        <v>59.85</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3337,9 +3337,11 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K64" s="2" t="n"/>
+        <v>0.918</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.874</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3351,39 +3353,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.625</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1773600</v>
+        <v>2270000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H65" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.912</v>
+        <v>0.616</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.721</v>
+        <v>0.604</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3396,39 +3398,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2.04</v>
+        <v>0.54</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>0.0049</v>
+        <v>0.0588</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1766900</v>
+        <v>2264300</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.13</v>
+        <v>0.58</v>
       </c>
       <c r="H66" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.162</v>
+        <v>0.497</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2.232</v>
+        <v>0.464</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3441,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0.84</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1689300</v>
+        <v>2236400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H67" t="n">
-        <v>44.04</v>
+        <v>54.6</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3470,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.046</v>
+        <v>0.825</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.073</v>
+        <v>0.777</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3486,28 +3488,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1598200</v>
+        <v>2152200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H68" t="n">
-        <v>33.7</v>
+        <v>36.49</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3515,10 +3517,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.237</v>
+        <v>2.163</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.289</v>
+        <v>2.232</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3531,28 +3533,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3.87</v>
+        <v>1.2</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>0.0574</v>
+        <v>0.0169</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1593700</v>
+        <v>2017300</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H69" t="n">
-        <v>52.56</v>
+        <v>54.56</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3560,10 +3562,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3.854</v>
+        <v>1.171</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.664</v>
+        <v>1.133</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3576,39 +3578,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E70" s="9" t="n">
-        <v>0.0128</v>
+        <v>2.02</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1562000</v>
+        <v>1994700</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H70" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.04</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.388</v>
+        <v>2.046</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.391</v>
+        <v>2.073</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3621,28 +3623,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.525</v>
+        <v>0.8</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0191</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1513300</v>
+        <v>1966800</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H71" t="n">
-        <v>53.48</v>
+        <v>58.44</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3650,10 +3652,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.52</v>
+        <v>0.791</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.457</v>
+        <v>0.77</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3666,28 +3668,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>0.0037</v>
+        <v>0.415</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.046</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1470600</v>
+        <v>1932500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.11</v>
+        <v>0.34</v>
       </c>
       <c r="H72" t="n">
-        <v>45.79</v>
+        <v>16.79</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3695,11 +3697,9 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.778</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>2.735</v>
-      </c>
+        <v>0.463</v>
+      </c>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3711,28 +3711,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E73" s="9" t="n">
-        <v>0.0191</v>
+        <v>2.7</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1446200</v>
+        <v>1912300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H73" t="n">
-        <v>58.44</v>
+        <v>44.12</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.791</v>
+        <v>2.777</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.77</v>
+        <v>2.734</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3756,28 +3756,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.68</v>
+        <v>3.89</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1339100</v>
+        <v>1845400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.41</v>
+        <v>0.65</v>
       </c>
       <c r="H74" t="n">
-        <v>38.75</v>
+        <v>53.37</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.732</v>
+        <v>3.856</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.745</v>
+        <v>3.665</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3801,39 +3801,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>3.11</v>
+        <v>0.525</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>0.013</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1337500</v>
+        <v>1770000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="H75" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.48</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.802</v>
+        <v>0.52</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.406</v>
+        <v>0.457</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3846,28 +3846,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0.0108</v>
+        <v>6.37</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1329400</v>
+        <v>1750500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H76" t="n">
-        <v>56.82</v>
+        <v>44.1</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3.636</v>
+        <v>6.414</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.962</v>
+        <v>6.776</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3891,39 +3891,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>0.0196</v>
+        <v>4.67</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1257900</v>
+        <v>1736400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.14</v>
+        <v>0.96</v>
       </c>
       <c r="H77" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.278</v>
+        <v>4.591</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.302</v>
+        <v>4.493</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3936,39 +3936,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.07</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1240200</v>
+        <v>1662600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.19</v>
+        <v>3.02</v>
       </c>
       <c r="H78" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.03</v>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6.414</v>
+        <v>1.106</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>6.776</v>
+        <v>1.127</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3981,39 +3981,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0.0161</v>
+        <v>0.22</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1215500</v>
+        <v>1644400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="H79" t="n">
-        <v>60.57</v>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.7</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.188</v>
+        <v>0.237</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1.183</v>
+        <v>0.289</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4026,39 +4026,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2.82</v>
+        <v>0.395</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0444</v>
+        <v>0.0128</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1163200</v>
+        <v>1609000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
       <c r="H80" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.792</v>
+        <v>0.388</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2.656</v>
+        <v>0.391</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4071,28 +4071,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.29</v>
+        <v>0.675</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>0.032</v>
+        <v>0.0227</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1145300</v>
+        <v>1575200</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>0.49</v>
       </c>
       <c r="H81" t="n">
-        <v>56.29</v>
+        <v>37.6</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.251</v>
+        <v>0.731</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.169</v>
+        <v>0.745</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4116,28 +4116,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.265</v>
+        <v>0.595</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1094200</v>
+        <v>1545800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H82" t="n">
-        <v>44.4</v>
+        <v>39.79</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.275</v>
+        <v>0.656</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.296</v>
+        <v>0.619</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4161,28 +4161,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>7.29</v>
+        <v>1.3</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>0.0014</v>
+        <v>0.04</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1079100</v>
+        <v>1524700</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="H83" t="n">
-        <v>33.18</v>
+        <v>57.1</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>7.478</v>
+        <v>1.252</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>7.977</v>
+        <v>1.17</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4206,39 +4206,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.41</v>
+        <v>1.25</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.038</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1077600</v>
+        <v>1489600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.55</v>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.423</v>
+        <v>1.187</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.415</v>
+        <v>1.183</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4251,28 +4251,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E85" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.38</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1057100</v>
+        <v>1464800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.66</v>
+        <v>1.37</v>
       </c>
       <c r="H85" t="n">
-        <v>51.31</v>
+        <v>49.68</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.915</v>
+        <v>0.38</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.869</v>
+        <v>0.378</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4305,19 +4305,19 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.0187</v>
+        <v>0.0321</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1032300</v>
+        <v>1458400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H86" t="n">
-        <v>47.71</v>
+        <v>49.39</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.95</v>
+        <v>3.955</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3.536</v>
+        <v>3.537</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4341,28 +4341,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.535</v>
+        <v>2.31</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>0.049</v>
+        <v>0.0221</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1021000</v>
+        <v>1451800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="H87" t="n">
-        <v>61.68</v>
+        <v>58.82</v>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.497</v>
+        <v>2.216</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.463</v>
+        <v>2.158</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4386,28 +4386,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.605</v>
+        <v>2.82</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.0444</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1018900</v>
+        <v>1443700</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H88" t="n">
-        <v>41.82</v>
+        <v>53.62</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.656</v>
+        <v>2.792</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.619</v>
+        <v>2.656</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4431,39 +4431,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.555</v>
+        <v>2.57</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1018500</v>
+        <v>1434500</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.89</v>
+        <v>0.23</v>
       </c>
       <c r="H89" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.75</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.57</v>
+        <v>2.616</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.613</v>
+        <v>2.605</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,28 +4476,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.86</v>
+        <v>7.31</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.0325</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1011100</v>
+        <v>1422100</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H90" t="n">
-        <v>58.22</v>
+        <v>34.62</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.772</v>
+        <v>7.48</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.185</v>
+        <v>7.977</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4521,28 +4521,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E91" s="9" t="n">
-        <v>0.0118</v>
+        <v>0.63</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>970800</v>
+        <v>1405900</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="H91" t="n">
-        <v>47.56</v>
+        <v>47.9</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2.617</v>
+        <v>0.637</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2.605</v>
+        <v>0.621</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4566,39 +4566,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>6.54</v>
+        <v>0.41</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.038</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>964700</v>
+        <v>1380700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H92" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>6.142</v>
+        <v>0.423</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>5.895</v>
+        <v>0.415</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4611,28 +4611,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>0.0467</v>
+        <v>1.91</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>936300</v>
+        <v>1371100</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1.7</v>
+        <v>0.23</v>
       </c>
       <c r="H93" t="n">
-        <v>50.7</v>
+        <v>45.97</v>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.111</v>
+        <v>1.926</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.128</v>
+        <v>1.952</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4656,39 +4656,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>926000</v>
+        <v>1365500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="H94" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.37</v>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.733</v>
+        <v>2.801</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.728</v>
+        <v>2.406</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0247</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>870300</v>
+        <v>1361900</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="H95" t="n">
-        <v>15.81</v>
+        <v>15.31</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.953</v>
+        <v>0.952</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1.085</v>
@@ -4746,28 +4746,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.0135</v>
+        <v>0.26</v>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>860600</v>
+        <v>1360200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H96" t="n">
-        <v>32.57</v>
+        <v>30.1</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6.069</v>
+        <v>0.278</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>6.333</v>
+        <v>0.302</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4791,28 +4791,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>5.11</v>
+        <v>6.76</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0.0119</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>847600</v>
+        <v>1349100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H97" t="n">
-        <v>53.51</v>
+        <v>50.09</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>5.07</v>
+        <v>6.756</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5.062</v>
+        <v>6.83</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4836,39 +4836,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>0</v>
+        <v>6.47</v>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>817700</v>
+        <v>1309400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.412</v>
+        <v>6.135</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.571</v>
+        <v>5.893</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4881,28 +4881,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E99" s="9" t="n">
-        <v>0.02</v>
+        <v>0.85</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>779500</v>
+        <v>1303100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H99" t="n">
-        <v>53.42</v>
+        <v>17.77</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.764</v>
+        <v>0.924</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.976</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4926,28 +4926,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.65</v>
+        <v>0.865</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0058</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>763300</v>
+        <v>1275900</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="H100" t="n">
-        <v>43.65</v>
+        <v>51.9</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4971,39 +4971,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.63</v>
+        <v>0.645</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>743500</v>
+        <v>1255100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>9.779999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="H101" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.6</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.547</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.542</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5016,39 +5016,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.76</v>
+        <v>0.595</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.0259</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>720200</v>
+        <v>1253300</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>11.81</v>
+        <v>0.29</v>
       </c>
       <c r="H102" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.14</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.736</v>
+        <v>0.599</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.741</v>
+        <v>0.585</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5061,28 +5061,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.59</v>
+        <v>2.89</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>0.0172</v>
+        <v>0.0433</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>718500</v>
+        <v>1177600</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>49.06</v>
+        <v>59.13</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.598</v>
+        <v>2.775</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.585</v>
+        <v>2.185</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5106,28 +5106,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>0.0389</v>
+        <v>0.25</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>710600</v>
+        <v>1152600</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.19</v>
+        <v>1.47</v>
       </c>
       <c r="H104" t="n">
-        <v>53.59</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>5.515</v>
+        <v>0.22</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>5.398</v>
+        <v>0.209</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5151,39 +5151,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.0154</v>
+        <v>1.21</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>692300</v>
+        <v>1123100</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H105" t="n">
-        <v>47.53</v>
-      </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.44</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.927</v>
+        <v>1.238</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.952</v>
+        <v>1.329</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5196,28 +5196,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.77</v>
+        <v>0.265</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0147</v>
+        <v>0.0392</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>672800</v>
+        <v>1094200</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>39.3</v>
+        <v>44.4</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.906</v>
+        <v>0.275</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.018</v>
+        <v>0.296</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5241,28 +5241,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.3</v>
+        <v>5.09</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>0.04</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>660500</v>
+        <v>1091700</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H107" t="n">
-        <v>47.66</v>
+        <v>52.3</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.331</v>
+        <v>5.068</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.279</v>
+        <v>5.062</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5286,39 +5286,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.735</v>
+        <v>5.56</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.028</v>
+        <v>0.0296</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>645800</v>
+        <v>1086200</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H108" t="n">
-        <v>51.61</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.45</v>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.741</v>
+        <v>5.51</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.673</v>
+        <v>5.397</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5331,28 +5331,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>-0.006</v>
+        <v>0.345</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>640200</v>
+        <v>1077100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="H109" t="n">
-        <v>36.21</v>
+        <v>48.33</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.848</v>
+        <v>0.354</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.862</v>
+        <v>0.326</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5376,39 +5376,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2.3</v>
+        <v>0.92</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0222</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>623600</v>
+        <v>1058100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.17</v>
+        <v>0.66</v>
       </c>
       <c r="H110" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.215</v>
+        <v>0.916</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.158</v>
+        <v>0.87</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5421,28 +5421,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.036</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>612700</v>
+        <v>1040600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H111" t="n">
-        <v>57.27</v>
+        <v>57.09</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.732</v>
+        <v>1.112</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.703</v>
+        <v>0.879</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5466,28 +5466,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E112" s="9" t="n">
-        <v>0.009000000000000001</v>
+        <v>5.86</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>610700</v>
+        <v>1027000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H112" t="n">
-        <v>54.99</v>
+        <v>32.57</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.109</v>
+        <v>6.069</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.878</v>
+        <v>6.333</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5511,28 +5511,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="E113" s="9" t="n">
-        <v>0.0329</v>
+        <v>0.27</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>600400</v>
+        <v>1026200</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.16</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="n">
-        <v>58.02</v>
+        <v>41.54</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>10.414</v>
+        <v>0.272</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>9.731</v>
+        <v>0.276</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5556,28 +5556,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.885</v>
+        <v>0.33</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0476</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>599000</v>
+        <v>1023600</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
       <c r="H114" t="n">
-        <v>36.85</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.911</v>
+        <v>0.269</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.929</v>
+        <v>0.217</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5601,28 +5601,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>582800</v>
+        <v>1021900</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>50.91</v>
+        <v>30.55</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.637</v>
+        <v>0.975</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.621</v>
+        <v>1.056</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5646,39 +5646,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.575</v>
+        <v>0.555</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0374</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>580900</v>
+        <v>1018500</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.11</v>
+        <v>0.89</v>
       </c>
       <c r="H116" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.94</v>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.513</v>
+        <v>0.613</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5691,39 +5691,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>-0.0114</v>
+        <v>1.02</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>567500</v>
+        <v>1010600</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.18</v>
+        <v>1.43</v>
       </c>
       <c r="H117" t="n">
-        <v>28.83</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.833</v>
+        <v>1.002</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.972</v>
+        <v>0.983</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5736,39 +5736,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>565900</v>
+        <v>975300</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="H118" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.39</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.37</v>
+        <v>0.732</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.343</v>
+        <v>0.728</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5781,28 +5781,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>-0.0058</v>
+        <v>2.78</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>556600</v>
+        <v>968700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H119" t="n">
-        <v>17.77</v>
+        <v>40.07</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.924</v>
+        <v>2.907</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.976</v>
+        <v>3.018</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5826,39 +5826,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E120" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.28</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>555800</v>
+        <v>965700</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H120" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.28</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.109</v>
+        <v>1.412</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.059</v>
+        <v>1.571</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5871,28 +5871,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.52</v>
+        <v>0.765</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>0.0297</v>
+        <v>0.02</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>550400</v>
+        <v>929600</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="H121" t="n">
-        <v>49.81</v>
+        <v>53.42</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.525</v>
+        <v>0.764</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.506</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5916,28 +5916,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>7.42</v>
+        <v>0.765</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>0.0334</v>
+        <v>0.0408</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>545500</v>
+        <v>904700</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="H122" t="n">
-        <v>53.75</v>
+        <v>56.66</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>7.368</v>
+        <v>0.732</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>6.884</v>
+        <v>0.703</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5961,39 +5961,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1.02</v>
+        <v>0.625</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.0684</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>539600</v>
+        <v>880400</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.12</v>
+        <v>11.58</v>
       </c>
       <c r="H123" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.84</v>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.047</v>
+        <v>0.546</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.542</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6006,28 +6006,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>-0.0036</v>
+        <v>1.27</v>
+      </c>
+      <c r="E124" s="9" t="n">
+        <v>0.04099999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>536500</v>
+        <v>853100</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="H124" t="n">
-        <v>39.22</v>
+        <v>49.95</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.859</v>
+        <v>1.284</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.859</v>
+        <v>1.22</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6051,28 +6051,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>536100</v>
+        <v>834300</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="H125" t="n">
-        <v>63.4</v>
+        <v>36.85</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.569</v>
+        <v>0.911</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.467</v>
+        <v>0.929</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6096,28 +6096,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E126" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0282</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>535100</v>
+        <v>803000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="H126" t="n">
-        <v>54.43</v>
+        <v>40.66</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.778</v>
+        <v>0.757</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.768</v>
+        <v>0.723</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6141,39 +6141,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>-0.0211</v>
+        <v>2.15</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>503500</v>
+        <v>782800</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="H127" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.758</v>
+        <v>2.109</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.723</v>
+        <v>2.059</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6186,28 +6186,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2.1</v>
+        <v>0.575</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>0.0145</v>
+        <v>0.0177</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>502100</v>
+        <v>770700</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>51.21</v>
+        <v>56.23</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>2.112</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.988</v>
+        <v>0.513</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6231,28 +6231,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>501800</v>
+        <v>770300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="H129" t="n">
-        <v>40.72</v>
+        <v>47.66</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6260,16 +6260,1231 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2.209</v>
+        <v>1.331</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>2.233</v>
+        <v>1.279</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>754000</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H130" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>13.017</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>13.443</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>733600</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>733300</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H132" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>2.114</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>720200</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H133" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>710700</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H134" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H135" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>10.404</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>9.728999999999999</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>688900</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H136" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>675400</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H137" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>7.361</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E138" s="9" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>660500</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H138" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>2.661</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>658300</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H139" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>1.734</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>651400</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H140" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>639800</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H141" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E142" s="9" t="n">
+        <v>0.04480000000000001</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>636600</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H142" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>2.209</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>627600</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H143" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>624100</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H144" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>619800</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>613500</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H146" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>604400</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H147" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E148" s="9" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>591900</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>4.299</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>4.334</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H149" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2.874</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>569300</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H150" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>3.383</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>3.614</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E151" s="9" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>554600</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H151" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>2.851</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>550600</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H152" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>524300</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H153" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E154" s="9" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>514300</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H154" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>505500</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H155" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>502100</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H156" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M129"/>
+  <autoFilter ref="A1:M156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.1538</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>141070300</v>
+        <v>195863200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H2" t="n">
         <v>23.14</v>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>61950000</v>
+        <v>62286700</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.915</v>
+        <v>0.905</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>31660300</v>
+        <v>33011500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H4" t="n">
-        <v>67.76000000000001</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.822</v>
+        <v>0.821</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -669,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>21206400</v>
+        <v>25874000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>33.68</v>
+        <v>0.34</v>
       </c>
       <c r="H5" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.66</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.041</v>
+        <v>0.301</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.043</v>
+        <v>0.255</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -729,10 +729,10 @@
         <v>-0.0278</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20634400</v>
+        <v>21239100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H6" t="n">
         <v>40.36</v>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>19339400</v>
+        <v>21208400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.25</v>
+        <v>33.68</v>
       </c>
       <c r="H7" t="n">
-        <v>68.66</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.301</v>
+        <v>0.041</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.255</v>
+        <v>0.043</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,28 +804,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.016</v>
+        <v>0.055</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17363100</v>
+        <v>19976200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.17</v>
+        <v>8.57</v>
       </c>
       <c r="H8" t="n">
-        <v>39.06</v>
+        <v>69.25</v>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.557</v>
+        <v>0.045</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>7.7</v>
+        <v>0.047</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,28 +849,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>7.35</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17249800</v>
+        <v>19511700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>77.59999999999999</v>
+        <v>38.72</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.611</v>
+        <v>7.556</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.526</v>
+        <v>7.7</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,28 +894,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.06</v>
+        <v>0.68</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0074</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16747200</v>
+        <v>17772100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>7.18</v>
+        <v>0.71</v>
       </c>
       <c r="H10" t="n">
-        <v>73.95999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.046</v>
+        <v>0.611</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.047</v>
+        <v>0.526</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -954,10 +954,10 @@
         <v>-0.0118</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14988500</v>
+        <v>17131400</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
         <v>74.48999999999999</v>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14543000</v>
+        <v>14686600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.2</v>
+        <v>13.64</v>
       </c>
       <c r="H12" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.44</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.161</v>
+        <v>0.059</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.138</v>
+        <v>0.057</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>14297700</v>
+        <v>14638200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>262.13</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.057</v>
+        <v>0.161</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.062</v>
+        <v>0.138</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,28 +1074,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>13654300</v>
+        <v>14362600</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>12.68</v>
+        <v>263.32</v>
       </c>
       <c r="H14" t="n">
-        <v>68.44</v>
+        <v>57.82</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,33 +1119,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.0196</v>
+        <v>0.45</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11556900</v>
+        <v>13129900</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>40</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.482</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1157,39 +1164,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.455</v>
+        <v>2.02</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.01</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11258400</v>
+        <v>13081200</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="H16" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.39</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.482</v>
+        <v>1.92</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.482</v>
+        <v>1.727</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1202,40 +1209,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10091300</v>
+        <v>11756900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H17" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1247,28 +1247,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.01</v>
+        <v>0.82</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0061</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9668900</v>
+        <v>11248300</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.32</v>
+        <v>0.71</v>
       </c>
       <c r="H18" t="n">
-        <v>58.91</v>
+        <v>57.12</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.919</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.727</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1292,39 +1292,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.115</v>
+        <v>6.74</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.0417</v>
+        <v>-0.06</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8896800</v>
+        <v>11236000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.29</v>
+        <v>1.45</v>
       </c>
       <c r="H19" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.25</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.092</v>
+        <v>7.287</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.092</v>
+        <v>7.643</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         <v>0.0464</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8691500</v>
+        <v>9597100</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
@@ -1375,40 +1375,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0544</v>
+        <v>0.375</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.1194</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8669100</v>
+        <v>9511700</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="H21" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.2</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.291</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>7.644</v>
-      </c>
+        <v>0.315</v>
+      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1420,28 +1418,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.1343</v>
+        <v>0.31</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8611200</v>
+        <v>9317600</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.56</v>
+        <v>0.49</v>
       </c>
       <c r="H22" t="n">
-        <v>67.05</v>
+        <v>54.55</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
@@ -1449,9 +1447,11 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="K22" s="2" t="n"/>
+        <v>0.309</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.299</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1463,28 +1463,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.31</v>
+        <v>0.775</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7921700</v>
+        <v>9156700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="n">
-        <v>54.55</v>
+        <v>50.17</v>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.309</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.299</v>
+        <v>0.776</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1508,39 +1508,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.02</v>
+        <v>0.115</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.0417</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7799200</v>
+        <v>8955200</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>39.69</v>
+        <v>3.31</v>
       </c>
       <c r="H24" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.55</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.023</v>
+        <v>0.092</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.024</v>
+        <v>0.092</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1553,28 +1553,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.385</v>
+        <v>0.455</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0341</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7518800</v>
+        <v>8826600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H25" t="n">
-        <v>63.48</v>
+        <v>60.99</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.371</v>
+        <v>0.423</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1598,28 +1598,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0133</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7367000</v>
+        <v>8299400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.36</v>
+        <v>1.16</v>
       </c>
       <c r="H26" t="n">
-        <v>60.06</v>
+        <v>60.05</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.422</v>
+        <v>0.371</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.364</v>
+        <v>0.369</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1643,39 +1643,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6634100</v>
+        <v>8067200</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.43</v>
+        <v>41.05</v>
       </c>
       <c r="H27" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.23</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.023</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.776</v>
+        <v>0.024</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-0.0167</v>
+        <v>0.3</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6621900</v>
+        <v>8024300</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H28" t="n">
-        <v>50.32</v>
+        <v>53.32</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1733,39 +1733,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.46</v>
+        <v>0.865</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0108</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6116500</v>
+        <v>7621900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="H29" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.513</v>
+        <v>0.868</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.0395</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6100800</v>
+        <v>7158500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="H30" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.868</v>
+        <v>0.389</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.869</v>
+        <v>0.377</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1838,10 +1838,10 @@
         <v>-0.0444</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5655900</v>
+        <v>6884600</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
         <v>42.22</v>
@@ -1868,28 +1868,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.0303</v>
+        <v>4.8</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5543300</v>
+        <v>6870500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="H32" t="n">
-        <v>49.14</v>
+        <v>45.87</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.347</v>
+        <v>4.909</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.333</v>
+        <v>4.721</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1913,28 +1913,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.155</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5244800</v>
+        <v>6325000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="H33" t="n">
-        <v>51.22</v>
+        <v>48.63</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.388</v>
+        <v>0.155</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.377</v>
+        <v>0.157</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1958,28 +1958,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.27</v>
+        <v>0.455</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.0019</v>
+        <v>-0.0215</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4608600</v>
+        <v>6244600</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H34" t="n">
-        <v>38.63</v>
+        <v>27.74</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5.546</v>
+        <v>0.513</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>5.435</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2003,39 +2003,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4.78</v>
+        <v>0.34</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4281900</v>
+        <v>5858900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="H35" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.726</v>
+        <v>0.347</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4.856</v>
+        <v>0.333</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,28 +2048,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>4.79</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4183100</v>
+        <v>5682800</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>4.69</v>
+        <v>0.31</v>
       </c>
       <c r="H36" t="n">
-        <v>54.33</v>
+        <v>54.23</v>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.439</v>
+        <v>4.727</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.439</v>
+        <v>4.856</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2093,39 +2093,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0.0069</v>
+        <v>10.02</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4046900</v>
+        <v>5188700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H37" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.16</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.72</v>
+        <v>10.014</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.958</v>
+        <v>10.16</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2138,39 +2138,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3963700</v>
+        <v>5157000</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0.47</v>
       </c>
       <c r="H38" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.51</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.51</v>
+        <v>0.616</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.526</v>
+        <v>0.614</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2183,39 +2183,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0</v>
+        <v>5.27</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-0.0019</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3885600</v>
+        <v>4932400</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="H39" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.63</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.616</v>
+        <v>5.546</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.614</v>
+        <v>5.435</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,28 +2228,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.555</v>
+        <v>1.46</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.0069</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3737700</v>
+        <v>4896000</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H40" t="n">
-        <v>47.94</v>
+        <v>23.66</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.576</v>
+        <v>1.72</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.538</v>
+        <v>1.958</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3703000</v>
+        <v>4610600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.19</v>
+        <v>0.22</v>
       </c>
       <c r="H41" t="n">
-        <v>49.15</v>
+        <v>48.82</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.295</v>
+        <v>0.576</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.295</v>
+        <v>0.539</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,28 +2318,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.185</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3560500</v>
+        <v>4346000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.27</v>
+        <v>0.8</v>
       </c>
       <c r="H42" t="n">
-        <v>46.97</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.013</v>
+        <v>0.165</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>10.16</v>
+        <v>0.166</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.165</v>
+        <v>0.44</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3411500</v>
+        <v>4183100</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.48</v>
+        <v>4.69</v>
       </c>
       <c r="H43" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.33</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.179</v>
+        <v>0.439</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.197</v>
+        <v>0.439</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,39 +2408,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0.0526</v>
+        <v>0.48</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3404200</v>
+        <v>4166600</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H44" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="H44" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0.11</v>
-      </c>
       <c r="K44" s="2" t="n">
-        <v>0.121</v>
+        <v>0.526</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2453,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.07139999999999999</v>
+        <v>0.625</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3295900</v>
+        <v>4056100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.36</v>
+        <v>1.29</v>
       </c>
       <c r="H45" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.126</v>
+        <v>0.616</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.1</v>
+        <v>0.604</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.66</v>
+        <v>0.13</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3197400</v>
+        <v>3714400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="H46" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.1</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.623</v>
+        <v>0.126</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.699</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,39 +2543,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0.0286</v>
+        <v>0.295</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3175900</v>
+        <v>3703000</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.59</v>
+        <v>1.19</v>
       </c>
       <c r="H47" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.164</v>
+        <v>0.295</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.165</v>
+        <v>0.295</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0.1066</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3157700</v>
+        <v>3647800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.34</v>
+        <v>2.53</v>
       </c>
       <c r="H48" t="n">
-        <v>45.07</v>
+        <v>50.05</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.306</v>
+        <v>1.089</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.314</v>
+        <v>1.096</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,28 +2633,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>0.1066</v>
+        <v>0.745</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3116800</v>
+        <v>3496800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.16</v>
+        <v>0.42</v>
       </c>
       <c r="H49" t="n">
-        <v>50.05</v>
+        <v>41.25</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.089</v>
+        <v>0.773</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.096</v>
+        <v>0.772</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.89</v>
+        <v>0.105</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>0.0471</v>
+        <v>0.1053</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3106900</v>
+        <v>3480200</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="H50" t="n">
-        <v>45.75</v>
+        <v>42.3</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.844</v>
+        <v>0.121</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,39 +2723,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.42</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3089400</v>
+        <v>3468700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.16</v>
+        <v>0.43</v>
       </c>
       <c r="H51" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.54</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.649</v>
+        <v>0.538</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.55</v>
+        <v>0.619</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,39 +2768,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2921700</v>
+        <v>3450500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="H52" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.56</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.773</v>
+        <v>2.649</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.772</v>
+        <v>2.55</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,28 +2813,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2920700</v>
+        <v>3432300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H53" t="n">
-        <v>22.54</v>
+        <v>39.69</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.538</v>
+        <v>0.179</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.619</v>
+        <v>0.197</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,28 +2858,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3.84</v>
+        <v>0.885</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0323</v>
+        <v>0.0412</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2828000</v>
+        <v>3391100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="H54" t="n">
-        <v>58.58</v>
+        <v>45.01</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.644</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.964</v>
+        <v>0.843</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,28 +2903,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.81</v>
+        <v>1.74</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0114</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2782200</v>
+        <v>3345700</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.11</v>
+        <v>1.03</v>
       </c>
       <c r="H55" t="n">
-        <v>46.36</v>
+        <v>28.83</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.91</v>
+        <v>1.833</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.721</v>
+        <v>1.972</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,28 +2948,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0</v>
+        <v>1.66</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2736400</v>
+        <v>3315200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="H56" t="n">
-        <v>74.05</v>
+        <v>53.01</v>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.825</v>
+        <v>1.623</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.699</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.017</v>
+        <v>1.28</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2715500</v>
+        <v>3283800</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.84</v>
+        <v>0.35</v>
       </c>
       <c r="H57" t="n">
-        <v>27.95</v>
+        <v>45.07</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.832</v>
+        <v>1.306</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.971</v>
+        <v>1.314</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,39 +3038,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.7</v>
+        <v>3.79</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0188</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2492900</v>
+        <v>3221200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.99</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.5</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.646</v>
+        <v>3.639</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.552</v>
+        <v>2.963</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2485200</v>
+        <v>3043300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H59" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.44</v>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.048</v>
+        <v>1.19</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.904</v>
+        <v>1.184</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,28 +3128,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0306</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2398700</v>
+        <v>2972600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H60" t="n">
-        <v>55.47</v>
+        <v>46.04</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.078</v>
+        <v>1.055</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.044</v>
+        <v>0.953</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3173,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.39</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2378000</v>
+        <v>2867300</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H61" t="n">
-        <v>46.04</v>
+        <v>33.84</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.055</v>
+        <v>0.397</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.953</v>
+        <v>0.407</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.0357</v>
+        <v>2.71</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2365500</v>
+        <v>2845000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="H62" t="n">
-        <v>25.38</v>
+        <v>44.87</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.339</v>
+        <v>2.778</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.374</v>
+        <v>2.735</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,39 +3263,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2317300</v>
+        <v>2813900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="H63" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.397</v>
+        <v>0.826</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.407</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0053</v>
+        <v>-0.0345</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2289400</v>
+        <v>2614000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H64" t="n">
-        <v>59.85</v>
+        <v>17.96</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3337,11 +3337,9 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>0.874</v>
-      </c>
+        <v>0.464</v>
+      </c>
+      <c r="K64" s="2" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3353,39 +3351,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.625</v>
+        <v>1.11</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0673</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2270000</v>
+        <v>2592900</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H65" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.81</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.616</v>
+        <v>1.049</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.604</v>
+        <v>0.905</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,28 +3396,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>0.0588</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2264300</v>
+        <v>2567800</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H66" t="n">
-        <v>62.52</v>
+        <v>66.02</v>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
@@ -3427,10 +3425,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.497</v>
+        <v>0.646</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.464</v>
+        <v>0.552</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,28 +3441,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.84</v>
+        <v>2.05</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>0.0435</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2236400</v>
+        <v>2565500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.59</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>54.6</v>
+        <v>36.49</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3472,10 +3470,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.825</v>
+        <v>2.163</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.777</v>
+        <v>2.232</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,39 +3486,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.05</v>
+        <v>0.55</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2152200</v>
+        <v>2544200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="H68" t="n">
-        <v>36.49</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.09</v>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.163</v>
+        <v>0.498</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.232</v>
+        <v>0.464</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,28 +3531,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1.2</v>
+        <v>0.295</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0536</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2017300</v>
+        <v>2452400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H69" t="n">
-        <v>54.56</v>
+        <v>28.25</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3562,10 +3560,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.171</v>
+        <v>0.339</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.133</v>
+        <v>0.374</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,28 +3576,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0.84</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1994700</v>
+        <v>2425400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H70" t="n">
-        <v>44.04</v>
+        <v>54.6</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3607,10 +3605,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.046</v>
+        <v>0.825</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.073</v>
+        <v>0.777</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,28 +3621,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>0.0191</v>
+        <v>0.0183</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1966800</v>
+        <v>2423600</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H71" t="n">
-        <v>58.44</v>
+        <v>55.47</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3652,10 +3650,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.791</v>
+        <v>1.078</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.77</v>
+        <v>1.044</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3668,28 +3666,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.046</v>
+        <v>1.2</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1932500</v>
+        <v>2342700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H72" t="n">
-        <v>16.79</v>
+        <v>54.56</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3697,9 +3695,11 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="K72" s="2" t="n"/>
+        <v>1.171</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1.133</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3711,39 +3711,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0037</v>
+        <v>1.07</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1912300</v>
+        <v>2293400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.15</v>
+        <v>4.17</v>
       </c>
       <c r="H73" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.03</v>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.777</v>
+        <v>1.106</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.734</v>
+        <v>1.127</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3756,28 +3756,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1845400</v>
+        <v>2289400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="H74" t="n">
-        <v>53.37</v>
+        <v>59.85</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>3.856</v>
+        <v>0.918</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3.665</v>
+        <v>0.874</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3801,28 +3801,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.525</v>
+        <v>0.8</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0191</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1770000</v>
+        <v>2260600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="H75" t="n">
-        <v>53.48</v>
+        <v>58.44</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.52</v>
+        <v>0.791</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.457</v>
+        <v>0.77</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         <v>-0.007800000000000001</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1750500</v>
+        <v>2248700</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H76" t="n">
         <v>44.1</v>
@@ -3891,39 +3891,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>-0.0168</v>
+        <v>7.31</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1736400</v>
+        <v>2201600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.96</v>
+        <v>0.21</v>
       </c>
       <c r="H77" t="n">
-        <v>57.44</v>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.62</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4.591</v>
+        <v>7.48</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4.493</v>
+        <v>7.977</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3936,39 +3936,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1662600</v>
+        <v>2151600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>3.02</v>
+        <v>0.29</v>
       </c>
       <c r="H78" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.67</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.106</v>
+        <v>1.236</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.127</v>
+        <v>1.329</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3981,28 +3981,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
+        <v>6.76</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1644400</v>
+        <v>2087300</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.08</v>
+        <v>0.48</v>
       </c>
       <c r="H79" t="n">
-        <v>33.7</v>
+        <v>50.09</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.237</v>
+        <v>6.756</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.289</v>
+        <v>6.83</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4026,39 +4026,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.395</v>
+        <v>3.84</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.0492</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1609000</v>
+        <v>2085600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H80" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.3</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.388</v>
+        <v>3.851</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.391</v>
+        <v>3.664</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4071,28 +4071,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.675</v>
+        <v>0.525</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1575200</v>
+        <v>2073700</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.49</v>
+        <v>0.15</v>
       </c>
       <c r="H81" t="n">
-        <v>37.6</v>
+        <v>53.48</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.731</v>
+        <v>0.52</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.745</v>
+        <v>0.457</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4116,28 +4116,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>0.008500000000000001</v>
+        <v>2.02</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1545800</v>
+        <v>2057100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.17</v>
+        <v>0.64</v>
       </c>
       <c r="H82" t="n">
-        <v>39.79</v>
+        <v>44.04</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.656</v>
+        <v>2.046</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.619</v>
+        <v>2.073</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4161,28 +4161,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>0.04</v>
+        <v>0.845</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1524700</v>
+        <v>2041300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="H83" t="n">
-        <v>57.1</v>
+        <v>17.19</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.252</v>
+        <v>0.923</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.17</v>
+        <v>0.976</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4206,39 +4206,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0169</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1489600</v>
+        <v>2008800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H84" t="n">
-        <v>59.55</v>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.82</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.187</v>
+        <v>0.656</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.183</v>
+        <v>0.619</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4251,28 +4251,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0</v>
+        <v>3.84</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1464800</v>
+        <v>1948400</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1.37</v>
+        <v>0.2</v>
       </c>
       <c r="H85" t="n">
-        <v>49.68</v>
+        <v>48.74</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.38</v>
+        <v>3.953</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.378</v>
+        <v>3.537</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4296,28 +4296,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3.86</v>
+        <v>2.82</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.0321</v>
+        <v>0.0444</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1458400</v>
+        <v>1895400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H86" t="n">
-        <v>49.39</v>
+        <v>53.62</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.955</v>
+        <v>2.792</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3.537</v>
+        <v>2.656</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4341,28 +4341,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E87" s="9" t="n">
-        <v>0.0221</v>
+        <v>1.91</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1451800</v>
+        <v>1793100</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H87" t="n">
-        <v>58.82</v>
+        <v>45.97</v>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.216</v>
+        <v>1.926</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.158</v>
+        <v>1.952</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4386,28 +4386,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2.82</v>
+        <v>0.225</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.0444</v>
+        <v>0.0227</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1443700</v>
+        <v>1769600</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H88" t="n">
-        <v>53.62</v>
+        <v>37.16</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.792</v>
+        <v>0.237</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2.656</v>
+        <v>0.289</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4431,39 +4431,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E89" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>4.66</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1434500</v>
+        <v>1753000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.23</v>
+        <v>0.97</v>
       </c>
       <c r="H89" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.65</v>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.616</v>
+        <v>4.59</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.605</v>
+        <v>4.492</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,39 +4476,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7.31</v>
+        <v>2.3</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0177</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1422100</v>
+        <v>1704900</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="H90" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.17</v>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>7.48</v>
+        <v>2.215</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>7.977</v>
+        <v>2.158</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4521,28 +4521,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1405900</v>
+        <v>1676000</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.64</v>
+        <v>1.56</v>
       </c>
       <c r="H91" t="n">
-        <v>47.9</v>
+        <v>56.29</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.637</v>
+        <v>0.381</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.621</v>
+        <v>0.378</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4566,28 +4566,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E92" s="9" t="n">
-        <v>0.038</v>
+        <v>0.255</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1380700</v>
+        <v>1619500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H92" t="n">
-        <v>47.49</v>
+        <v>24.06</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.423</v>
+        <v>0.278</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.415</v>
+        <v>0.302</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4611,28 +4611,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>-0.0205</v>
+        <v>0.395</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1371100</v>
+        <v>1609100</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="H93" t="n">
-        <v>45.97</v>
+        <v>52.86</v>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.926</v>
+        <v>0.388</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.952</v>
+        <v>0.391</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4656,39 +4656,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>3.1</v>
+        <v>0.675</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.0098</v>
+        <v>0.0227</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1365500</v>
+        <v>1597800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H94" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.6</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.801</v>
+        <v>0.731</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.406</v>
+        <v>0.745</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4701,28 +4701,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>1.36</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1361900</v>
+        <v>1577800</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H95" t="n">
-        <v>15.31</v>
+        <v>47.38</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.952</v>
+        <v>1.37</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.085</v>
+        <v>1.343</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4746,28 +4746,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0244</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1360200</v>
+        <v>1573200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.15</v>
+        <v>1.02</v>
       </c>
       <c r="H96" t="n">
-        <v>30.1</v>
+        <v>40.04</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.278</v>
+        <v>0.223</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.302</v>
+        <v>0.232</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4791,28 +4791,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.76</v>
+        <v>1.3</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1349100</v>
+        <v>1569700</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.31</v>
+        <v>0.67</v>
       </c>
       <c r="H97" t="n">
-        <v>50.09</v>
+        <v>57.1</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>6.756</v>
+        <v>1.252</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>6.83</v>
+        <v>1.17</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4836,39 +4836,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.47</v>
+        <v>0.35</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0141</v>
+        <v>0.0145</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1309400</v>
+        <v>1566200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H98" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.49</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>6.135</v>
+        <v>0.354</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5.893</v>
+        <v>0.326</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.0058</v>
+        <v>6.44</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1303100</v>
+        <v>1549400</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="H99" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.32</v>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.924</v>
+        <v>6.132</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.976</v>
+        <v>5.893</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4926,28 +4926,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E100" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.785</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0309</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1275900</v>
+        <v>1532200</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="H100" t="n">
-        <v>51.9</v>
+        <v>15.56</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.864</v>
+        <v>0.953</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.86</v>
+        <v>1.085</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4971,28 +4971,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.645</v>
+        <v>2.57</v>
       </c>
       <c r="E101" s="9" t="n">
         <v>0.007800000000000001</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1255100</v>
+        <v>1520500</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H101" t="n">
-        <v>42.6</v>
+        <v>46.75</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.616</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>2.605</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5016,28 +5016,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E102" s="9" t="n">
-        <v>0.0259</v>
+        <v>5.85</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1253300</v>
+        <v>1490100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="H102" t="n">
-        <v>50.14</v>
+        <v>32.16</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.599</v>
+        <v>6.068</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.585</v>
+        <v>6.333</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5061,28 +5061,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>2.89</v>
+        <v>0.77</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>0.0433</v>
+        <v>0.0476</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1177600</v>
+        <v>1457900</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="H103" t="n">
-        <v>59.13</v>
+        <v>57.27</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.775</v>
+        <v>0.732</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.185</v>
+        <v>0.703</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5106,39 +5106,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.0385</v>
+        <v>0.41</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>0.038</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1152600</v>
+        <v>1411300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1.47</v>
+        <v>0.2</v>
       </c>
       <c r="H104" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.22</v>
+        <v>0.423</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.209</v>
+        <v>0.415</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5151,28 +5151,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E105" s="9" t="n">
-        <v>0.0168</v>
+        <v>0.63</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1123100</v>
+        <v>1406900</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H105" t="n">
-        <v>40.44</v>
+        <v>47.9</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.238</v>
+        <v>0.637</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.329</v>
+        <v>0.621</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5196,39 +5196,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.265</v>
+        <v>5.56</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.0296</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1094200</v>
+        <v>1405500</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H106" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.45</v>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.275</v>
+        <v>5.51</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.296</v>
+        <v>5.397</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5241,28 +5241,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.09</v>
+        <v>0.65</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0156</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1091700</v>
+        <v>1403300</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H107" t="n">
-        <v>52.3</v>
+        <v>43.65</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>5.068</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>5.062</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5286,28 +5286,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.56</v>
+        <v>3.1</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.0098</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1086200</v>
+        <v>1376700</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H108" t="n">
-        <v>52.45</v>
+        <v>82.37</v>
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>5.51</v>
+        <v>2.801</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>5.397</v>
+        <v>2.406</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5331,28 +5331,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1077100</v>
+        <v>1333100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="H109" t="n">
-        <v>48.33</v>
+        <v>49.06</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.354</v>
+        <v>0.598</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.326</v>
+        <v>0.585</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5376,39 +5376,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E110" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.25</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1058100</v>
+        <v>1289800</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.66</v>
+        <v>1.65</v>
       </c>
       <c r="H110" t="n">
-        <v>52</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.916</v>
+        <v>0.22</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.87</v>
+        <v>0.209</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5421,28 +5421,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>0.036</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1040600</v>
+        <v>1286000</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H111" t="n">
-        <v>57.09</v>
+        <v>52.91</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.112</v>
+        <v>5.069</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.879</v>
+        <v>5.062</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5466,28 +5466,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>-0.0135</v>
+        <v>0.865</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1027000</v>
+        <v>1275900</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="H112" t="n">
-        <v>32.57</v>
+        <v>51.9</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>6.069</v>
+        <v>0.864</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>6.333</v>
+        <v>0.86</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5511,28 +5511,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>0</v>
+        <v>2.89</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0.0433</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1026200</v>
+        <v>1273000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.92</v>
+        <v>0.25</v>
       </c>
       <c r="H113" t="n">
-        <v>41.54</v>
+        <v>59.13</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.272</v>
+        <v>2.775</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.276</v>
+        <v>2.185</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5556,28 +5556,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0.0476</v>
+        <v>1.27</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1023600</v>
+        <v>1257300</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.74</v>
+        <v>0.3</v>
       </c>
       <c r="H114" t="n">
-        <v>77.73999999999999</v>
+        <v>26.62</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.269</v>
+        <v>1.411</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.217</v>
+        <v>1.57</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5601,39 +5601,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E115" s="9" t="n">
-        <v>0.0053</v>
+        <v>0.335</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1021900</v>
+        <v>1252200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H115" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.975</v>
+        <v>0.336</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.056</v>
+        <v>0.343</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5646,39 +5646,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E116" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.71</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1018500</v>
+        <v>1240700</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="H116" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.57</v>
+        <v>0.732</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.613</v>
+        <v>0.728</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5691,39 +5691,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1010600</v>
+        <v>1199100</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.43</v>
+        <v>0.15</v>
       </c>
       <c r="H117" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.09</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.002</v>
+        <v>1.112</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.983</v>
+        <v>0.879</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5736,28 +5736,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0069</v>
+        <v>2.8</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>975300</v>
+        <v>1176000</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.68</v>
+        <v>0.32</v>
       </c>
       <c r="H118" t="n">
-        <v>44.39</v>
+        <v>41.54</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.732</v>
+        <v>2.909</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.728</v>
+        <v>3.018</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5781,28 +5781,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.78</v>
+        <v>0.265</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0392</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>968700</v>
+        <v>1164500</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H119" t="n">
-        <v>40.07</v>
+        <v>44.4</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>2.907</v>
+        <v>0.275</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.018</v>
+        <v>0.296</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5826,28 +5826,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>965700</v>
+        <v>1072000</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H120" t="n">
-        <v>27.28</v>
+        <v>44.67</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.412</v>
+        <v>0.247</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1.571</v>
+        <v>0.255</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5871,28 +5871,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E121" s="9" t="n">
-        <v>0.02</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.0352</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>929600</v>
+        <v>1071200</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>53.42</v>
+        <v>40.08</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.764</v>
+        <v>0.757</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5916,39 +5916,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E122" s="9" t="n">
-        <v>0.0408</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>904700</v>
+        <v>1069600</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="H122" t="n">
-        <v>56.66</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.27</v>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.732</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.703</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5961,39 +5961,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.625</v>
+        <v>0.915</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>0.0684</v>
+        <v>0.0167</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>880400</v>
+        <v>1068000</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>11.58</v>
+        <v>0.67</v>
       </c>
       <c r="H123" t="n">
-        <v>75.84</v>
-      </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.31</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.546</v>
+        <v>0.915</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.542</v>
+        <v>0.869</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6006,28 +6006,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>853100</v>
+        <v>1067200</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H124" t="n">
-        <v>49.95</v>
+        <v>30.55</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.284</v>
+        <v>0.975</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.22</v>
+        <v>1.056</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6051,39 +6051,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E125" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>2.1</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>834300</v>
+        <v>1064900</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="H125" t="n">
-        <v>36.85</v>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.93</v>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.911</v>
+        <v>2.11</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.929</v>
+        <v>2.099</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6096,28 +6096,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0282</v>
+        <v>0.33</v>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>803000</v>
+        <v>1056700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.05</v>
+        <v>0.76</v>
       </c>
       <c r="H126" t="n">
-        <v>40.66</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.757</v>
+        <v>0.269</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.723</v>
+        <v>0.217</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6141,39 +6141,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.15</v>
+        <v>0.46</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>782800</v>
+        <v>1038900</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="H127" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.42</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.109</v>
+        <v>0.502</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.059</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6186,28 +6186,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E128" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.27</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>770700</v>
+        <v>1026200</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
       <c r="H128" t="n">
-        <v>56.23</v>
+        <v>41.54</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.272</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.513</v>
+        <v>0.276</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6231,28 +6231,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1.3</v>
+        <v>0.765</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>770300</v>
+        <v>1025600</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="H129" t="n">
-        <v>47.66</v>
+        <v>53.42</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.331</v>
+        <v>0.764</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>1.279</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6276,28 +6276,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>754000</v>
+        <v>1018500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.08</v>
+        <v>0.89</v>
       </c>
       <c r="H130" t="n">
-        <v>44.06</v>
+        <v>41.94</v>
       </c>
       <c r="I130" s="10" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>13.017</v>
+        <v>0.57</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>13.443</v>
+        <v>0.613</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6321,28 +6321,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>0.028</v>
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>733600</v>
+        <v>1012600</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="H131" t="n">
-        <v>51.61</v>
+        <v>43.17</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.741</v>
+        <v>8.661</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.673</v>
+        <v>8.702999999999999</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6366,39 +6366,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.12</v>
+        <v>1.02</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>0.0242</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>733300</v>
+        <v>1010600</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.29</v>
+        <v>1.43</v>
       </c>
       <c r="H132" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2.114</v>
+        <v>1.002</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1.988</v>
+        <v>0.983</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,39 +6411,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.76</v>
+        <v>0.885</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>720200</v>
+        <v>967700</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>11.81</v>
+        <v>0.59</v>
       </c>
       <c r="H133" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.85</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.736</v>
+        <v>0.911</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.741</v>
+        <v>0.929</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6456,39 +6456,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.79</v>
+        <v>2.15</v>
       </c>
       <c r="E134" s="9" t="n">
-        <v>0.0327</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>710700</v>
+        <v>919700</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="H134" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.777</v>
+        <v>2.109</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.768</v>
+        <v>2.059</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6501,39 +6501,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>10.56</v>
+        <v>0.615</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0513</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>693300</v>
+        <v>910400</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.19</v>
+        <v>11.97</v>
       </c>
       <c r="H135" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.33</v>
+      </c>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>10.404</v>
+        <v>0.545</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>9.728999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6546,39 +6546,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E136" s="8" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>0.04099999999999999</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>688900</v>
+        <v>895500</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="H136" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.95</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.37</v>
+        <v>1.284</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.343</v>
+        <v>1.22</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,28 +6591,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E137" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.825</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>675400</v>
+        <v>884600</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.16</v>
+        <v>0.59</v>
       </c>
       <c r="H137" t="n">
-        <v>52.42</v>
+        <v>36.21</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>7.361</v>
+        <v>0.848</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>6.882</v>
+        <v>0.862</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,28 +6636,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.7</v>
+        <v>0.57</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.0672</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>660500</v>
+        <v>861600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="H138" t="n">
-        <v>55.45</v>
+        <v>55.17</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.661</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>2.24</v>
+        <v>0.513</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,28 +6681,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.68</v>
+        <v>0.74</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>0.006</v>
+        <v>0.035</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>658300</v>
+        <v>849200</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H139" t="n">
-        <v>41.09</v>
+        <v>52.39</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.734</v>
+        <v>0.741</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1.769</v>
+        <v>0.673</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6726,39 +6726,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>-0.006</v>
+        <v>12.98</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>651400</v>
+        <v>825400</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="H140" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.06</v>
+      </c>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.848</v>
+        <v>13.017</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.862</v>
+        <v>13.443</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,28 +6771,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.51</v>
+        <v>0.79</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0327</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>639800</v>
+        <v>821500</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="H141" t="n">
-        <v>46.48</v>
+        <v>53.5</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.524</v>
+        <v>0.777</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.506</v>
+        <v>0.768</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,28 +6816,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.1</v>
+        <v>7.37</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>636600</v>
+        <v>813200</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.88</v>
+        <v>0.19</v>
       </c>
       <c r="H142" t="n">
-        <v>40.72</v>
+        <v>52.81</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.209</v>
+        <v>7.363</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.233</v>
+        <v>6.883</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,28 +6861,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.01</v>
+        <v>2.13</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>0.0202</v>
+        <v>0.029</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>627600</v>
+        <v>812600</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H143" t="n">
-        <v>47.79</v>
+        <v>52.91</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.047</v>
+        <v>2.115</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.989</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,39 +6906,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>-0.0186</v>
+        <v>2.62</v>
+      </c>
+      <c r="E144" s="9" t="n">
+        <v>0.0356</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>624100</v>
+        <v>803000</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H144" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="I144" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.41</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.726</v>
+        <v>2.846</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.644</v>
+        <v>2.874</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6951,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>0.0036</v>
+        <v>0.0593</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>619800</v>
+        <v>775300</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.6</v>
+        <v>0.22</v>
       </c>
       <c r="H145" t="n">
-        <v>40.97</v>
+        <v>54.69</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.86</v>
+        <v>2.659</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.859</v>
+        <v>2.24</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,39 +6996,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.009399999999999999</v>
+        <v>1.3</v>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>0.04</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>613500</v>
+        <v>770300</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="H146" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I146" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>2.11</v>
+        <v>1.331</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>2.099</v>
+        <v>1.279</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,28 +7041,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E147" s="8" t="n">
-        <v>0</v>
+        <v>10.58</v>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>604400</v>
+        <v>740600</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H147" t="n">
-        <v>63.4</v>
+        <v>56.81</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.569</v>
+        <v>10.406</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.467</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,28 +7086,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E148" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>3.17</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>-0.0216</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>591900</v>
+        <v>739000</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H148" t="n">
-        <v>45.79</v>
+        <v>26.45</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>4.299</v>
+        <v>3.383</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>4.334</v>
+        <v>3.614</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,39 +7131,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PWF</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.61</v>
+        <v>0.76</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>0.0316</v>
+        <v>0.0133</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>583500</v>
+        <v>720200</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.11</v>
+        <v>11.81</v>
       </c>
       <c r="H149" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2.846</v>
+        <v>0.736</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2.874</v>
+        <v>0.741</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3.17</v>
+        <v>0.62</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>-0.0216</v>
+        <v>-0.0159</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>569300</v>
+        <v>719900</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H150" t="n">
-        <v>26.45</v>
+        <v>61.66</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>3.383</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.614</v>
+        <v>0.466</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,28 +7221,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>3.01</v>
+        <v>4.18</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0048</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>554600</v>
+        <v>690000</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H151" t="n">
-        <v>51.57</v>
+        <v>45.03</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>3.023</v>
+        <v>4.297</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>2.851</v>
+        <v>4.333</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7266,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.67</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>550600</v>
+        <v>668900</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="H152" t="n">
-        <v>35.15</v>
+        <v>39.49</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.631</v>
+        <v>1.734</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0.631</v>
+        <v>1.769</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,28 +7311,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>-0.0069</v>
+        <v>1.71</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>524300</v>
+        <v>662500</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H153" t="n">
-        <v>41.89</v>
+        <v>35.52</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.465</v>
+        <v>1.895</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,28 +7356,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.0288</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>514300</v>
+        <v>657800</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="H154" t="n">
-        <v>35.26</v>
+        <v>40.72</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.212</v>
+        <v>2.209</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1.297</v>
+        <v>2.233</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,28 +7401,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>-0.019</v>
+        <v>0.51</v>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>505500</v>
+        <v>654300</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.12</v>
+        <v>0.58</v>
       </c>
       <c r="H155" t="n">
-        <v>31.96</v>
+        <v>46.48</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.589</v>
+        <v>0.524</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.601</v>
+        <v>0.506</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,28 +7446,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E156" s="8" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>502100</v>
+        <v>654100</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="H156" t="n">
-        <v>54.38</v>
+        <v>76.38</v>
       </c>
       <c r="I156" s="10" t="inlineStr">
         <is>
@@ -7475,16 +7475,646 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.258</v>
+        <v>0.727</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.279</v>
+        <v>0.645</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>646100</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H157" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>643600</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H158" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>623400</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H159" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>615400</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H160" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>590600</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H161" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E162" s="9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>585200</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H162" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>2.851</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>565300</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H163" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>558200</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H164" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>538600</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H165" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E166" s="9" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>516300</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H166" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>2.448</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>2.379</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E167" s="9" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>514300</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H167" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E168" s="9" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>510000</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H168" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>506800</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H169" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>501200</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H170" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M156"/>
+  <autoFilter ref="A1:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.1538</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>195863200</v>
+        <v>204083800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
-        <v>23.14</v>
+        <v>23.66</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>62286700</v>
+        <v>62797800</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -624,28 +624,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.905</v>
+        <v>0.345</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0455</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>33011500</v>
+        <v>37346600</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.49</v>
       </c>
       <c r="H4" t="n">
-        <v>66.79000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.821</v>
+        <v>0.302</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.731</v>
+        <v>0.255</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -669,28 +669,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.91</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.0111</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>25874000</v>
+        <v>37124700</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
       <c r="H5" t="n">
-        <v>68.66</v>
+        <v>67.28</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.301</v>
+        <v>0.822</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.255</v>
+        <v>0.732</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.175</v>
+        <v>7.31</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0278</v>
+        <v>-0.0227</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21239100</v>
+        <v>22705300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.91</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
-        <v>40.36</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.41</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.19</v>
+        <v>7.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.185</v>
+        <v>7.699</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>21208400</v>
+        <v>22633800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>33.68</v>
+        <v>0.64</v>
       </c>
       <c r="H7" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.84999999999999</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.041</v>
+        <v>0.378</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.043</v>
+        <v>0.27</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>19976200</v>
+        <v>21324200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>8.57</v>
+        <v>0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.36</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.045</v>
+        <v>0.19</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.047</v>
+        <v>0.185</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,28 +849,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.0174</v>
+        <v>0.045</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.125</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>19511700</v>
+        <v>21258500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.32</v>
+        <v>33.76</v>
       </c>
       <c r="H9" t="n">
-        <v>38.72</v>
+        <v>57.71</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.556</v>
+        <v>0.041</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>7.7</v>
+        <v>0.043</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,28 +894,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0.0074</v>
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17772100</v>
+        <v>19996200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.71</v>
+        <v>8.58</v>
       </c>
       <c r="H10" t="n">
-        <v>78.29000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.611</v>
+        <v>0.045</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.526</v>
+        <v>0.047</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -939,28 +939,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-0.0118</v>
+        <v>0.675</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>17131400</v>
+        <v>17997800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="H11" t="n">
-        <v>74.48999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.378</v>
+        <v>0.611</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.27</v>
+        <v>0.526</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>14686600</v>
+        <v>17060200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>13.64</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.059</v>
+        <v>0.155</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.057</v>
+        <v>0.157</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.025</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>14638200</v>
+        <v>15535300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="H13" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.74</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.161</v>
+        <v>1.923</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.138</v>
+        <v>1.728</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.06</v>
+        <v>0.455</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14362600</v>
+        <v>15413700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>263.32</v>
+        <v>0.42</v>
       </c>
       <c r="H14" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.76</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.057</v>
+        <v>0.482</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.062</v>
+        <v>0.482</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,28 +1119,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0112</v>
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>13129900</v>
+        <v>15009200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="H15" t="n">
-        <v>40</v>
+        <v>46.24</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.482</v>
+        <v>0.161</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.482</v>
+        <v>0.138</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,28 +1164,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2.02</v>
+        <v>0.075</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.01</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>13081200</v>
+        <v>14815200</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.43</v>
+        <v>13.76</v>
       </c>
       <c r="H16" t="n">
-        <v>59.39</v>
+        <v>68.44</v>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.92</v>
+        <v>0.059</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.727</v>
+        <v>0.057</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,33 +1209,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.25</v>
+        <v>6.62</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0196</v>
+        <v>-0.0767</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>11756900</v>
+        <v>14689300</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.45</v>
+        <v>1.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>21.23</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="J17" s="2" t="n">
+        <v>7.276</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>7.641</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1247,28 +1254,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>11248300</v>
+        <v>14362600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.71</v>
+        <v>263.32</v>
       </c>
       <c r="H18" t="n">
-        <v>57.12</v>
+        <v>57.82</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -1276,10 +1283,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1292,39 +1299,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.82</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11236000</v>
+        <v>12720500</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.45</v>
+        <v>0.8</v>
       </c>
       <c r="H19" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.12</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.287</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>7.643</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1337,33 +1344,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.0464</v>
+        <v>0.31</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9597100</v>
+        <v>12650700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.09</v>
+        <v>0.67</v>
+      </c>
+      <c r="H20" t="n">
+        <v>54.55</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
+      <c r="J20" s="2" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.299</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
     </row>
@@ -1375,37 +1389,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.1194</v>
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9511700</v>
+        <v>12137600</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H21" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0.315</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1418,28 +1427,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.31</v>
+        <v>0.775</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9317600</v>
+        <v>11844800</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="H22" t="n">
-        <v>54.55</v>
+        <v>50.17</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
@@ -1447,10 +1456,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.309</v>
+        <v>0.775</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.299</v>
+        <v>0.776</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1463,40 +1472,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0.0464</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>9156700</v>
+        <v>10430200</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50.17</v>
+        <v>0.1</v>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0.776</v>
-      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1508,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0417</v>
+        <v>0.37</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.1045</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8955200</v>
+        <v>10415700</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3.31</v>
+        <v>1.89</v>
       </c>
       <c r="H24" t="n">
-        <v>69.55</v>
+        <v>65.31</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1539,9 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>0.092</v>
-      </c>
+        <v>0.315</v>
+      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1553,39 +1553,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.455</v>
+        <v>0.31</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.0341</v>
+        <v>0.0333</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8826600</v>
+        <v>10346200</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.43</v>
+        <v>1.27</v>
       </c>
       <c r="H25" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.28</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.423</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.364</v>
+        <v>0.28</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1598,28 +1598,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.38</v>
+        <v>0.455</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.0341</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8299400</v>
+        <v>10286900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>60.05</v>
+        <v>60.99</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.371</v>
+        <v>0.423</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1643,39 +1643,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.02</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8067200</v>
+        <v>9425500</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>41.05</v>
+        <v>0.48</v>
       </c>
       <c r="H27" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.023</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.024</v>
+        <v>0.869</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1688,28 +1688,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0658</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8024300</v>
+        <v>9409600</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.98</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
-        <v>53.32</v>
+        <v>55.08</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.299</v>
+        <v>0.39</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.28</v>
+        <v>0.378</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1733,28 +1733,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.375</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7621900</v>
+        <v>9107700</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.38</v>
+        <v>1.27</v>
       </c>
       <c r="H29" t="n">
-        <v>45.57</v>
+        <v>55.91</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.868</v>
+        <v>0.371</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.869</v>
+        <v>0.369</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0.0395</v>
+        <v>0.115</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7158500</v>
+        <v>8967200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.57</v>
+        <v>3.31</v>
       </c>
       <c r="H30" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.55</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.389</v>
+        <v>0.092</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.377</v>
+        <v>0.092</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.215</v>
+        <v>0.02</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.2</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6884600</v>
+        <v>8363600</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.33</v>
+        <v>42.56</v>
       </c>
       <c r="H31" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.23</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.223</v>
+        <v>0.023</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.239</v>
+        <v>0.024</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-0.0103</v>
+        <v>-0.0062</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6870500</v>
+        <v>8231500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
-        <v>45.87</v>
+        <v>46.86</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.909</v>
+        <v>4.911</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>4.721</v>
@@ -1913,39 +1913,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6325000</v>
+        <v>7770100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="H33" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.22</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.155</v>
+        <v>0.223</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.157</v>
+        <v>0.239</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.0215</v>
+        <v>4.79</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6244600</v>
+        <v>7066600</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="H34" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.23</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.513</v>
+        <v>4.727</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>4.856</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2003,28 +2003,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.34</v>
+        <v>1.11</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.1269</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5858900</v>
+        <v>6435100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.62</v>
+        <v>4.47</v>
       </c>
       <c r="H35" t="n">
-        <v>49.14</v>
+        <v>52.19</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.347</v>
+        <v>1.091</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.333</v>
+        <v>1.097</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,39 +2048,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.455</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5682800</v>
+        <v>6256200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H36" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.74</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4.727</v>
+        <v>0.513</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4.856</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5188700</v>
+        <v>5943000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="n">
-        <v>48.16</v>
+        <v>46.97</v>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.014</v>
+        <v>10.013</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>10.16</v>
@@ -2138,39 +2138,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.008</v>
+        <v>0.34</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5157000</v>
+        <v>5930000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="H38" t="n">
-        <v>53.51</v>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.616</v>
+        <v>0.347</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.614</v>
+        <v>0.333</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2192,19 +2192,19 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.0019</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4932400</v>
+        <v>5664500</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>38.63</v>
+        <v>38.01</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.546</v>
+        <v>5.544</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>5.435</v>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0.0069</v>
+        <v>1.45</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4896000</v>
+        <v>5515600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>23.66</v>
+        <v>22.46</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.72</v>
+        <v>1.719</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>1.958</v>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.0467</v>
+        <v>0.625</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4610600</v>
+        <v>5406500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.22</v>
+        <v>0.49</v>
       </c>
       <c r="H41" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.576</v>
+        <v>0.616</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.539</v>
+        <v>0.614</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,39 +2318,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.185</v>
+        <v>1.2</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4346000</v>
+        <v>4972200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="H42" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.15</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.165</v>
+        <v>1.237</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.166</v>
+        <v>1.329</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,39 +2363,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4183100</v>
+        <v>4961200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>4.69</v>
+        <v>1.26</v>
       </c>
       <c r="H43" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.28</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.439</v>
+        <v>0.097</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.439</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4166600</v>
+        <v>4899900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="H44" t="n">
-        <v>38.06</v>
+        <v>47.94</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.51</v>
+        <v>0.576</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.526</v>
+        <v>0.538</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2453,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4056100</v>
+        <v>4632400</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.29</v>
+        <v>0.55</v>
       </c>
       <c r="H45" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.06</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.616</v>
+        <v>0.51</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.604</v>
+        <v>0.526</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.07139999999999999</v>
+        <v>2.66</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0.035</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3714400</v>
+        <v>4517800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.13</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.126</v>
+        <v>2.65</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3703000</v>
+        <v>4411500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.19</v>
+        <v>0.55</v>
       </c>
       <c r="H47" t="n">
-        <v>49.15</v>
+        <v>23.94</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.295</v>
+        <v>0.539</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.295</v>
+        <v>0.619</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,39 +2588,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.09</v>
+        <v>0.19</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.1066</v>
+        <v>0.0857</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3647800</v>
+        <v>4346100</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2.53</v>
+        <v>0.8</v>
       </c>
       <c r="H48" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.38</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.089</v>
+        <v>0.165</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.096</v>
+        <v>0.166</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,39 +2633,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.745</v>
+        <v>0.44</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3496800</v>
+        <v>4183100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.42</v>
+        <v>4.69</v>
       </c>
       <c r="H49" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.33</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.773</v>
+        <v>0.439</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.772</v>
+        <v>0.439</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>0.1053</v>
+        <v>0.13</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3480200</v>
+        <v>4177700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="H50" t="n">
-        <v>42.3</v>
+        <v>57.1</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.121</v>
+        <v>0.1</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,28 +2723,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0</v>
+        <v>3.75</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3468700</v>
+        <v>4127200</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>0.43</v>
       </c>
       <c r="H51" t="n">
-        <v>22.54</v>
+        <v>56.59</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.538</v>
+        <v>3.635</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.619</v>
+        <v>2.962</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,28 +2768,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.65</v>
+        <v>0.625</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3450500</v>
+        <v>4056100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.18</v>
+        <v>1.29</v>
       </c>
       <c r="H52" t="n">
-        <v>51.56</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.649</v>
+        <v>0.616</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.55</v>
+        <v>0.604</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,28 +2813,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.745</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3432300</v>
+        <v>3922800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H53" t="n">
-        <v>39.69</v>
+        <v>41.25</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.179</v>
+        <v>0.773</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.197</v>
+        <v>0.772</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,28 +2858,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.885</v>
+        <v>1.11</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0412</v>
+        <v>0.0183</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3391100</v>
+        <v>3853200</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="H54" t="n">
-        <v>45.01</v>
+        <v>55.47</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.078</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.843</v>
+        <v>1.044</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,28 +2903,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1.74</v>
+        <v>0.29</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0114</v>
+        <v>-0.0169</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3345700</v>
+        <v>3752500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="H55" t="n">
-        <v>28.83</v>
+        <v>28.48</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.833</v>
+        <v>0.295</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1.972</v>
+        <v>0.295</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,39 +2948,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.0227</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3315200</v>
+        <v>3726200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.48</v>
+        <v>1.15</v>
       </c>
       <c r="H56" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.12</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.623</v>
+        <v>1.831</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.699</v>
+        <v>1.971</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3283800</v>
+        <v>3700700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>45.07</v>
+        <v>36.27</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.306</v>
+        <v>0.11</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.314</v>
+        <v>0.121</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,28 +3038,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3.79</v>
+        <v>0.89</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0188</v>
+        <v>0.0471</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3221200</v>
+        <v>3643200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H58" t="n">
-        <v>57.5</v>
+        <v>45.75</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.639</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.963</v>
+        <v>0.844</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,28 +3083,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>0.0323</v>
+        <v>1.66</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3043300</v>
+        <v>3511300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H59" t="n">
-        <v>62.44</v>
+        <v>53.01</v>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.19</v>
+        <v>1.623</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.184</v>
+        <v>1.699</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,28 +3128,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.01</v>
+        <v>0.17</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.0303</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2972600</v>
+        <v>3464200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="H60" t="n">
-        <v>46.04</v>
+        <v>39.69</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.055</v>
+        <v>0.179</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.953</v>
+        <v>0.197</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3173,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2867300</v>
+        <v>3426500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H61" t="n">
-        <v>33.84</v>
+        <v>43.72</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.397</v>
+        <v>1.305</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.407</v>
+        <v>1.314</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,39 +3218,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2845000</v>
+        <v>3426400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="H62" t="n">
-        <v>44.87</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.44</v>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.778</v>
+        <v>1.19</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.735</v>
+        <v>1.184</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,40 +3263,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>0.0092</v>
+        <v>0.425</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2813900</v>
+        <v>3387200</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H63" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.3</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>0.5590000000000001</v>
-      </c>
+        <v>0.464</v>
+      </c>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
     </row>
@@ -3308,28 +3306,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>-0.0345</v>
+        <v>3.8</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0.016</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2614000</v>
+        <v>3286800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="H64" t="n">
-        <v>17.96</v>
+        <v>47.36</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3337,9 +3335,11 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K64" s="2" t="n"/>
+        <v>3.949</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>3.536</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3351,39 +3351,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>0.0673</v>
+        <v>0.0222</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2592900</v>
+        <v>3263800</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.61</v>
+        <v>1.29</v>
       </c>
       <c r="H65" t="n">
-        <v>58.81</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.56</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.049</v>
+        <v>0.645</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.905</v>
+        <v>0.552</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3396,39 +3396,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0306</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2567800</v>
+        <v>3054500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1.02</v>
+        <v>0.37</v>
       </c>
       <c r="H66" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.04</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.646</v>
+        <v>1.055</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.552</v>
+        <v>0.953</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3441,28 +3441,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>2.7</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2565500</v>
+        <v>2979600</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H67" t="n">
-        <v>36.49</v>
+        <v>44.12</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.163</v>
+        <v>2.777</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.232</v>
+        <v>2.734</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3495,19 +3495,19 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.0784</v>
+        <v>0.098</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2544200</v>
+        <v>2944900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H68" t="n">
-        <v>64.09</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0.464</v>
@@ -3531,28 +3531,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E69" s="9" t="n">
-        <v>0.0536</v>
+        <v>1.04</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2452400</v>
+        <v>2941100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.41</v>
+        <v>5.34</v>
       </c>
       <c r="H69" t="n">
-        <v>28.25</v>
+        <v>31.74</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.339</v>
+        <v>1.104</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.374</v>
+        <v>1.126</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3576,39 +3576,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.0435</v>
+        <v>0.0183</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2425400</v>
+        <v>2920500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H70" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.73</v>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.777</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3621,28 +3621,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E71" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.39</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2423600</v>
+        <v>2872600</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H71" t="n">
-        <v>55.47</v>
+        <v>33.84</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.078</v>
+        <v>0.397</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.044</v>
+        <v>0.407</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3666,28 +3666,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.2</v>
+        <v>7.31</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2342700</v>
+        <v>2774200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H72" t="n">
-        <v>54.56</v>
+        <v>34.62</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.171</v>
+        <v>7.48</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.133</v>
+        <v>7.977</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3711,39 +3711,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.07</v>
+        <v>0.52</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2293400</v>
+        <v>2773800</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4.17</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.106</v>
+        <v>0.52</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.127</v>
+        <v>0.457</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3756,28 +3756,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>-0.0053</v>
+        <v>1.12</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2289400</v>
+        <v>2772900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="H74" t="n">
-        <v>59.85</v>
+        <v>59.53</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.918</v>
+        <v>1.05</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.874</v>
+        <v>0.905</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3801,28 +3801,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.8</v>
+        <v>0.295</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>0.0191</v>
+        <v>0.0536</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2260600</v>
+        <v>2726600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="H75" t="n">
-        <v>58.44</v>
+        <v>28.25</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.791</v>
+        <v>0.339</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.77</v>
+        <v>0.374</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3846,28 +3846,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.05</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2248700</v>
+        <v>2717800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H76" t="n">
-        <v>44.1</v>
+        <v>36.49</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6.414</v>
+        <v>2.163</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>6.776</v>
+        <v>2.232</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3891,39 +3891,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>0.004099999999999999</v>
+        <v>1.91</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2201600</v>
+        <v>2573600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="H77" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.97</v>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7.48</v>
+        <v>1.926</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>7.977</v>
+        <v>1.952</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3936,28 +3936,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0</v>
+        <v>6.37</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2151600</v>
+        <v>2562100</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>35.67</v>
+        <v>44.1</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.236</v>
+        <v>6.414</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.329</v>
+        <v>6.776</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3981,28 +3981,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6.76</v>
+        <v>0.845</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2087300</v>
+        <v>2490800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.48</v>
+        <v>0.66</v>
       </c>
       <c r="H79" t="n">
-        <v>50.09</v>
+        <v>55.37</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>6.756</v>
+        <v>0.826</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>6.83</v>
+        <v>0.777</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4026,28 +4026,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0.0492</v>
+        <v>0.93</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2085600</v>
+        <v>2485600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="H80" t="n">
-        <v>51.3</v>
+        <v>56.39</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3.851</v>
+        <v>0.918</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.664</v>
+        <v>0.873</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4071,28 +4071,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.525</v>
+        <v>1.2</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0169</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2073700</v>
+        <v>2457000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="H81" t="n">
-        <v>53.48</v>
+        <v>54.56</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.52</v>
+        <v>1.171</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.457</v>
+        <v>1.133</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4116,28 +4116,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0.6</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2057100</v>
+        <v>2413400</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H82" t="n">
-        <v>44.04</v>
+        <v>40.82</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.046</v>
+        <v>0.656</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.073</v>
+        <v>0.619</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4170,19 +4170,19 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.845</v>
+        <v>0.85</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0117</v>
+        <v>-0.0058</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2041300</v>
+        <v>2370000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="H83" t="n">
-        <v>17.19</v>
+        <v>17.77</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.923</v>
+        <v>0.924</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0.976</v>
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.6</v>
+        <v>0.865</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0058</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2008800</v>
+        <v>2342900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.22</v>
+        <v>0.75</v>
       </c>
       <c r="H84" t="n">
-        <v>40.82</v>
+        <v>51.9</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.656</v>
+        <v>0.864</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.619</v>
+        <v>0.86</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4251,28 +4251,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0519</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1948400</v>
+        <v>2268300</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H85" t="n">
-        <v>48.74</v>
+        <v>51.73</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3.953</v>
+        <v>3.852</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.537</v>
+        <v>3.664</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4296,28 +4296,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2.82</v>
+        <v>6.75</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.0444</v>
+        <v>0.003</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1895400</v>
+        <v>2263500</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="H86" t="n">
-        <v>53.62</v>
+        <v>49.39</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.792</v>
+        <v>6.755</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2.656</v>
+        <v>6.83</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4341,39 +4341,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>-0.0205</v>
+        <v>0.8</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1793100</v>
+        <v>2260600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H87" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.926</v>
+        <v>0.791</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.952</v>
+        <v>0.77</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4386,28 +4386,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.225</v>
+        <v>2.84</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0403</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1769600</v>
+        <v>2144800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.09</v>
+        <v>0.58</v>
       </c>
       <c r="H88" t="n">
-        <v>37.16</v>
+        <v>44.27</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.237</v>
+        <v>2.913</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.289</v>
+        <v>3.019</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4431,39 +4431,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4.66</v>
+        <v>2.02</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0098</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1753000</v>
+        <v>2131200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="H89" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.04</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>4.59</v>
+        <v>2.046</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4.492</v>
+        <v>2.073</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,39 +4476,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0444</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1704900</v>
+        <v>2091000</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.47</v>
+        <v>0.23</v>
       </c>
       <c r="H90" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.215</v>
+        <v>2.792</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.158</v>
+        <v>2.656</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4521,39 +4521,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.385</v>
+        <v>5.61</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.0389</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1676000</v>
+        <v>2055200</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1.56</v>
+        <v>0.55</v>
       </c>
       <c r="H91" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.59</v>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.381</v>
+        <v>5.515</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.378</v>
+        <v>5.398</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4566,39 +4566,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>REACHTEN</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1619500</v>
+        <v>2006700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.18</v>
+        <v>2.99</v>
       </c>
       <c r="H92" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.278</v>
+        <v>0.344</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.302</v>
+        <v>0.361</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4611,39 +4611,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.515</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1609100</v>
+        <v>1987900</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="H93" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.96</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.388</v>
+        <v>0.589</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.391</v>
+        <v>0.601</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4656,28 +4656,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.675</v>
+        <v>1.37</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0074</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1597800</v>
+        <v>1970900</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.49</v>
+        <v>1.02</v>
       </c>
       <c r="H94" t="n">
-        <v>37.6</v>
+        <v>51.55</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.731</v>
+        <v>1.371</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.745</v>
+        <v>1.343</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4701,28 +4701,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0423</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1577800</v>
+        <v>1939100</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.82</v>
+        <v>0.13</v>
       </c>
       <c r="H95" t="n">
-        <v>47.38</v>
+        <v>39.53</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.37</v>
+        <v>0.756</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.343</v>
+        <v>0.722</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4746,28 +4746,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E96" s="9" t="n">
-        <v>0.0244</v>
+        <v>5.83</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1573200</v>
+        <v>1897900</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1.02</v>
+        <v>0.23</v>
       </c>
       <c r="H96" t="n">
-        <v>40.04</v>
+        <v>31.39</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.223</v>
+        <v>6.066</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.232</v>
+        <v>6.333</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4791,39 +4791,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E97" s="9" t="n">
-        <v>0.04</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1569700</v>
+        <v>1880300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="H97" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.27</v>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.252</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.17</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4836,28 +4836,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0145</v>
+        <v>0.0156</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1566200</v>
+        <v>1852200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H98" t="n">
-        <v>50.49</v>
+        <v>43.65</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.354</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.326</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="E99" s="9" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.78</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1549400</v>
+        <v>1826900</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.27</v>
+        <v>0.84</v>
       </c>
       <c r="H99" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>15.31</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>6.132</v>
+        <v>0.952</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>5.893</v>
+        <v>1.085</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4926,28 +4926,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0309</v>
+        <v>0.22</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1532200</v>
+        <v>1826500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.7</v>
+        <v>0.09</v>
       </c>
       <c r="H100" t="n">
-        <v>15.56</v>
+        <v>33.7</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.953</v>
+        <v>0.237</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.085</v>
+        <v>0.289</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4971,28 +4971,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1520500</v>
+        <v>1785400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H101" t="n">
-        <v>46.75</v>
+        <v>31.28</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.616</v>
+        <v>3.391</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2.605</v>
+        <v>3.615</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5016,28 +5016,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>5.85</v>
+        <v>8.44</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0152</v>
+        <v>-0.0071</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1490100</v>
+        <v>1779400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.18</v>
+        <v>0.84</v>
       </c>
       <c r="H102" t="n">
-        <v>32.16</v>
+        <v>44.22</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>6.068</v>
+        <v>8.664999999999999</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>6.333</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5061,28 +5061,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.77</v>
+        <v>0.35</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.0145</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1457900</v>
+        <v>1762100</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.62</v>
+        <v>0.19</v>
       </c>
       <c r="H103" t="n">
-        <v>57.27</v>
+        <v>50.49</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.732</v>
+        <v>0.354</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.703</v>
+        <v>0.326</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5106,39 +5106,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>0.038</v>
+        <v>4.66</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1411300</v>
+        <v>1755800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="H104" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.65</v>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.423</v>
+        <v>4.59</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.415</v>
+        <v>4.492</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5151,39 +5151,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>2.3</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1406900</v>
+        <v>1753100</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="H105" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.17</v>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.637</v>
+        <v>2.215</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.621</v>
+        <v>2.158</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5196,39 +5196,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>5.56</v>
+        <v>0.26</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.0196</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1405500</v>
+        <v>1746300</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H106" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.1</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>5.51</v>
+        <v>0.278</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>5.397</v>
+        <v>0.302</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5241,39 +5241,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.39</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1403300</v>
+        <v>1719700</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.15</v>
+        <v>0.73</v>
       </c>
       <c r="H107" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.92</v>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.388</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.391</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5286,39 +5286,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>3.1</v>
+        <v>0.385</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.0098</v>
+        <v>0.0132</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1376700</v>
+        <v>1676000</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.43</v>
+        <v>1.56</v>
       </c>
       <c r="H108" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.801</v>
+        <v>0.381</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.406</v>
+        <v>0.378</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5331,39 +5331,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.59</v>
+        <v>6.49</v>
       </c>
       <c r="E109" s="9" t="n">
         <v>0.0172</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1333100</v>
+        <v>1668400</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H109" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.96</v>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.598</v>
+        <v>6.137</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.585</v>
+        <v>5.894</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5376,39 +5376,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>-0.0385</v>
+        <v>0.77</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1289800</v>
+        <v>1665000</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1.65</v>
+        <v>0.71</v>
       </c>
       <c r="H110" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.27</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.22</v>
+        <v>0.732</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.209</v>
+        <v>0.703</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5421,28 +5421,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.1</v>
+        <v>1.29</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1286000</v>
+        <v>1633400</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="H111" t="n">
-        <v>52.91</v>
+        <v>56.29</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>5.069</v>
+        <v>1.251</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>5.062</v>
+        <v>1.169</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5466,28 +5466,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.865</v>
+        <v>0.675</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.0227</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1275900</v>
+        <v>1626100</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="H112" t="n">
-        <v>51.9</v>
+        <v>37.6</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.864</v>
+        <v>0.731</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.86</v>
+        <v>0.745</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5511,28 +5511,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>0.0433</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1273000</v>
+        <v>1607300</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>59.13</v>
+        <v>46.75</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.775</v>
+        <v>2.616</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.185</v>
+        <v>2.605</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5556,28 +5556,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.21</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1257300</v>
+        <v>1604400</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.3</v>
+        <v>1.04</v>
       </c>
       <c r="H114" t="n">
-        <v>26.62</v>
+        <v>40.04</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.411</v>
+        <v>0.223</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1.57</v>
+        <v>0.232</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5601,39 +5601,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1252200</v>
+        <v>1561400</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="H115" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.89</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.336</v>
+        <v>1.45</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.343</v>
+        <v>1.465</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5646,28 +5646,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>-0.0139</v>
+        <v>0.595</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1240700</v>
+        <v>1526600</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
       <c r="H116" t="n">
-        <v>43.12</v>
+        <v>50.14</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.732</v>
+        <v>0.599</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.728</v>
+        <v>0.585</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5691,28 +5691,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.15</v>
+        <v>2.6</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>0.036</v>
+        <v>0.0277</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1199100</v>
+        <v>1514200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H117" t="n">
-        <v>57.09</v>
+        <v>37.26</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.112</v>
+        <v>2.845</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.879</v>
+        <v>2.874</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5736,28 +5736,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2.8</v>
+        <v>0.405</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>0.0256</v>
+        <v>0.0253</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1176000</v>
+        <v>1501300</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H118" t="n">
-        <v>41.54</v>
+        <v>46.12</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.909</v>
+        <v>0.422</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>3.018</v>
+        <v>0.415</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5781,28 +5781,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.625</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1164500</v>
+        <v>1451900</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.15</v>
+        <v>0.66</v>
       </c>
       <c r="H119" t="n">
-        <v>44.4</v>
+        <v>45.22</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.275</v>
+        <v>0.637</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.296</v>
+        <v>0.62</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5826,28 +5826,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E120" s="9" t="n">
-        <v>0.0217</v>
+        <v>1.28</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1072000</v>
+        <v>1446600</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H120" t="n">
-        <v>44.67</v>
+        <v>27.28</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.247</v>
+        <v>1.412</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.255</v>
+        <v>1.571</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5871,28 +5871,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>-0.0352</v>
+        <v>5.1</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1071200</v>
+        <v>1437800</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>40.08</v>
+        <v>52.91</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.757</v>
+        <v>5.069</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.722</v>
+        <v>5.062</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5916,28 +5916,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1069600</v>
+        <v>1433100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>48.27</v>
+        <v>48.93</v>
       </c>
       <c r="I122" s="10" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.11</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.099</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5961,28 +5961,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.915</v>
+        <v>2.84</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.0253</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1068000</v>
+        <v>1383900</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.67</v>
+        <v>0.27</v>
       </c>
       <c r="H123" t="n">
-        <v>51.31</v>
+        <v>57.59</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.915</v>
+        <v>2.77</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.869</v>
+        <v>2.184</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6006,39 +6006,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0053</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1067200</v>
+        <v>1376800</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="H124" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.09</v>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.975</v>
+        <v>2.8</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.056</v>
+        <v>2.406</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6051,39 +6051,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.1</v>
+        <v>0.71</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1064900</v>
+        <v>1371200</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="H125" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.12</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>2.11</v>
+        <v>0.732</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.099</v>
+        <v>0.728</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6096,28 +6096,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E126" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.93</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1056700</v>
+        <v>1361500</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="H126" t="n">
-        <v>77.73999999999999</v>
+        <v>26.87</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.269</v>
+        <v>0.974</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.217</v>
+        <v>1.056</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6141,28 +6141,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.46</v>
+        <v>0.215</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>0.011</v>
+        <v>0.0488</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1038900</v>
+        <v>1317900</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="H127" t="n">
-        <v>28.42</v>
+        <v>50.02</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.502</v>
+        <v>0.217</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6186,28 +6186,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>0.022</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1026200</v>
+        <v>1296400</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.92</v>
+        <v>0.17</v>
       </c>
       <c r="H128" t="n">
-        <v>41.54</v>
+        <v>30.99</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.272</v>
+        <v>0.502</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.276</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6231,39 +6231,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E129" s="9" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1025600</v>
+        <v>1289800</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.18</v>
+        <v>1.65</v>
       </c>
       <c r="H129" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.764</v>
+        <v>0.22</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6276,39 +6276,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.555</v>
+        <v>1.14</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.027</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1018500</v>
+        <v>1263100</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.89</v>
+        <v>0.15</v>
       </c>
       <c r="H130" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="I130" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.41</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.57</v>
+        <v>1.111</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.613</v>
+        <v>0.879</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6321,39 +6321,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>-0.0129</v>
+        <v>0.335</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1012600</v>
+        <v>1255000</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="H131" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>8.661</v>
+        <v>0.336</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>8.702999999999999</v>
+        <v>0.343</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6366,39 +6366,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.02</v>
+        <v>0.265</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0392</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1010600</v>
+        <v>1164500</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.43</v>
+        <v>0.15</v>
       </c>
       <c r="H132" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.002</v>
+        <v>0.275</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.983</v>
+        <v>0.296</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,28 +6411,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.885</v>
+        <v>1.28</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0492</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>967700</v>
+        <v>1154800</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H133" t="n">
-        <v>36.85</v>
+        <v>50.79</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.911</v>
+        <v>1.285</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.929</v>
+        <v>1.22</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6456,39 +6456,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.15</v>
+        <v>0.33</v>
       </c>
       <c r="E134" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0476</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>919700</v>
+        <v>1151000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="H134" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>77.73999999999999</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.109</v>
+        <v>0.269</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.059</v>
+        <v>0.217</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6501,39 +6501,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.615</v>
+        <v>0.305</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>0.0513</v>
+        <v>0.0339</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>910400</v>
+        <v>1137700</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>11.97</v>
+        <v>0.18</v>
       </c>
       <c r="H135" t="n">
-        <v>74.33</v>
-      </c>
-      <c r="I135" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.53</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.545</v>
+        <v>0.318</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.542</v>
+        <v>0.338</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6546,39 +6546,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.27</v>
+        <v>0.44</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>895500</v>
+        <v>1099900</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H136" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.95</v>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.284</v>
+        <v>0.388</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.22</v>
+        <v>0.359</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,28 +6591,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>-0.006</v>
+        <v>0.77</v>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>884600</v>
+        <v>1099800</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.59</v>
+        <v>0.19</v>
       </c>
       <c r="H137" t="n">
-        <v>36.21</v>
+        <v>54.2</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.848</v>
+        <v>0.765</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.862</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,28 +6636,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0111</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>861600</v>
+        <v>1099700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>55.17</v>
+        <v>50.61</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.915</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.513</v>
+        <v>0.869</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,28 +6681,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.74</v>
+        <v>7.32</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>0.035</v>
+        <v>0.0195</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>849200</v>
+        <v>1087500</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H139" t="n">
-        <v>52.39</v>
+        <v>51.83</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.741</v>
+        <v>7.359</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.673</v>
+        <v>6.882</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6726,39 +6726,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E140" s="8" t="n">
-        <v>0</v>
+        <v>0.825</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>825400</v>
+        <v>1074800</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.09</v>
+        <v>0.72</v>
       </c>
       <c r="H140" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I140" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.21</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>13.017</v>
+        <v>0.848</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>13.443</v>
+        <v>0.862</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,28 +6771,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.79</v>
+        <v>0.235</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>0.0327</v>
+        <v>0.0217</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>821500</v>
+        <v>1072000</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="H141" t="n">
-        <v>53.5</v>
+        <v>44.67</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.777</v>
+        <v>0.247</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.768</v>
+        <v>0.255</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,28 +6816,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7.37</v>
+        <v>2.69</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>0.0265</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>813200</v>
+        <v>1048100</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H142" t="n">
-        <v>52.81</v>
+        <v>55.08</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>7.363</v>
+        <v>2.66</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>6.883</v>
+        <v>2.24</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,28 +6861,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.13</v>
+        <v>10.74</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>0.029</v>
+        <v>0.0407</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>812600</v>
+        <v>1041700</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H143" t="n">
-        <v>52.91</v>
+        <v>59.17</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>2.115</v>
+        <v>10.421</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.989</v>
+        <v>9.731999999999999</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,28 +6906,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E144" s="9" t="n">
-        <v>0.0356</v>
+        <v>0.27</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>803000</v>
+        <v>1026200</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.16</v>
+        <v>0.92</v>
       </c>
       <c r="H144" t="n">
-        <v>38.41</v>
+        <v>41.54</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>2.846</v>
+        <v>0.272</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.874</v>
+        <v>0.276</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6951,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>0.0593</v>
+        <v>0.0042</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>775300</v>
+        <v>1022000</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H145" t="n">
-        <v>54.69</v>
+        <v>43.29</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.659</v>
+        <v>2.448</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.24</v>
+        <v>2.379</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,28 +6996,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.3</v>
+        <v>0.885</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>0.04</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>770300</v>
+        <v>1021000</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="H146" t="n">
-        <v>47.66</v>
+        <v>36.85</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.331</v>
+        <v>0.911</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>1.279</v>
+        <v>0.929</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,39 +7041,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>10.58</v>
+        <v>13</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>0.0252</v>
+        <v>0.0015</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>740600</v>
+        <v>1020000</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="H147" t="n">
-        <v>56.81</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>10.406</v>
+        <v>13.019</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>9.728999999999999</v>
+        <v>13.443</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,39 +7086,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>-0.0216</v>
+        <v>0.555</v>
+      </c>
+      <c r="E148" s="9" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>739000</v>
+        <v>1018500</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.12</v>
+        <v>0.89</v>
       </c>
       <c r="H148" t="n">
-        <v>26.45</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.94</v>
+      </c>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>3.383</v>
+        <v>0.57</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>3.614</v>
+        <v>0.613</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,28 +7131,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>720200</v>
+        <v>1010600</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>11.81</v>
+        <v>1.43</v>
       </c>
       <c r="H149" t="n">
-        <v>58.79</v>
+        <v>59.5</v>
       </c>
       <c r="I149" s="10" t="inlineStr">
         <is>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.736</v>
+        <v>1.002</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.741</v>
+        <v>0.983</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>-0.0159</v>
+        <v>0.575</v>
+      </c>
+      <c r="E150" s="9" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>719900</v>
+        <v>947400</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H150" t="n">
-        <v>61.66</v>
+        <v>56.23</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.466</v>
+        <v>0.513</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,28 +7221,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>4.18</v>
+        <v>0.735</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>0.0048</v>
+        <v>0.028</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>690000</v>
+        <v>943900</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H151" t="n">
-        <v>45.03</v>
+        <v>51.61</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>4.297</v>
+        <v>0.741</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>4.333</v>
+        <v>0.673</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7266,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E152" s="9" t="n">
+        <v>0.029</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>668900</v>
+        <v>924500</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H152" t="n">
-        <v>39.49</v>
+        <v>52.91</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.734</v>
+        <v>2.115</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.769</v>
+        <v>1.989</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,39 +7311,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E153" s="8" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>662500</v>
+        <v>924100</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.11</v>
+        <v>12.15</v>
       </c>
       <c r="H153" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.33</v>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.78</v>
+        <v>0.545</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.895</v>
+        <v>0.542</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,39 +7356,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>657800</v>
+        <v>919800</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H154" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.209</v>
+        <v>2.109</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.233</v>
+        <v>2.059</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,28 +7401,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E155" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.62</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>654300</v>
+        <v>857100</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.58</v>
+        <v>0.15</v>
       </c>
       <c r="H155" t="n">
-        <v>46.48</v>
+        <v>61.66</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.524</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.506</v>
+        <v>0.466</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,39 +7446,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>-0.0062</v>
+        <v>0.79</v>
+      </c>
+      <c r="E156" s="9" t="n">
+        <v>0.0327</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>654100</v>
+        <v>831100</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H156" t="n">
-        <v>76.38</v>
-      </c>
-      <c r="I156" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.5</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.727</v>
+        <v>0.777</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.645</v>
+        <v>0.768</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7491,28 +7491,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>0.0036</v>
+        <v>0.027</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>646100</v>
+        <v>828900</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="H157" t="n">
-        <v>40.97</v>
+        <v>52.85</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>2.86</v>
+        <v>3.026</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>2.859</v>
+        <v>2.851</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7545,19 +7545,19 @@
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.0404</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>643600</v>
+        <v>796600</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H158" t="n">
-        <v>49.25</v>
+        <v>50.63</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.047</v>
+        <v>1.048</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7581,39 +7581,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>623400</v>
+        <v>790000</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H159" t="n">
-        <v>54.38</v>
-      </c>
-      <c r="I159" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.79</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.258</v>
+        <v>4.299</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.279</v>
+        <v>4.334</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7626,28 +7626,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E160" s="8" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E160" s="9" t="n">
+        <v>0.032</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>615400</v>
+        <v>788500</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="H160" t="n">
-        <v>33.37</v>
+        <v>46.58</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.59</v>
+        <v>1.33</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0.602</v>
+        <v>1.278</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7671,39 +7671,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.29</v>
+      </c>
+      <c r="E161" s="9" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>590600</v>
+        <v>755500</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.52</v>
+        <v>0.14</v>
       </c>
       <c r="H161" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.631</v>
+        <v>1.259</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.631</v>
+        <v>1.279</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7716,39 +7716,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>PWF</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>3.04</v>
+        <v>0.76</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.027</v>
+        <v>0.0133</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>585200</v>
+        <v>735800</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.18</v>
+        <v>12.07</v>
       </c>
       <c r="H162" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.79</v>
+      </c>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>3.026</v>
+        <v>0.736</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2.851</v>
+        <v>0.741</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7761,39 +7761,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E163" s="9" t="n">
-        <v>0.0288</v>
+        <v>0.8</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>565300</v>
+        <v>707200</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H163" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.38</v>
+      </c>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.212</v>
+        <v>0.727</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.297</v>
+        <v>0.645</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7806,39 +7806,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>-0.0185</v>
+        <v>1.67</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>558200</v>
+        <v>703100</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="H164" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="I164" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.49</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.842</v>
+        <v>1.734</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.904</v>
+        <v>1.769</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7851,28 +7851,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.87</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>538600</v>
+        <v>698700</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H165" t="n">
-        <v>41.89</v>
+        <v>34.38</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1.45</v>
+        <v>0.903</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1.465</v>
+        <v>0.956</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7896,28 +7896,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E166" s="9" t="n">
-        <v>0.0042</v>
+        <v>1.2</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>516300</v>
+        <v>694200</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="H166" t="n">
-        <v>43.29</v>
+        <v>49.36</v>
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>2.448</v>
+        <v>1.245</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2.379</v>
+        <v>1.059</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7941,28 +7941,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.875</v>
+        <v>1.72</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>514300</v>
+        <v>685400</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H167" t="n">
-        <v>36.65</v>
+        <v>37.33</v>
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.903</v>
+        <v>1.781</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0.956</v>
+        <v>1.895</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7986,39 +7986,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.49</v>
+        <v>0.515</v>
       </c>
       <c r="E168" s="9" t="n">
-        <v>0.0034</v>
+        <v>0.0198</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>510000</v>
+        <v>684300</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H168" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I168" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.2</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>1.509</v>
+        <v>0.525</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>1.501</v>
+        <v>0.506</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8031,28 +8031,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E169" s="8" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E169" s="9" t="n">
+        <v>0.0498</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>506800</v>
+        <v>679500</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H169" t="n">
-        <v>34.52</v>
+        <v>41.59</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.95</v>
+        <v>2.209</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>1.005</v>
+        <v>2.233</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8076,45 +8076,630 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E170" s="9" t="n">
-        <v>0.0117</v>
+        <v>2.76</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>501200</v>
+        <v>661000</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.09</v>
+        <v>0.64</v>
       </c>
       <c r="H170" t="n">
-        <v>47.31</v>
-      </c>
-      <c r="I170" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>4.35</v>
+        <v>2.859</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>4.431</v>
+        <v>2.859</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E171" s="9" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>660900</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H171" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>646600</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H172" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E173" s="9" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>615000</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H173" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>4.432</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>602200</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H174" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I174" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>556000</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H175" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="I175" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>2.566</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>539700</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H176" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="I176" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>531900</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H177" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E178" s="9" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>524800</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H178" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I178" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IGBREIT</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>520300</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H179" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>2.764</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>511300</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H180" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>3.423</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>510500</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H181" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="I181" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>7.587</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>509300</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H182" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>3.176</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E183" s="9" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>508400</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H183" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M170"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.07690000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>204083800</v>
+        <v>209740900</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H2" t="n">
         <v>23.66</v>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>62797800</v>
+        <v>62942400</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -639,10 +639,10 @@
         <v>0.0455</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>37346600</v>
+        <v>41073600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
         <v>69.7</v>
@@ -684,10 +684,10 @@
         <v>0.0111</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>37124700</v>
+        <v>39650800</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H5" t="n">
         <v>67.28</v>
@@ -714,28 +714,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7.31</v>
+        <v>0.415</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0235</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22705300</v>
+        <v>29707300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.53</v>
+        <v>0.84</v>
       </c>
       <c r="H6" t="n">
-        <v>37.41</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.552</v>
+        <v>0.378</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7.699</v>
+        <v>0.27</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,28 +759,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.415</v>
+        <v>7.31</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.0235</v>
+        <v>-0.0227</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22633800</v>
+        <v>24115900</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.64</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
-        <v>71.84999999999999</v>
+        <v>37.41</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.378</v>
+        <v>7.552</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.27</v>
+        <v>7.699</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>-0.0278</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>21324200</v>
+        <v>21476400</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.92</v>
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>19996200</v>
+        <v>20121200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>8.58</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>69.25</v>
+        <v>58.64</v>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>17997800</v>
+        <v>18080800</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.72</v>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>17060200</v>
+        <v>17395100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.5</v>
+        <v>16.16</v>
       </c>
       <c r="H12" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.44</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.155</v>
+        <v>0.059</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.157</v>
+        <v>0.057</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.025</v>
+        <v>0.155</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15535300</v>
+        <v>17060300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>60.74</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.923</v>
+        <v>0.155</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.728</v>
+        <v>0.157</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.31</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>15413700</v>
+        <v>16747400</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.55</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.482</v>
+        <v>0.309</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.482</v>
+        <v>0.299</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,28 +1119,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
+        <v>6.66</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.0711</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>15009200</v>
+        <v>16646000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.21</v>
+        <v>2.15</v>
       </c>
       <c r="H15" t="n">
-        <v>46.24</v>
+        <v>21.86</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.161</v>
+        <v>7.28</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.138</v>
+        <v>7.641</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,28 +1164,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.075</v>
+        <v>2.03</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>14815200</v>
+        <v>16171400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>13.76</v>
+        <v>0.53</v>
       </c>
       <c r="H16" t="n">
-        <v>68.44</v>
+        <v>59.85</v>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.059</v>
+        <v>1.921</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.057</v>
+        <v>1.727</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,28 +1209,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0767</v>
+        <v>0.455</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>14689300</v>
+        <v>15767600</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.9</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="n">
-        <v>21.23</v>
+        <v>41.76</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.276</v>
+        <v>0.482</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>7.641</v>
+        <v>0.482</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,39 +1254,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.145</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>14362600</v>
+        <v>15722100</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>263.32</v>
+        <v>0.22</v>
       </c>
       <c r="H18" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.17</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.057</v>
+        <v>0.161</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.062</v>
+        <v>0.138</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12720500</v>
+        <v>15048900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>57.12</v>
+        <v>52.75</v>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0.8100000000000001</v>
@@ -1344,28 +1344,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.1818</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>12650700</v>
+        <v>14362800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.67</v>
+        <v>263.32</v>
       </c>
       <c r="H20" t="n">
-        <v>54.55</v>
+        <v>69.25</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.309</v>
+        <v>0.057</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.299</v>
+        <v>0.063</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,33 +1389,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0196</v>
+        <v>0.775</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>12137600</v>
+        <v>12982200</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
+        <v>0.85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1427,39 +1434,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0</v>
+        <v>0.315</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.05</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>11844800</v>
+        <v>12828200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.77</v>
+        <v>1.57</v>
       </c>
       <c r="H22" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.39</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.775</v>
+        <v>0.301</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.776</v>
+        <v>0.28</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,29 +1479,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.0464</v>
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>10430200</v>
+        <v>12371400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>0.47</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n"/>
@@ -1510,28 +1517,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.1045</v>
+        <v>0.865</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10415700</v>
+        <v>12003100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.89</v>
+        <v>0.61</v>
       </c>
       <c r="H24" t="n">
-        <v>65.31</v>
+        <v>45.57</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
@@ -1539,9 +1546,11 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="K24" s="2" t="n"/>
+        <v>0.868</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.869</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1553,39 +1562,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.31</v>
+        <v>4.82</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.0169</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10346200</v>
+        <v>10947200</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.27</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.68</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3</v>
+        <v>4.729</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.28</v>
+        <v>4.856</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1598,40 +1607,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.455</v>
+        <v>0.785</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0341</v>
+        <v>0.0397</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10286900</v>
+        <v>10578800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>60.99</v>
+        <v>0.1</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0.364</v>
-      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1643,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.46</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9425500</v>
+        <v>10569700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
-        <v>45.57</v>
+        <v>61.88</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
@@ -1672,10 +1674,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.868</v>
+        <v>0.423</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.869</v>
+        <v>0.364</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1688,40 +1690,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.405</v>
+        <v>0.375</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.0658</v>
+        <v>0.1194</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9409600</v>
+        <v>10548700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.75</v>
+        <v>1.91</v>
       </c>
       <c r="H28" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.2</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0.378</v>
-      </c>
+        <v>0.315</v>
+      </c>
+      <c r="K28" s="2" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1733,39 +1733,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9107700</v>
+        <v>9652900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.27</v>
+        <v>0.77</v>
       </c>
       <c r="H29" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.87</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.371</v>
+        <v>0.389</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.369</v>
+        <v>0.378</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,28 +1778,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0417</v>
+        <v>1.15</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.1675</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8967200</v>
+        <v>9639600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3.31</v>
+        <v>6.69</v>
       </c>
       <c r="H30" t="n">
-        <v>69.55</v>
+        <v>55.95</v>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.092</v>
+        <v>1.095</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.092</v>
+        <v>1.097</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1823,39 +1823,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0170</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KANGER</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.38</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8363600</v>
+        <v>9189400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>42.56</v>
+        <v>1.28</v>
       </c>
       <c r="H31" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.05</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.023</v>
+        <v>0.371</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.024</v>
+        <v>0.369</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1868,39 +1868,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4.82</v>
+        <v>0.115</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0417</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8231500</v>
+        <v>9003000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.32</v>
+        <v>3.33</v>
       </c>
       <c r="H32" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.55</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.911</v>
+        <v>0.092</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>4.721</v>
+        <v>0.092</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1922,19 +1922,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.215</v>
+        <v>0.22</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.0222</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7770100</v>
+        <v>8937900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H33" t="n">
-        <v>42.22</v>
+        <v>45.22</v>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.0105</v>
+        <v>4.8</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7066600</v>
+        <v>8913800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H34" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.727</v>
+        <v>4.909</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.856</v>
+        <v>4.721</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2003,28 +2003,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0170</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KANGER</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0.1269</v>
+        <v>0.02</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6435100</v>
+        <v>8416600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4.47</v>
+        <v>42.83</v>
       </c>
       <c r="H35" t="n">
-        <v>52.19</v>
+        <v>43.23</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.091</v>
+        <v>0.023</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.097</v>
+        <v>0.024</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2048,39 +2048,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.455</v>
+        <v>9.99</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0215</v>
+        <v>-0.0089</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6256200</v>
+        <v>6930600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.4</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.513</v>
+        <v>10.012</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2093,39 +2093,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>0.46</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5943000</v>
+        <v>6905400</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="H37" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.37</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.013</v>
+        <v>0.513</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>10.16</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         <v>0.0303</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5930000</v>
+        <v>6269300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H38" t="n">
         <v>49.14</v>
@@ -2183,28 +2183,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.46</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5664500</v>
+        <v>6226000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>38.01</v>
+        <v>23.66</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.544</v>
+        <v>1.72</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.435</v>
+        <v>1.958</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,28 +2228,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0</v>
+        <v>5.25</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5515600</v>
+        <v>6147400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="H40" t="n">
-        <v>22.46</v>
+        <v>38.01</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.719</v>
+        <v>5.544</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1.958</v>
+        <v>5.435</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5406500</v>
+        <v>5918300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
       <c r="H41" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.82</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.616</v>
+        <v>0.576</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.614</v>
+        <v>0.539</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         <v>0.008399999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4972200</v>
+        <v>5874200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="H42" t="n">
         <v>38.15</v>
@@ -2363,28 +2363,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4961200</v>
+        <v>5651900</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.26</v>
+        <v>0.7</v>
       </c>
       <c r="H43" t="n">
-        <v>54.28</v>
+        <v>22.54</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.097</v>
+        <v>0.538</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.475</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4899900</v>
+        <v>5630000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.24</v>
+        <v>0.66</v>
       </c>
       <c r="H44" t="n">
-        <v>47.94</v>
+        <v>36.81</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.576</v>
+        <v>0.51</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.538</v>
+        <v>0.526</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2453,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.48</v>
+        <v>0.625</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4632400</v>
+        <v>5474500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H45" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.51</v>
+        <v>0.616</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.526</v>
+        <v>0.614</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,40 +2498,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.035</v>
+        <v>0.005</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4517800</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H46" t="n">
-        <v>52.13</v>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>2.55</v>
-      </c>
+        <v>5391100</v>
+      </c>
+      <c r="G46" s="5" t="n"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
     </row>
@@ -2543,28 +2534,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0.0119</v>
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4411500</v>
+        <v>5061300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.55</v>
+        <v>1.28</v>
       </c>
       <c r="H47" t="n">
-        <v>23.94</v>
+        <v>54.28</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2572,10 +2563,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.539</v>
+        <v>0.097</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.619</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2579,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.19</v>
+        <v>2.67</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.0857</v>
+        <v>0.0389</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4346100</v>
+        <v>4823000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="H48" t="n">
-        <v>67.38</v>
+        <v>52.68</v>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
@@ -2617,10 +2608,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.165</v>
+        <v>2.651</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.166</v>
+        <v>2.55</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,28 +2624,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0</v>
+        <v>0.19</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4183100</v>
+        <v>4644800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>4.69</v>
+        <v>0.86</v>
       </c>
       <c r="H49" t="n">
-        <v>54.33</v>
+        <v>67.38</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -2662,10 +2653,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.439</v>
+        <v>0.165</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.439</v>
+        <v>0.166</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2693,10 +2684,10 @@
         <v>-0.07139999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4177700</v>
+        <v>4453400</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="H50" t="n">
         <v>57.1</v>
@@ -2723,28 +2714,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.745</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4127200</v>
+        <v>4407800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="H51" t="n">
-        <v>56.59</v>
+        <v>41.25</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2752,10 +2743,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.635</v>
+        <v>0.773</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.962</v>
+        <v>0.772</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,39 +2759,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.625</v>
+        <v>0.1</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4056100</v>
+        <v>4351700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.29</v>
+        <v>0.66</v>
       </c>
       <c r="H52" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.27</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.616</v>
+        <v>0.11</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.604</v>
+        <v>0.121</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,28 +2804,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3922800</v>
+        <v>4287400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="H53" t="n">
-        <v>41.25</v>
+        <v>55.47</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2842,10 +2833,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.773</v>
+        <v>1.078</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.772</v>
+        <v>1.044</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,28 +2849,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.11</v>
+        <v>3.73</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0027</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3853200</v>
+        <v>4272400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H54" t="n">
-        <v>55.47</v>
+        <v>56.12</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2887,10 +2878,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.078</v>
+        <v>3.633</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.044</v>
+        <v>2.962</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,28 +2894,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.0169</v>
+        <v>3.82</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3752500</v>
+        <v>4236700</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.21</v>
+        <v>0.43</v>
       </c>
       <c r="H55" t="n">
-        <v>28.48</v>
+        <v>48.06</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2932,10 +2923,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.295</v>
+        <v>3.951</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.295</v>
+        <v>3.537</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,39 +2939,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0227</v>
+        <v>0.44</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3726200</v>
+        <v>4183100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1.15</v>
+        <v>4.69</v>
       </c>
       <c r="H56" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.33</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.831</v>
+        <v>0.439</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.971</v>
+        <v>0.439</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,28 +2984,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>0.0526</v>
+        <v>0.0357</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3700700</v>
+        <v>4076900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>36.27</v>
+        <v>25.38</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3022,10 +3013,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.11</v>
+        <v>0.339</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.121</v>
+        <v>0.374</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,39 +3029,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.89</v>
+        <v>0.625</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0471</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3643200</v>
+        <v>4056100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.42</v>
+        <v>1.29</v>
       </c>
       <c r="H58" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.844</v>
+        <v>0.604</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,39 +3074,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.017</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3511300</v>
+        <v>4001200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.51</v>
+        <v>1.24</v>
       </c>
       <c r="H59" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.95</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.623</v>
+        <v>1.832</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.699</v>
+        <v>1.971</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,28 +3119,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E60" s="9" t="n">
-        <v>0.0303</v>
+        <v>1.27</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3464200</v>
+        <v>3843600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="H60" t="n">
-        <v>39.69</v>
+        <v>43.72</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3157,10 +3148,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.179</v>
+        <v>1.305</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.197</v>
+        <v>1.314</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3164,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>3.26</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3426500</v>
+        <v>3828900</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="H61" t="n">
-        <v>43.72</v>
+        <v>32.54</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3193,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.305</v>
+        <v>3.392</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.314</v>
+        <v>3.616</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,28 +3209,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.0323</v>
+        <v>1.66</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3426400</v>
+        <v>3804700</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>62.44</v>
+        <v>53.01</v>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
@@ -3247,10 +3238,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.19</v>
+        <v>1.623</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.184</v>
+        <v>1.699</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,28 +3254,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>-0.023</v>
+        <v>0.895</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0.0529</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3387200</v>
+        <v>3787700</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="n">
-        <v>19.3</v>
+        <v>46.48</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3292,9 +3283,11 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K63" s="2" t="n"/>
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.844</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
     </row>
@@ -3306,39 +3299,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3.8</v>
+        <v>1.27</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.016</v>
+        <v>0.0242</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3286800</v>
+        <v>3773800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H64" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.53</v>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3.949</v>
+        <v>1.189</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3.536</v>
+        <v>1.184</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3351,39 +3344,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.29</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3263800</v>
+        <v>3752500</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="H65" t="n">
-        <v>64.56</v>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.48</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.645</v>
+        <v>0.295</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.552</v>
+        <v>0.295</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3396,39 +3389,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.01</v>
+        <v>0.695</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.0296</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3054500</v>
+        <v>3733400</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.37</v>
+        <v>1.48</v>
       </c>
       <c r="H66" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.055</v>
+        <v>0.646</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.953</v>
+        <v>0.552</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3441,39 +3434,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.0037</v>
+        <v>-0.028</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2979600</v>
+        <v>3621500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.23</v>
+        <v>6.58</v>
       </c>
       <c r="H67" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.74</v>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.777</v>
+        <v>1.104</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.734</v>
+        <v>1.126</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3486,39 +3479,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.098</v>
+        <v>0.0408</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2944900</v>
+        <v>3529600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H68" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.499</v>
+        <v>1.056</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.464</v>
+        <v>0.953</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3531,28 +3524,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>-0.028</v>
+        <v>0.17</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2941100</v>
+        <v>3497200</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>5.34</v>
+        <v>0.49</v>
       </c>
       <c r="H69" t="n">
-        <v>31.74</v>
+        <v>39.69</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3560,10 +3553,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.104</v>
+        <v>0.179</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.126</v>
+        <v>0.197</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3576,39 +3569,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.11</v>
+        <v>0.525</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2920500</v>
+        <v>3467400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.74</v>
+        <v>0.25</v>
       </c>
       <c r="H70" t="n">
-        <v>74.73</v>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.48</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.827</v>
+        <v>0.52</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.457</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3621,39 +3614,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2872600</v>
+        <v>3397400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.5</v>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.397</v>
+        <v>1.925</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.407</v>
+        <v>1.952</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3666,28 +3659,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>0.004099999999999999</v>
+        <v>6.38</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2774200</v>
+        <v>3394500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H72" t="n">
-        <v>34.62</v>
+        <v>44.58</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3695,10 +3688,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7.48</v>
+        <v>6.415</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>7.977</v>
+        <v>6.776</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3711,28 +3704,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2773800</v>
+        <v>3387200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="H73" t="n">
-        <v>52.58</v>
+        <v>19.3</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3740,11 +3733,9 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>0.457</v>
-      </c>
+        <v>0.464</v>
+      </c>
+      <c r="K73" s="2" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
     </row>
@@ -3756,28 +3747,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2772900</v>
+        <v>3372600</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="H74" t="n">
-        <v>59.53</v>
+        <v>33.84</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3785,10 +3776,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.05</v>
+        <v>0.397</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.905</v>
+        <v>0.407</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3801,28 +3792,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.295</v>
+        <v>7.33</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>0.0536</v>
+        <v>0.0069</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2726600</v>
+        <v>3340700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="H75" t="n">
-        <v>28.25</v>
+        <v>35.99</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3830,10 +3821,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.339</v>
+        <v>7.482</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.374</v>
+        <v>7.978</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3846,28 +3837,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.125</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2717800</v>
+        <v>3295400</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H76" t="n">
-        <v>36.49</v>
+        <v>36.74</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3875,10 +3866,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.163</v>
+        <v>0.146</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.232</v>
+        <v>0.148</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3891,39 +3882,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>-0.0205</v>
+        <v>2.71</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2573600</v>
+        <v>3130900</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.87</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.926</v>
+        <v>2.778</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.952</v>
+        <v>2.735</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3936,28 +3927,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.05</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2562100</v>
+        <v>3122800</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="H78" t="n">
-        <v>44.1</v>
+        <v>36.49</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3965,10 +3956,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6.414</v>
+        <v>2.163</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>6.776</v>
+        <v>2.232</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3981,39 +3972,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.845</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2490800</v>
+        <v>3078600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H79" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.826</v>
+        <v>0.499</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.777</v>
+        <v>0.464</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4026,39 +4017,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0092</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2485600</v>
+        <v>2964100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H80" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.06999999999999</v>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.918</v>
+        <v>0.824</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.873</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4071,28 +4062,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.945</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2457000</v>
+        <v>2960500</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.33</v>
+        <v>0.52</v>
       </c>
       <c r="H81" t="n">
-        <v>54.56</v>
+        <v>61.74</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4100,10 +4091,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.171</v>
+        <v>0.919</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.133</v>
+        <v>0.874</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4116,28 +4107,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2413400</v>
+        <v>2929000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.26</v>
+        <v>0.68</v>
       </c>
       <c r="H82" t="n">
-        <v>40.82</v>
+        <v>58.07</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4145,10 +4136,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.656</v>
+        <v>1.048</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.619</v>
+        <v>0.904</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4161,28 +4152,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0058</v>
+        <v>0.865</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2370000</v>
+        <v>2842900</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H83" t="n">
-        <v>17.77</v>
+        <v>51.9</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4190,10 +4181,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.924</v>
+        <v>0.864</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.976</v>
+        <v>0.86</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4206,28 +4197,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0352</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2342900</v>
+        <v>2810300</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.75</v>
+        <v>0.19</v>
       </c>
       <c r="H84" t="n">
-        <v>51.9</v>
+        <v>40.08</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4235,10 +4226,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.864</v>
+        <v>0.757</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.86</v>
+        <v>0.722</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4251,28 +4242,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>0.0519</v>
+        <v>0.0366</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2268300</v>
+        <v>2691600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H85" t="n">
-        <v>51.73</v>
+        <v>43.61</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4280,10 +4271,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3.852</v>
+        <v>2.912</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.664</v>
+        <v>3.019</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4296,28 +4287,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E86" s="9" t="n">
-        <v>0.003</v>
+        <v>0.85</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2263500</v>
+        <v>2665600</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.52</v>
+        <v>0.95</v>
       </c>
       <c r="H86" t="n">
-        <v>49.39</v>
+        <v>17.77</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4325,10 +4316,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>6.755</v>
+        <v>0.924</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>6.83</v>
+        <v>0.976</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4341,28 +4332,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.8</v>
+        <v>1.21</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>0.0191</v>
+        <v>0.0254</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2260600</v>
+        <v>2656000</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H87" t="n">
-        <v>58.44</v>
+        <v>55.6</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4370,10 +4361,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.791</v>
+        <v>1.172</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.77</v>
+        <v>1.134</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4386,28 +4377,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2.84</v>
+        <v>0.6</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.0403</v>
+        <v>0.0169</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2144800</v>
+        <v>2651300</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="H88" t="n">
-        <v>44.27</v>
+        <v>40.82</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4415,10 +4406,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.913</v>
+        <v>0.656</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3.019</v>
+        <v>0.619</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4431,39 +4422,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>-0.0098</v>
+        <v>5.6</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2131200</v>
+        <v>2631900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="H89" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.37</v>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.046</v>
+        <v>5.514</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.073</v>
+        <v>5.398</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,28 +4467,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.82</v>
+        <v>6.75</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.0444</v>
+        <v>0.003</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2091000</v>
+        <v>2621200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="H90" t="n">
-        <v>53.62</v>
+        <v>49.39</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4505,10 +4496,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.792</v>
+        <v>6.755</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.656</v>
+        <v>6.83</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4521,39 +4512,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>5.61</v>
+        <v>3.85</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0.0389</v>
+        <v>0.0519</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2055200</v>
+        <v>2595400</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.55</v>
+        <v>0.92</v>
       </c>
       <c r="H91" t="n">
-        <v>53.59</v>
-      </c>
-      <c r="I91" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.73</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>5.515</v>
+        <v>3.852</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>5.398</v>
+        <v>3.664</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4566,39 +4557,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REACHTEN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.35</v>
+        <v>0.84</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0435</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2006700</v>
+        <v>2537300</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>2.99</v>
+        <v>0.67</v>
       </c>
       <c r="H92" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.6</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.344</v>
+        <v>0.825</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.361</v>
+        <v>0.777</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4611,39 +4602,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>-0.019</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1987900</v>
+        <v>2513400</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.46</v>
+        <v>1.18</v>
       </c>
       <c r="H93" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.589</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.601</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4656,28 +4647,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E94" s="9" t="n">
-        <v>0.0074</v>
+        <v>2.02</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1970900</v>
+        <v>2485600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="H94" t="n">
-        <v>51.55</v>
+        <v>44.04</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4685,10 +4676,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.371</v>
+        <v>2.046</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.343</v>
+        <v>2.073</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4701,39 +4692,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>REACHTEN</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>-0.0423</v>
+        <v>0.35</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1939100</v>
+        <v>2408000</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.13</v>
+        <v>3.59</v>
       </c>
       <c r="H95" t="n">
-        <v>39.53</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.756</v>
+        <v>0.344</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.722</v>
+        <v>0.361</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4755,19 +4746,19 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.0185</v>
+        <v>-0.0236</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1897900</v>
+        <v>2401500</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>31.39</v>
+        <v>30.29</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4775,10 +4766,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6.066</v>
+        <v>6.063</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>6.333</v>
+        <v>6.332</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4791,39 +4782,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1880300</v>
+        <v>2369200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.88</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.1</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.278</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.302</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4836,28 +4827,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.65</v>
+        <v>2.83</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0481</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1852200</v>
+        <v>2281900</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H98" t="n">
-        <v>43.65</v>
+        <v>54.14</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4865,10 +4856,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.793</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>2.656</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4881,28 +4872,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.795</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1826900</v>
+        <v>2274000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="H99" t="n">
-        <v>15.31</v>
+        <v>55.94</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4910,10 +4901,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.952</v>
+        <v>0.791</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.085</v>
+        <v>0.77</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4926,28 +4917,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1826500</v>
+        <v>2261400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.09</v>
+        <v>1.04</v>
       </c>
       <c r="H100" t="n">
-        <v>33.7</v>
+        <v>16.07</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4955,10 +4946,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.237</v>
+        <v>0.954</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.289</v>
+        <v>1.085</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4971,28 +4962,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E101" s="9" t="n">
-        <v>0.0031</v>
+        <v>1.36</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1785400</v>
+        <v>2223400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.29</v>
+        <v>1.15</v>
       </c>
       <c r="H101" t="n">
-        <v>31.28</v>
+        <v>47.38</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5000,10 +4991,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>3.391</v>
+        <v>1.37</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>3.615</v>
+        <v>1.343</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5016,28 +5007,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.775</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>0.0544</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1779400</v>
+        <v>2182700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="H102" t="n">
-        <v>44.22</v>
+        <v>57.86</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5045,10 +5036,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8.664999999999999</v>
+        <v>0.732</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>8.704000000000001</v>
+        <v>0.703</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5061,28 +5052,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.35</v>
+        <v>1.32</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>0.0145</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1762100</v>
+        <v>2156300</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.19</v>
+        <v>0.66</v>
       </c>
       <c r="H103" t="n">
-        <v>50.49</v>
+        <v>53.87</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5090,10 +5081,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.354</v>
+        <v>1.289</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.326</v>
+        <v>1.221</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5106,39 +5097,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>4.66</v>
+        <v>1.43</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0069</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1755800</v>
+        <v>2078800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H104" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.89</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>4.59</v>
+        <v>1.45</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>4.492</v>
+        <v>1.465</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5151,39 +5142,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.3</v>
+        <v>0.65</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0156</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1753100</v>
+        <v>2069600</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
       <c r="H105" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.65</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.215</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.158</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5196,28 +5187,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E106" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.515</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1746300</v>
+        <v>2060900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="H106" t="n">
-        <v>30.1</v>
+        <v>31.96</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5225,10 +5216,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.278</v>
+        <v>0.589</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.302</v>
+        <v>0.601</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5241,39 +5232,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1719700</v>
+        <v>2018100</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.73</v>
+        <v>1.24</v>
       </c>
       <c r="H107" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="I107" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.85</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.388</v>
+        <v>0.911</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.391</v>
+        <v>0.929</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5286,28 +5277,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.705</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1676000</v>
+        <v>1999400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="H108" t="n">
-        <v>56.29</v>
+        <v>41.93</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5315,10 +5306,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.381</v>
+        <v>0.731</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.378</v>
+        <v>0.728</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5331,39 +5322,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E109" s="9" t="n">
-        <v>0.0172</v>
+        <v>8.44</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1668400</v>
+        <v>1911800</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.29</v>
+        <v>0.9</v>
       </c>
       <c r="H109" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="I109" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.22</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>6.137</v>
+        <v>8.664999999999999</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>5.894</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5376,28 +5367,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.032</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1665000</v>
+        <v>1903100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>57.27</v>
+        <v>56.29</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5405,10 +5396,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.732</v>
+        <v>1.251</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.703</v>
+        <v>1.169</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5421,28 +5412,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.29</v>
+        <v>5.07</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>0.032</v>
+        <v>0.004</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1633400</v>
+        <v>1888600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="H111" t="n">
-        <v>56.29</v>
+        <v>51.02</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5450,10 +5441,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.251</v>
+        <v>5.066</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.169</v>
+        <v>5.062</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5466,39 +5457,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.675</v>
+        <v>2.29</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0133</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1626100</v>
+        <v>1856700</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H112" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.5</v>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.731</v>
+        <v>2.214</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.745</v>
+        <v>2.158</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5511,39 +5502,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E113" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.09</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1607300</v>
+        <v>1855000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="H113" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.38</v>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.616</v>
+        <v>2.109</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.605</v>
+        <v>2.099</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5556,28 +5547,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>0.0244</v>
+        <v>0.0145</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1604400</v>
+        <v>1851400</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.04</v>
+        <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>40.04</v>
+        <v>50.49</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5585,10 +5576,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.223</v>
+        <v>0.354</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.232</v>
+        <v>0.326</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5601,28 +5592,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.22</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1561400</v>
+        <v>1832000</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="H115" t="n">
-        <v>41.89</v>
+        <v>33.7</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5630,10 +5621,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.45</v>
+        <v>0.237</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.465</v>
+        <v>0.289</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5646,39 +5637,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.595</v>
+        <v>6.48</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0259</v>
+        <v>0.0157</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1526600</v>
+        <v>1794400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H116" t="n">
-        <v>50.14</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.84</v>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.599</v>
+        <v>6.136</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.585</v>
+        <v>5.893</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5691,28 +5682,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>0.0277</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1514200</v>
+        <v>1764500</v>
       </c>
       <c r="G117" s="5" t="n">
         <v>0.29</v>
       </c>
       <c r="H117" t="n">
-        <v>37.26</v>
+        <v>46.75</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5720,10 +5711,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>2.845</v>
+        <v>2.616</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>2.874</v>
+        <v>2.605</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5736,39 +5727,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E118" s="9" t="n">
-        <v>0.0253</v>
+        <v>4.66</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1501300</v>
+        <v>1757300</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.21</v>
+        <v>0.97</v>
       </c>
       <c r="H118" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.65</v>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.422</v>
+        <v>4.59</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.415</v>
+        <v>4.492</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5781,28 +5772,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>-0.0157</v>
+        <v>1.28</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1451900</v>
+        <v>1725500</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="H119" t="n">
-        <v>45.22</v>
+        <v>27.28</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5810,10 +5801,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.637</v>
+        <v>1.412</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.62</v>
+        <v>1.571</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5826,39 +5817,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>0.395</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1446600</v>
+        <v>1721700</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H120" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.412</v>
+        <v>0.388</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1.571</v>
+        <v>0.391</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5871,28 +5862,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5.1</v>
+        <v>0.675</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0227</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1437800</v>
+        <v>1677100</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="H121" t="n">
-        <v>52.91</v>
+        <v>37.6</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5900,10 +5891,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>5.069</v>
+        <v>0.731</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>5.062</v>
+        <v>0.745</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5916,39 +5907,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.385</v>
+      </c>
+      <c r="E122" s="9" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1433100</v>
+        <v>1676000</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="H122" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.11</v>
+        <v>0.381</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.099</v>
+        <v>0.378</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5970,19 +5961,19 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>0.0253</v>
+        <v>0.0397</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1383900</v>
+        <v>1667900</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H123" t="n">
-        <v>57.59</v>
+        <v>58.83</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5990,10 +5981,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.77</v>
+        <v>2.774</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2.184</v>
+        <v>2.185</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6006,39 +5997,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>3.09</v>
+        <v>2.59</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0237</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1376800</v>
+        <v>1637900</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.43</v>
+        <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.68</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.8</v>
+        <v>2.844</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.406</v>
+        <v>2.874</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6051,28 +6042,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>-0.0139</v>
+        <v>0.215</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1371200</v>
+        <v>1631400</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="H125" t="n">
-        <v>43.12</v>
+        <v>43.53</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6080,10 +6071,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.732</v>
+        <v>0.224</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.728</v>
+        <v>0.232</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6096,39 +6087,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0053</v>
+        <v>0.225</v>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1361500</v>
+        <v>1568400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>26.87</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.974</v>
+        <v>0.198</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.056</v>
+        <v>0.187</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6141,28 +6132,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E127" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1317900</v>
+        <v>1558000</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="H127" t="n">
-        <v>50.02</v>
+        <v>27.9</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6170,10 +6161,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.217</v>
+        <v>0.975</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.209</v>
+        <v>1.056</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6186,28 +6177,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.465</v>
+        <v>0.595</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0259</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1296400</v>
+        <v>1533500</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H128" t="n">
-        <v>30.99</v>
+        <v>50.14</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6215,10 +6206,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.502</v>
+        <v>0.599</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.585</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6231,39 +6222,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.0385</v>
+        <v>0.41</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>0.038</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1289800</v>
+        <v>1505300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1.65</v>
+        <v>0.21</v>
       </c>
       <c r="H129" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.22</v>
+        <v>0.423</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.209</v>
+        <v>0.415</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6276,28 +6267,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E130" s="9" t="n">
-        <v>0.027</v>
+        <v>0.635</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1263100</v>
+        <v>1482500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
       <c r="H130" t="n">
-        <v>56.41</v>
+        <v>50.91</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6305,10 +6296,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.111</v>
+        <v>0.637</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.879</v>
+        <v>0.621</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6321,39 +6312,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E131" s="8" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>0.036</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1255000</v>
+        <v>1429100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H131" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.09</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.336</v>
+        <v>1.112</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.343</v>
+        <v>0.879</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6366,28 +6357,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E132" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.405</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1164500</v>
+        <v>1417300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="H132" t="n">
-        <v>44.4</v>
+        <v>35.96</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6395,10 +6386,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.275</v>
+        <v>0.417</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.296</v>
+        <v>0.435</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,39 +6402,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>0.0492</v>
+        <v>0.0098</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1154800</v>
+        <v>1384000</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="H133" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.37</v>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.285</v>
+        <v>2.801</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.22</v>
+        <v>2.406</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6456,28 +6447,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.33</v>
+        <v>0.215</v>
       </c>
       <c r="E134" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.0488</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1151000</v>
+        <v>1357900</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="H134" t="n">
-        <v>77.73999999999999</v>
+        <v>50.02</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6485,10 +6476,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.269</v>
+        <v>0.217</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.217</v>
+        <v>0.209</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6501,28 +6492,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.305</v>
+        <v>2.75</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>0.0339</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1137700</v>
+        <v>1341300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="H135" t="n">
-        <v>42.53</v>
+        <v>57.25</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6530,10 +6521,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.318</v>
+        <v>2.666</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.338</v>
+        <v>2.241</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6546,39 +6537,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.44</v>
+        <v>10.7</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0368</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1099900</v>
+        <v>1340200</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="H136" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.6</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.388</v>
+        <v>10.417</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.359</v>
+        <v>9.731</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,28 +6582,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.77</v>
+        <v>0.465</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.022</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1099800</v>
+        <v>1298400</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H137" t="n">
-        <v>54.2</v>
+        <v>30.99</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6620,10 +6611,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.765</v>
+        <v>0.502</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,39 +6627,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E138" s="9" t="n">
-        <v>0.0111</v>
+        <v>0.25</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1099700</v>
+        <v>1289800</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="H138" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.915</v>
+        <v>0.22</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.869</v>
+        <v>0.209</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,39 +6672,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>7.32</v>
+        <v>0.34</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0149</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1087500</v>
+        <v>1287500</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H139" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.75</v>
+      </c>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>7.359</v>
+        <v>0.336</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>6.882</v>
+        <v>0.343</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6726,28 +6717,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>-0.006</v>
+        <v>2.39</v>
+      </c>
+      <c r="E140" s="9" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1074800</v>
+        <v>1270200</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.72</v>
+        <v>0.1</v>
       </c>
       <c r="H140" t="n">
-        <v>36.21</v>
+        <v>43.29</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6755,10 +6746,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.848</v>
+        <v>2.448</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.862</v>
+        <v>2.379</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,28 +6762,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.235</v>
+        <v>0.74</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>0.0217</v>
+        <v>0.035</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1072000</v>
+        <v>1259200</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="H141" t="n">
-        <v>44.67</v>
+        <v>52.39</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6800,10 +6791,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.247</v>
+        <v>0.741</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.255</v>
+        <v>0.673</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,39 +6807,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.69</v>
+        <v>1.29</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1048100</v>
+        <v>1217500</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H142" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I142" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.66</v>
+        <v>1.259</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.24</v>
+        <v>1.279</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,28 +6852,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>10.74</v>
+        <v>0.305</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>0.0407</v>
+        <v>0.0339</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1041700</v>
+        <v>1211700</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H143" t="n">
-        <v>59.17</v>
+        <v>42.53</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6890,10 +6881,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>10.421</v>
+        <v>0.318</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>9.731999999999999</v>
+        <v>0.338</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,28 +6897,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E144" s="8" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E144" s="9" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1026200</v>
+        <v>1209300</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H144" t="n">
-        <v>41.54</v>
+        <v>53.32</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6935,10 +6926,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.272</v>
+        <v>0.917</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.276</v>
+        <v>0.87</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6942,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E145" s="9" t="n">
-        <v>0.0042</v>
+        <v>0.825</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1022000</v>
+        <v>1200800</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="H145" t="n">
-        <v>43.29</v>
+        <v>36.21</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6971,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.448</v>
+        <v>0.848</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.379</v>
+        <v>0.862</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,28 +6987,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.885</v>
+        <v>7.33</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0209</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1021000</v>
+        <v>1188200</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
       <c r="H146" t="n">
-        <v>36.85</v>
+        <v>52.03</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7025,10 +7016,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.911</v>
+        <v>7.36</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.929</v>
+        <v>6.882</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,28 +7032,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>13</v>
+        <v>0.44</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>0.0015</v>
+        <v>0.0233</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1020000</v>
+        <v>1182600</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H147" t="n">
-        <v>45.18</v>
+        <v>61.95</v>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
@@ -7070,10 +7061,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>13.019</v>
+        <v>0.388</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>13.443</v>
+        <v>0.359</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,39 +7077,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.555</v>
+        <v>0.265</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.0392</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1018500</v>
+        <v>1173500</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.89</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="I148" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.57</v>
+        <v>0.275</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.613</v>
+        <v>0.296</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,39 +7122,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.02</v>
+        <v>0.33</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0476</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1010600</v>
+        <v>1161200</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1.43</v>
+        <v>0.84</v>
       </c>
       <c r="H149" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I149" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>77.73999999999999</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.002</v>
+        <v>0.269</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.983</v>
+        <v>0.217</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,39 +7167,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E150" s="9" t="n">
-        <v>0.0177</v>
+        <v>12.98</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>947400</v>
+        <v>1158500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H150" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.06</v>
+      </c>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>13.017</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.513</v>
+        <v>13.443</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,28 +7212,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.735</v>
+        <v>0.765</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>943900</v>
+        <v>1132600</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H151" t="n">
-        <v>51.61</v>
+        <v>53.42</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7250,10 +7241,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.741</v>
+        <v>0.764</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7257,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>0.029</v>
+        <v>0.0304</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>924500</v>
+        <v>1128300</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H152" t="n">
-        <v>52.91</v>
+        <v>53.27</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7286,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.115</v>
+        <v>3.027</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.989</v>
+        <v>2.851</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,28 +7302,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.615</v>
+        <v>2.15</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>0.0513</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>924100</v>
+        <v>1123900</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>12.15</v>
+        <v>0.51</v>
       </c>
       <c r="H153" t="n">
-        <v>74.33</v>
+        <v>57.18</v>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
@@ -7340,10 +7331,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.545</v>
+        <v>2.109</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.542</v>
+        <v>2.059</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,39 +7347,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.15</v>
+        <v>0.24</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>919800</v>
+        <v>1072300</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H154" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I154" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.109</v>
+        <v>0.247</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.059</v>
+        <v>0.256</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,39 +7392,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.62</v>
+        <v>0.235</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0208</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>857100</v>
+        <v>1049300</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="H155" t="n">
-        <v>61.66</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.466</v>
+        <v>0.243</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,39 +7437,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>PWF</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E156" s="9" t="n">
-        <v>0.0327</v>
+        <v>0.75</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>831100</v>
+        <v>1040800</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.36</v>
+        <v>17.07</v>
       </c>
       <c r="H156" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.777</v>
+        <v>0.735</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.768</v>
+        <v>0.741</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7491,28 +7482,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E157" s="9" t="n">
-        <v>0.027</v>
+        <v>4.5</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>828900</v>
+        <v>1032100</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="H157" t="n">
-        <v>52.85</v>
+        <v>37.98</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7520,10 +7511,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>3.026</v>
+        <v>4.632</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>2.851</v>
+        <v>4.639</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7536,28 +7527,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E158" s="9" t="n">
-        <v>0.0404</v>
+        <v>0.27</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>796600</v>
+        <v>1026200</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.17</v>
+        <v>0.92</v>
       </c>
       <c r="H158" t="n">
-        <v>50.63</v>
+        <v>41.54</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7565,10 +7556,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.048</v>
+        <v>0.272</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.276</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7581,39 +7572,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>4.2</v>
+        <v>0.55</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>790000</v>
+        <v>1021000</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="H159" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.11</v>
+      </c>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>4.299</v>
+        <v>0.569</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>4.334</v>
+        <v>0.613</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7626,28 +7617,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.29</v>
+        <v>0.79</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>0.032</v>
+        <v>0.0327</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>788500</v>
+        <v>1019400</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H160" t="n">
-        <v>46.58</v>
+        <v>53.5</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7655,10 +7646,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1.33</v>
+        <v>0.777</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1.278</v>
+        <v>0.768</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7671,28 +7662,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>755500</v>
+        <v>1010600</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="H161" t="n">
-        <v>56.29</v>
+        <v>59.5</v>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
@@ -7700,10 +7691,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.259</v>
+        <v>1.002</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1.279</v>
+        <v>0.983</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7716,39 +7707,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.76</v>
+        <v>1.3</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.04</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>735800</v>
+        <v>1006600</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>12.07</v>
+        <v>0.42</v>
       </c>
       <c r="H162" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="I162" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.736</v>
+        <v>1.331</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0.741</v>
+        <v>1.279</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7761,39 +7752,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>-0.0062</v>
+        <v>2.13</v>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>0.029</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>707200</v>
+        <v>986300</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="H163" t="n">
-        <v>76.38</v>
-      </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.91</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.727</v>
+        <v>2.115</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.645</v>
+        <v>1.989</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7806,28 +7797,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E164" s="8" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E164" s="9" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>703100</v>
+        <v>948100</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H164" t="n">
-        <v>39.49</v>
+        <v>56.23</v>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
@@ -7835,10 +7826,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.734</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1.769</v>
+        <v>0.513</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7851,39 +7842,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E165" s="8" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>0.05980000000000001</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>698700</v>
+        <v>946100</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.23</v>
+        <v>12.44</v>
       </c>
       <c r="H165" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.11</v>
+      </c>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.903</v>
+        <v>0.546</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.956</v>
+        <v>0.542</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7896,28 +7887,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E166" s="8" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>694200</v>
+        <v>945100</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H166" t="n">
-        <v>49.36</v>
+        <v>62.52</v>
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
@@ -7925,10 +7916,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.245</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1.059</v>
+        <v>0.467</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7941,28 +7932,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>685400</v>
+        <v>924500</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="H167" t="n">
-        <v>37.33</v>
+        <v>45.79</v>
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
@@ -7970,10 +7961,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>1.781</v>
+        <v>4.299</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>1.895</v>
+        <v>4.334</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7986,28 +7977,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0.515</v>
+        <v>1.03</v>
       </c>
       <c r="E168" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0404</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>684300</v>
+        <v>832700</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.61</v>
+        <v>0.18</v>
       </c>
       <c r="H168" t="n">
-        <v>48.2</v>
+        <v>50.63</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8015,10 +8006,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.525</v>
+        <v>1.048</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.506</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8031,28 +8022,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>2.11</v>
+        <v>0.875</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>0.0498</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>679500</v>
+        <v>827800</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H169" t="n">
-        <v>41.59</v>
+        <v>36.65</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8060,10 +8051,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>2.209</v>
+        <v>0.903</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>2.233</v>
+        <v>0.956</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8076,28 +8067,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>0</v>
+        <v>1.68</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>0.006</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>661000</v>
+        <v>826300</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.64</v>
+        <v>0.17</v>
       </c>
       <c r="H170" t="n">
-        <v>39.92</v>
+        <v>41.09</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8105,10 +8096,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>2.859</v>
+        <v>1.734</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>2.859</v>
+        <v>1.769</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8121,28 +8112,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E171" s="9" t="n">
-        <v>0.0288</v>
+        <v>2.72</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>660900</v>
+        <v>815500</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H171" t="n">
-        <v>35.26</v>
+        <v>43.88</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8150,10 +8141,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.212</v>
+        <v>2.756</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1.297</v>
+        <v>2.765</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8166,28 +8157,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.2</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>646600</v>
+        <v>807500</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H172" t="n">
-        <v>35.15</v>
+        <v>49.36</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8195,10 +8186,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.631</v>
+        <v>1.245</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0.631</v>
+        <v>1.059</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8211,28 +8202,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E173" s="9" t="n">
-        <v>0.0188</v>
+        <v>7.5</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>615000</v>
+        <v>745100</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="H173" t="n">
-        <v>48.47</v>
+        <v>45.72</v>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
@@ -8240,10 +8231,10 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>4.353</v>
+        <v>7.587</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>4.432</v>
+        <v>7.78</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8256,28 +8247,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>-0.0123</v>
+        <v>-0.0124</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>602200</v>
+        <v>732800</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H174" t="n">
-        <v>34.6</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I174" s="10" t="inlineStr">
         <is>
@@ -8285,10 +8276,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.843</v>
+        <v>0.726</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0.904</v>
+        <v>0.644</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8301,39 +8292,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>-0.0039</v>
+        <v>2.12</v>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>0.0547</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>556000</v>
+        <v>709900</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="H175" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="I175" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.44</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.566</v>
+        <v>2.21</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.695</v>
+        <v>2.233</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8346,39 +8337,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.59</v>
+        <v>0.625</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>-0.0484</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>539700</v>
+        <v>709600</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H176" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="I176" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.57</v>
+        <v>0.631</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.525</v>
+        <v>0.631</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8400,19 +8391,19 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E177" s="8" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>531900</v>
+        <v>709100</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="H177" t="n">
-        <v>34.52</v>
+        <v>33.35</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8420,7 +8411,7 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.95</v>
+        <v>0.949</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>1.005</v>
@@ -8436,39 +8427,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E178" s="9" t="n">
-        <v>0.0034</v>
+        <v>1.71</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>524800</v>
+        <v>708900</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.7</v>
+        <v>0.11</v>
       </c>
       <c r="H178" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I178" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.52</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1.509</v>
+        <v>1.78</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1.501</v>
+        <v>1.895</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8481,28 +8472,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.51</v>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>520300</v>
+        <v>687300</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="n">
-        <v>40.28</v>
+        <v>46.48</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8510,10 +8501,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>2.753</v>
+        <v>0.524</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>2.764</v>
+        <v>0.506</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8526,28 +8517,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>-0.012</v>
+        <v>1.07</v>
+      </c>
+      <c r="E180" s="9" t="n">
+        <v>0.0288</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>511300</v>
+        <v>675200</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H180" t="n">
-        <v>44.06</v>
+        <v>35.26</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8555,10 +8546,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>3.423</v>
+        <v>1.212</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>3.16</v>
+        <v>1.297</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8571,39 +8562,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E181" s="8" t="n">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>510500</v>
+        <v>673900</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.17</v>
+        <v>0.66</v>
       </c>
       <c r="H181" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="I181" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.22</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>7.587</v>
+        <v>2.859</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>7.78</v>
+        <v>2.859</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8616,39 +8607,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>-0.0126</v>
+        <v>1.49</v>
+      </c>
+      <c r="E182" s="9" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>509300</v>
+        <v>671000</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="H182" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.8</v>
+      </c>
+      <c r="I182" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>3.176</v>
+        <v>1.509</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>2.857</v>
+        <v>1.501</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8661,45 +8652,585 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>2.56</v>
+        <v>4.33</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>0.0364</v>
+        <v>0.0164</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>508400</v>
+        <v>656100</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H183" t="n">
-        <v>55.04</v>
-      </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.09</v>
+      </c>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>2.528</v>
+        <v>4.352</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>2.236</v>
+        <v>4.432</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>652800</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H184" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="I184" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>631700</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H185" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="I185" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>622100</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H186" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>616200</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H187" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="I187" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E188" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>598300</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H188" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="I188" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>596000</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H189" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>3.424</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>595600</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H190" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>2.858</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E191" s="9" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>540700</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H191" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>540300</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H192" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E193" s="9" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>534100</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H193" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E194" s="9" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>513300</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H194" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>3.154</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E195" s="9" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>508700</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H195" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M183"/>
+  <autoFilter ref="A1:M195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
+++ b/docs/downloads/2026-10-16/bursa-report-2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-16'!$A$1:$M$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M195"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.1538</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>209740900</v>
+        <v>213718300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>23.66</v>
+        <v>23.14</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>62942400</v>
+        <v>63022600</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -639,10 +639,10 @@
         <v>0.0455</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>41073600</v>
+        <v>42439100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>69.7</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.91</v>
+        <v>0.905</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.0111</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>39650800</v>
+        <v>41334100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H5" t="n">
-        <v>67.28</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.822</v>
+        <v>0.821</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -729,10 +729,10 @@
         <v>-0.0235</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>29707300</v>
+        <v>30834200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="H6" t="n">
         <v>71.84999999999999</v>
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0214</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24115900</v>
+        <v>24208700</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1.63</v>
       </c>
       <c r="H7" t="n">
-        <v>37.41</v>
+        <v>37.73</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.552</v>
+        <v>7.553</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>7.699</v>
+        <v>7.7</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>-0.0278</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>21476400</v>
+        <v>21504500</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.92</v>
@@ -864,7 +864,7 @@
         <v>0.125</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>21258500</v>
+        <v>21258800</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>33.76</v>
@@ -939,28 +939,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TECHBASE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>18080800</v>
+        <v>18902100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.72</v>
+        <v>17.56</v>
       </c>
       <c r="H11" t="n">
-        <v>77.59999999999999</v>
+        <v>68.44</v>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.611</v>
+        <v>0.059</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.526</v>
+        <v>0.057</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TECHBASE</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>6.5</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.0934</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>17395100</v>
+        <v>18168500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>16.16</v>
+        <v>2.35</v>
       </c>
       <c r="H12" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.53</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.059</v>
+        <v>7.265</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.057</v>
+        <v>7.638</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.155</v>
+        <v>0.675</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17060300</v>
+        <v>18168100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.155</v>
+        <v>0.611</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.157</v>
+        <v>0.526</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.31</v>
+        <v>0.155</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16747400</v>
+        <v>17060300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.309</v>
+        <v>0.155</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.299</v>
+        <v>0.157</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,39 +1119,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.0711</v>
+        <v>0.31</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>16646000</v>
+        <v>16747400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.15</v>
+        <v>0.88</v>
       </c>
       <c r="H15" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.55</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.28</v>
+        <v>0.309</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>7.641</v>
+        <v>0.299</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         <v>0.015</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>16171400</v>
+        <v>16210100</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0.53</v>
@@ -1224,10 +1224,10 @@
         <v>0.0225</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>15767600</v>
+        <v>16081100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="H17" t="n">
         <v>41.76</v>
@@ -1269,7 +1269,7 @@
         <v>-0.0333</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>15722100</v>
+        <v>15805800</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0.22</v>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>15048900</v>
+        <v>15060400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H19" t="n">
         <v>52.75</v>
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1818</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>14362800</v>
+        <v>14363900</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>263.32</v>
+        <v>263.34</v>
       </c>
       <c r="H20" t="n">
-        <v>69.25</v>
+        <v>57.82</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>0.057</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>12982200</v>
+        <v>13252500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H21" t="n">
         <v>50.17</v>
@@ -1449,10 +1449,10 @@
         <v>0.05</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>12828200</v>
+        <v>12990200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H22" t="n">
         <v>60.39</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0196</v>
+        <v>-0.0392</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>12371400</v>
+        <v>12435900</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0.47</v>
@@ -1571,19 +1571,19 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0148</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10947200</v>
+        <v>11101100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H25" t="n">
-        <v>56.68</v>
+        <v>55.89</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.729</v>
+        <v>4.728</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>4.856</v>
@@ -1622,7 +1622,7 @@
         <v>0.0397</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10578800</v>
+        <v>10941500</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0.1</v>
@@ -1645,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.46</v>
+        <v>0.375</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.0455</v>
+        <v>0.1194</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10569700</v>
+        <v>10628100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.52</v>
+        <v>1.93</v>
       </c>
       <c r="H27" t="n">
-        <v>61.88</v>
+        <v>66.2</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
@@ -1674,11 +1674,9 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0.364</v>
-      </c>
+        <v>0.315</v>
+      </c>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
     </row>
@@ -1690,28 +1688,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.375</v>
+        <v>0.455</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1194</v>
+        <v>0.0341</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10548700</v>
+        <v>10598000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.91</v>
+        <v>0.52</v>
       </c>
       <c r="H28" t="n">
-        <v>66.2</v>
+        <v>60.99</v>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
@@ -1719,9 +1717,11 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="K28" s="2" t="n"/>
+        <v>0.423</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.364</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1733,28 +1733,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.0526</v>
+        <v>4.79</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9652900</v>
+        <v>9989500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
-        <v>53.87</v>
+        <v>45.39</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.389</v>
+        <v>4.908</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.378</v>
+        <v>4.72</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.15</v>
+        <v>0.405</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1675</v>
+        <v>0.0658</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9639600</v>
+        <v>9672500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6.69</v>
+        <v>0.77</v>
       </c>
       <c r="H30" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.095</v>
+        <v>0.39</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.097</v>
+        <v>0.378</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1823,28 +1823,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.38</v>
+        <v>1.14</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.1574</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9189400</v>
+        <v>9650500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.28</v>
+        <v>6.7</v>
       </c>
       <c r="H31" t="n">
-        <v>60.05</v>
+        <v>55.07</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.371</v>
+        <v>1.094</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.369</v>
+        <v>1.097</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1868,28 +1868,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-0.0417</v>
+        <v>0.375</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9003000</v>
+        <v>9307400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>3.33</v>
+        <v>1.3</v>
       </c>
       <c r="H32" t="n">
-        <v>69.55</v>
+        <v>55.91</v>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.092</v>
+        <v>0.371</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.092</v>
+        <v>0.369</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         <v>-0.0222</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8937900</v>
+        <v>9131500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H33" t="n">
         <v>45.22</v>
@@ -1958,39 +1958,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.0103</v>
+        <v>0.12</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8913800</v>
+        <v>9088000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.35</v>
+        <v>3.36</v>
       </c>
       <c r="H34" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.909</v>
+        <v>0.093</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.721</v>
+        <v>0.092</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         <v>-0.2</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8416600</v>
+        <v>8418600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>42.83</v>
+        <v>42.84</v>
       </c>
       <c r="H35" t="n">
         <v>43.23</v>
@@ -2063,10 +2063,10 @@
         <v>-0.0089</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6930600</v>
+        <v>7052700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H36" t="n">
         <v>46.4</v>
@@ -2108,7 +2108,7 @@
         <v>-0.0108</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6905400</v>
+        <v>6905700</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0.22</v>
@@ -2138,28 +2138,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.34</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.0561</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6269300</v>
+        <v>6760300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H38" t="n">
-        <v>49.14</v>
+        <v>49.68</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.347</v>
+        <v>0.577</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.333</v>
+        <v>0.539</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         <v>0.0069</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6226000</v>
+        <v>6360800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="n">
         <v>23.66</v>
@@ -2243,10 +2243,10 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6147400</v>
+        <v>6287000</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="H40" t="n">
         <v>38.01</v>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.0467</v>
+        <v>0.0303</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5918300</v>
+        <v>6269300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="H41" t="n">
-        <v>48.82</v>
+        <v>49.14</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.576</v>
+        <v>0.347</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.539</v>
+        <v>0.333</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         <v>0.008399999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5874200</v>
+        <v>5927200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>38.15</v>
@@ -2378,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5651900</v>
+        <v>5770200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H43" t="n">
         <v>22.54</v>
@@ -2417,19 +2417,19 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-0.0104</v>
+        <v>0.48</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5630000</v>
+        <v>5661100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H44" t="n">
-        <v>36.81</v>
+        <v>38.06</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5391100</v>
+        <v>5441100</v>
       </c>
       <c r="G46" s="5" t="n"/>
       <c r="I46" s="6" t="inlineStr">
@@ -2534,39 +2534,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>0.19</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5061300</v>
+        <v>5175900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.28</v>
+        <v>0.96</v>
       </c>
       <c r="H47" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.38</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.097</v>
+        <v>0.165</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.166</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2579,39 +2579,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0.0389</v>
+        <v>0.1</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4823000</v>
+        <v>5061300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.25</v>
+        <v>1.28</v>
       </c>
       <c r="H48" t="n">
-        <v>52.68</v>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.28</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.651</v>
+        <v>0.097</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.55</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2624,28 +2624,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.19</v>
+        <v>2.66</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>0.0857</v>
+        <v>0.035</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4644800</v>
+        <v>4835700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.86</v>
+        <v>0.26</v>
       </c>
       <c r="H49" t="n">
-        <v>67.38</v>
+        <v>52.13</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.165</v>
+        <v>2.65</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.166</v>
+        <v>2.55</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2669,28 +2669,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.07139999999999999</v>
+        <v>0.745</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4453400</v>
+        <v>4542800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="H50" t="n">
-        <v>57.1</v>
+        <v>41.25</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.126</v>
+        <v>0.773</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.1</v>
+        <v>0.772</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2714,28 +2714,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4407800</v>
+        <v>4536000</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="H51" t="n">
-        <v>41.25</v>
+        <v>31.28</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.773</v>
+        <v>0.158</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.772</v>
+        <v>0.19</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2759,39 +2759,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.07139999999999999</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>4504400</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H52" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="K52" s="2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0.0526</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>4351700</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H52" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>0.121</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2804,28 +2804,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0.0183</v>
+        <v>1.72</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4287400</v>
+        <v>4412500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.44</v>
+        <v>1.36</v>
       </c>
       <c r="H53" t="n">
-        <v>55.47</v>
+        <v>27.12</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.078</v>
+        <v>1.831</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.044</v>
+        <v>1.971</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2849,28 +2849,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3.73</v>
+        <v>0.1</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0027</v>
+        <v>0.0526</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4272400</v>
+        <v>4351800</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="H54" t="n">
-        <v>56.12</v>
+        <v>36.27</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.633</v>
+        <v>0.11</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.962</v>
+        <v>0.121</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2894,28 +2894,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E55" s="9" t="n">
-        <v>0.0214</v>
+        <v>3.72</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4236700</v>
+        <v>4334300</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H55" t="n">
-        <v>48.06</v>
+        <v>55.88</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.951</v>
+        <v>3.632</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3.537</v>
+        <v>2.962</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2939,39 +2939,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>4301400</v>
+      </c>
+      <c r="G56" s="5" t="n">
         <v>0.44</v>
       </c>
-      <c r="E56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>4183100</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>4.69</v>
-      </c>
       <c r="H56" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.47</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.439</v>
+        <v>1.078</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.439</v>
+        <v>1.044</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2984,28 +2984,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.29</v>
+        <v>3.81</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.0187</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>4076900</v>
+        <v>4270900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H57" t="n">
-        <v>25.38</v>
+        <v>47.71</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.339</v>
+        <v>3.95</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.374</v>
+        <v>3.536</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3029,28 +3029,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.44</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>4056100</v>
+        <v>4186600</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1.29</v>
+        <v>4.7</v>
       </c>
       <c r="H58" t="n">
-        <v>70.15000000000001</v>
+        <v>54.33</v>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.616</v>
+        <v>0.439</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.604</v>
+        <v>0.439</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3074,28 +3074,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-0.017</v>
+        <v>0.29</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>4001200</v>
+        <v>4131000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="H59" t="n">
-        <v>27.95</v>
+        <v>25.38</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.832</v>
+        <v>0.339</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.971</v>
+        <v>0.374</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3119,39 +3119,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.625</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3843600</v>
+        <v>4056100</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.41</v>
+        <v>1.29</v>
       </c>
       <c r="H60" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.305</v>
+        <v>0.616</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.314</v>
+        <v>0.604</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3164,28 +3164,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0.0062</v>
+        <v>1.26</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3828900</v>
+        <v>3962500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="H61" t="n">
-        <v>32.54</v>
+        <v>42.44</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3.392</v>
+        <v>1.304</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3.616</v>
+        <v>1.313</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         <v>-0.006</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3804700</v>
+        <v>3877500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H62" t="n">
         <v>53.01</v>
@@ -3254,28 +3254,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.895</v>
+        <v>3.26</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>0.0529</v>
+        <v>0.0062</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3787700</v>
+        <v>3847300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="H63" t="n">
-        <v>46.48</v>
+        <v>32.54</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.9340000000000001</v>
+        <v>3.392</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.844</v>
+        <v>3.616</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3299,39 +3299,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.27</v>
+        <v>0.89</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.0242</v>
+        <v>0.0471</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3773800</v>
+        <v>3829200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H64" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.75</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.189</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.184</v>
+        <v>0.844</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3344,39 +3344,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>-0.0169</v>
+        <v>1.27</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3752500</v>
+        <v>3793000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.21</v>
+        <v>0.6</v>
       </c>
       <c r="H65" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.53</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.295</v>
+        <v>1.189</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.295</v>
+        <v>1.184</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3389,39 +3389,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.125</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3733400</v>
+        <v>3768600</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1.48</v>
+        <v>0.16</v>
       </c>
       <c r="H66" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.74</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.646</v>
+        <v>0.146</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.552</v>
+        <v>0.148</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.0169</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3621500</v>
+        <v>3752500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>6.58</v>
+        <v>1.21</v>
       </c>
       <c r="H67" t="n">
-        <v>31.74</v>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.48</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.104</v>
+        <v>0.295</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.126</v>
+        <v>0.295</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3479,39 +3479,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.02</v>
+        <v>0.695</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.0408</v>
+        <v>0.0296</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3529600</v>
+        <v>3735400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.43</v>
+        <v>1.48</v>
       </c>
       <c r="H68" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.056</v>
+        <v>0.646</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.953</v>
+        <v>0.552</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3524,39 +3524,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>WELLCHIP</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E69" s="9" t="n">
-        <v>0.0303</v>
+        <v>1.04</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3497200</v>
+        <v>3670200</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.49</v>
+        <v>6.67</v>
       </c>
       <c r="H69" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.74</v>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.179</v>
+        <v>1.104</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.197</v>
+        <v>1.126</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3569,28 +3569,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.525</v>
+        <v>1.01</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3467400</v>
+        <v>3630500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="H70" t="n">
-        <v>53.48</v>
+        <v>46.04</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.52</v>
+        <v>1.055</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.457</v>
+        <v>0.953</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3614,39 +3614,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>-0.0256</v>
+        <v>0.17</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3397400</v>
+        <v>3508800</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H71" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.69</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.925</v>
+        <v>0.179</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.952</v>
+        <v>0.197</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3659,39 +3659,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0062</v>
+        <v>0.525</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3394500</v>
+        <v>3489800</v>
       </c>
       <c r="G72" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H72" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="H72" t="n">
-        <v>44.58</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>6.415</v>
-      </c>
       <c r="K72" s="2" t="n">
-        <v>6.776</v>
+        <v>0.457</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3704,38 +3704,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.425</v>
+        <v>1.9</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>-0.023</v>
+        <v>-0.0256</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3387200</v>
+        <v>3424200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H73" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.5</v>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K73" s="2" t="n"/>
+        <v>1.925</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1.952</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
     </row>
@@ -3747,28 +3749,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0</v>
+        <v>6.37</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3372600</v>
+        <v>3411800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="H74" t="n">
-        <v>33.84</v>
+        <v>44.1</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3776,10 +3778,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.397</v>
+        <v>6.414</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.407</v>
+        <v>6.776</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3792,28 +3794,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>0.0069</v>
+        <v>0.425</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3340700</v>
+        <v>3393200</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="H75" t="n">
-        <v>35.99</v>
+        <v>19.3</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3821,11 +3823,9 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>7.482</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>7.978</v>
-      </c>
+        <v>0.464</v>
+      </c>
+      <c r="K75" s="2" t="n"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
     </row>
@@ -3837,28 +3837,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.125</v>
+        <v>0.39</v>
       </c>
       <c r="E76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3295400</v>
+        <v>3372600</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H76" t="n">
-        <v>36.74</v>
+        <v>33.84</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.146</v>
+        <v>0.397</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.148</v>
+        <v>0.407</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3882,28 +3882,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0</v>
+        <v>7.33</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>3130900</v>
+        <v>3359500</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H77" t="n">
-        <v>44.87</v>
+        <v>35.99</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.778</v>
+        <v>7.482</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.735</v>
+        <v>7.978</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         <v>0.009899999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>3122800</v>
+        <v>3240500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H78" t="n">
         <v>36.49</v>
@@ -3972,39 +3972,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0.098</v>
+        <v>2.7</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3078600</v>
+        <v>3187800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="H79" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.12</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.499</v>
+        <v>2.777</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.464</v>
+        <v>2.734</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4017,28 +4017,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.0092</v>
+        <v>0.555</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.0882</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2964100</v>
+        <v>3160400</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>73.06999999999999</v>
+        <v>64.83</v>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.824</v>
+        <v>0.499</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4062,39 +4062,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2960500</v>
+        <v>2997200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="H81" t="n">
-        <v>61.74</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.06999999999999</v>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.919</v>
+        <v>0.824</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.874</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4107,25 +4107,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2929000</v>
+        <v>2995200</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H82" t="n">
         <v>58.07</v>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.048</v>
+        <v>0.918</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.904</v>
+        <v>0.873</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4152,28 +4152,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.865</v>
+        <v>1.11</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.0673</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2842900</v>
+        <v>2934800</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>51.9</v>
+        <v>58.81</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.864</v>
+        <v>1.049</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.86</v>
+        <v>0.905</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4197,28 +4197,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0352</v>
+        <v>0.595</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2810300</v>
+        <v>2872100</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="H84" t="n">
-        <v>40.08</v>
+        <v>39.79</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.757</v>
+        <v>0.656</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.722</v>
+        <v>0.619</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4242,28 +4242,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2.83</v>
+        <v>0.865</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>0.0366</v>
+        <v>0.0058</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2691600</v>
+        <v>2842900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="H85" t="n">
-        <v>43.61</v>
+        <v>51.9</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.912</v>
+        <v>0.864</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.019</v>
+        <v>0.86</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4287,28 +4287,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.85</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.0058</v>
+        <v>-0.0352</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2665600</v>
+        <v>2820300</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.95</v>
+        <v>0.19</v>
       </c>
       <c r="H86" t="n">
-        <v>17.77</v>
+        <v>40.08</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.924</v>
+        <v>0.757</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.976</v>
+        <v>0.722</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4332,28 +4332,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E87" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.85</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2656000</v>
+        <v>2738300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.36</v>
+        <v>0.98</v>
       </c>
       <c r="H87" t="n">
-        <v>55.6</v>
+        <v>17.77</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.172</v>
+        <v>0.924</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.134</v>
+        <v>0.976</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4377,28 +4377,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.6</v>
+        <v>2.83</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0366</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2651300</v>
+        <v>2704900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.29</v>
+        <v>0.74</v>
       </c>
       <c r="H88" t="n">
-        <v>40.82</v>
+        <v>43.61</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.656</v>
+        <v>2.912</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.619</v>
+        <v>3.019</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4422,39 +4422,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0519</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2631900</v>
+        <v>2672000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.73</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>5.514</v>
+        <v>3.852</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>5.398</v>
+        <v>3.664</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4476,19 +4476,19 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6.75</v>
+        <v>6.77</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.003</v>
+        <v>0.0059</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2621200</v>
+        <v>2669700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H90" t="n">
-        <v>49.39</v>
+        <v>50.77</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>6.755</v>
+        <v>6.757</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>6.83</v>
@@ -4512,28 +4512,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>3.85</v>
+        <v>1.2</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>0.0519</v>
+        <v>0.0169</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2595400</v>
+        <v>2658600</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.92</v>
+        <v>0.36</v>
       </c>
       <c r="H91" t="n">
-        <v>51.73</v>
+        <v>54.56</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>3.852</v>
+        <v>1.171</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3.664</v>
+        <v>1.133</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4557,39 +4557,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.84</v>
+        <v>5.6</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.0435</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2537300</v>
+        <v>2652500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H92" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.37</v>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.825</v>
+        <v>5.514</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.777</v>
+        <v>5.398</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4602,39 +4602,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2513400</v>
+        <v>2594700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H93" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.04</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.046</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.073</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4647,28 +4647,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0.84</v>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2485600</v>
+        <v>2538400</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H94" t="n">
-        <v>44.04</v>
+        <v>54.6</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.046</v>
+        <v>0.825</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.073</v>
+        <v>0.777</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4692,28 +4692,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REACHTEN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2408000</v>
+        <v>2513400</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>3.59</v>
+        <v>1.18</v>
       </c>
       <c r="H95" t="n">
-        <v>51.93</v>
+        <v>51.46</v>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.344</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.361</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         <v>-0.0236</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2401500</v>
+        <v>2467900</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H96" t="n">
         <v>30.29</v>
@@ -4782,39 +4782,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>REACHTEN</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2369200</v>
+        <v>2408000</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.26</v>
+        <v>3.59</v>
       </c>
       <c r="H97" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.278</v>
+        <v>0.344</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.302</v>
+        <v>0.361</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4827,28 +4827,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.83</v>
+        <v>0.26</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0481</v>
+        <v>0.0196</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2281900</v>
+        <v>2373000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H98" t="n">
-        <v>54.14</v>
+        <v>30.1</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.793</v>
+        <v>0.278</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.656</v>
+        <v>0.302</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4872,28 +4872,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.795</v>
+        <v>2.83</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>0.0127</v>
+        <v>0.0481</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2274000</v>
+        <v>2332000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H99" t="n">
-        <v>55.94</v>
+        <v>54.14</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.791</v>
+        <v>2.793</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.77</v>
+        <v>2.656</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4917,28 +4917,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.805</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2261400</v>
+        <v>2322000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1.04</v>
+        <v>0.41</v>
       </c>
       <c r="H100" t="n">
-        <v>16.07</v>
+        <v>60.67</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.954</v>
+        <v>0.792</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.085</v>
+        <v>0.77</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4962,28 +4962,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2223400</v>
+        <v>2293100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="H101" t="n">
-        <v>47.38</v>
+        <v>16.07</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.37</v>
+        <v>0.954</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.343</v>
+        <v>1.085</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5007,28 +5007,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.775</v>
+        <v>1.3</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>0.0544</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2182700</v>
+        <v>2268200</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="H102" t="n">
-        <v>57.86</v>
+        <v>52.38</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.732</v>
+        <v>1.287</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.703</v>
+        <v>1.221</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5052,28 +5052,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E103" s="9" t="n">
-        <v>0.08199999999999999</v>
+        <v>1.36</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2156300</v>
+        <v>2223400</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.66</v>
+        <v>1.15</v>
       </c>
       <c r="H103" t="n">
-        <v>53.87</v>
+        <v>47.38</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.289</v>
+        <v>1.37</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1.221</v>
+        <v>1.343</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5097,28 +5097,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.775</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>0.0544</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2078800</v>
+        <v>2192700</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.53</v>
+        <v>0.93</v>
       </c>
       <c r="H104" t="n">
-        <v>41.89</v>
+        <v>57.86</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.45</v>
+        <v>0.732</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1.465</v>
+        <v>0.703</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
         <v>0.0156</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2069600</v>
+        <v>2137500</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>0.23</v>
@@ -5187,28 +5187,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.515</v>
+        <v>1.43</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.019</v>
+        <v>-0.0069</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>2060900</v>
+        <v>2098800</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H106" t="n">
-        <v>31.96</v>
+        <v>41.89</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.589</v>
+        <v>1.45</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.601</v>
+        <v>1.465</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         <v>0.005699999999999999</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2018100</v>
+        <v>2061200</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="H107" t="n">
         <v>36.85</v>
@@ -5277,28 +5277,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.705</v>
+        <v>0.515</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.019</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1999400</v>
+        <v>2060900</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1.4</v>
+        <v>0.48</v>
       </c>
       <c r="H108" t="n">
-        <v>41.93</v>
+        <v>31.96</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.731</v>
+        <v>0.589</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.728</v>
+        <v>0.601</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5322,28 +5322,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>8.44</v>
+        <v>0.705</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0071</v>
+        <v>-0.0208</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1911800</v>
+        <v>2016500</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.9</v>
+        <v>1.41</v>
       </c>
       <c r="H109" t="n">
-        <v>44.22</v>
+        <v>41.93</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>8.664999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>8.704000000000001</v>
+        <v>0.728</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5367,28 +5367,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E110" s="9" t="n">
-        <v>0.032</v>
+        <v>8.44</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1903100</v>
+        <v>1962900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="H110" t="n">
-        <v>56.29</v>
+        <v>44.22</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.251</v>
+        <v>8.664999999999999</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.169</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5412,39 +5412,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>5.07</v>
+        <v>2.28</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>0.004</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1888600</v>
+        <v>1925600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H111" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>5.066</v>
+        <v>2.213</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>5.062</v>
+        <v>2.158</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5457,39 +5457,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2.29</v>
+        <v>5.08</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.0059</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1856700</v>
+        <v>1907700</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H112" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.67</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.214</v>
+        <v>5.067</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2.158</v>
+        <v>5.062</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5502,39 +5502,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>-0.0142</v>
+        <v>1.3</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0.04</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1855000</v>
+        <v>1905600</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.1</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.109</v>
+        <v>1.252</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.099</v>
+        <v>1.17</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5547,28 +5547,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0.0145</v>
+        <v>0.22</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1851400</v>
+        <v>1888500</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H114" t="n">
-        <v>50.49</v>
+        <v>33.7</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.354</v>
+        <v>0.237</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.326</v>
+        <v>0.289</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5592,39 +5592,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1832000</v>
+        <v>1860100</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0.09</v>
       </c>
       <c r="H115" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.38</v>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.237</v>
+        <v>2.109</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.289</v>
+        <v>2.099</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5637,39 +5637,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>6.48</v>
+        <v>0.35</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0157</v>
+        <v>0.0145</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1794400</v>
+        <v>1851600</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H116" t="n">
-        <v>56.84</v>
-      </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.49</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>6.136</v>
+        <v>0.354</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>5.893</v>
+        <v>0.326</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5682,28 +5682,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E117" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1764500</v>
+        <v>1832700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="H117" t="n">
-        <v>46.75</v>
+        <v>26.87</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>2.616</v>
+        <v>0.974</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>2.605</v>
+        <v>1.056</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5727,39 +5727,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0189</v>
+        <v>1.28</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1757300</v>
+        <v>1820000</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H118" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.28</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>4.59</v>
+        <v>1.412</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>4.492</v>
+        <v>1.571</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5772,39 +5772,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>0</v>
+        <v>6.46</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1725500</v>
+        <v>1795700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
       <c r="H119" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.412</v>
+        <v>6.134</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.571</v>
+        <v>5.893</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5817,39 +5817,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.395</v>
+        <v>2.57</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1721700</v>
+        <v>1767900</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="H120" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.75</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.388</v>
+        <v>2.616</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.391</v>
+        <v>2.605</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5862,39 +5862,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E121" s="9" t="n">
-        <v>0.0227</v>
+        <v>4.66</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1677100</v>
+        <v>1757300</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.52</v>
+        <v>0.97</v>
       </c>
       <c r="H121" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.65</v>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.731</v>
+        <v>4.59</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.745</v>
+        <v>4.492</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5907,39 +5907,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.385</v>
+        <v>0.395</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.0128</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1676000</v>
+        <v>1727100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>1.56</v>
+        <v>0.73</v>
       </c>
       <c r="H122" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.381</v>
+        <v>0.388</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.378</v>
+        <v>0.391</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5952,28 +5952,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E123" s="9" t="n">
-        <v>0.0397</v>
+        <v>0.38</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1667900</v>
+        <v>1687400</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.33</v>
+        <v>1.57</v>
       </c>
       <c r="H123" t="n">
-        <v>58.83</v>
+        <v>49.68</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.774</v>
+        <v>0.38</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2.185</v>
+        <v>0.378</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6006,19 +6006,19 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.0277</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1637900</v>
+        <v>1683400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H124" t="n">
-        <v>36.68</v>
+        <v>37.26</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.844</v>
+        <v>2.845</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>2.874</v>
@@ -6042,28 +6042,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.215</v>
+        <v>2.88</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.0397</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1631400</v>
+        <v>1683000</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="H125" t="n">
-        <v>43.53</v>
+        <v>58.83</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.224</v>
+        <v>2.774</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.232</v>
+        <v>2.185</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6087,39 +6087,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.225</v>
+        <v>0.21</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0244</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1568400</v>
+        <v>1681400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H126" t="n">
-        <v>69.51000000000001</v>
-      </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.04</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.198</v>
+        <v>0.223</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.187</v>
+        <v>0.232</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6132,28 +6132,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1558000</v>
+        <v>1677500</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="H127" t="n">
-        <v>27.9</v>
+        <v>37.6</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.975</v>
+        <v>0.731</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.056</v>
+        <v>0.745</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         <v>0.0259</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1533500</v>
+        <v>1586200</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H128" t="n">
         <v>50.14</v>
@@ -6222,39 +6222,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.41</v>
+        <v>0.225</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>0.038</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1505300</v>
+        <v>1575500</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.423</v>
+        <v>0.198</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.415</v>
+        <v>0.187</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6267,28 +6267,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>0.038</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1482500</v>
+        <v>1506000</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
       <c r="H130" t="n">
-        <v>50.91</v>
+        <v>47.49</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.637</v>
+        <v>0.423</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.621</v>
+        <v>0.415</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6312,28 +6312,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>0.036</v>
+        <v>0.635</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1429100</v>
+        <v>1487500</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="H131" t="n">
-        <v>57.09</v>
+        <v>50.91</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.112</v>
+        <v>0.637</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.879</v>
+        <v>0.621</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6357,28 +6357,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>-0.0122</v>
+        <v>1.14</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>0.027</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1417300</v>
+        <v>1446600</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="H132" t="n">
-        <v>35.96</v>
+        <v>56.41</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.417</v>
+        <v>1.111</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.435</v>
+        <v>0.879</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,19 +6411,19 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>0.0098</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1384000</v>
+        <v>1431300</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H133" t="n">
-        <v>82.37</v>
+        <v>82.09</v>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.801</v>
+        <v>2.8</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>2.406</v>
@@ -6447,36 +6447,36 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E134" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.245</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1357900</v>
+        <v>1421900</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.59</v>
+        <v>1.82</v>
       </c>
       <c r="H134" t="n">
-        <v>50.02</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.13</v>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0.209</v>
@@ -6492,28 +6492,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E135" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.405</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1341300</v>
+        <v>1417300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="H135" t="n">
-        <v>57.25</v>
+        <v>35.96</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.666</v>
+        <v>0.417</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.241</v>
+        <v>0.435</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6537,39 +6537,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>10.7</v>
+        <v>0.34</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.0368</v>
+        <v>0.0149</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1340200</v>
+        <v>1403000</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H136" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.75</v>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>10.417</v>
+        <v>0.336</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>9.731</v>
+        <v>0.343</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6582,28 +6582,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.465</v>
+        <v>0.215</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0488</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1298400</v>
+        <v>1384900</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="H137" t="n">
-        <v>30.99</v>
+        <v>50.02</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.502</v>
+        <v>0.217</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6627,39 +6627,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.0385</v>
+        <v>2.75</v>
+      </c>
+      <c r="E138" s="9" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1289800</v>
+        <v>1374700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>1.65</v>
+        <v>0.39</v>
       </c>
       <c r="H138" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.25</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.22</v>
+        <v>2.666</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.209</v>
+        <v>2.241</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.34</v>
+        <v>0.465</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.022</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1287500</v>
+        <v>1371400</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H139" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="I139" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.99</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.336</v>
+        <v>0.502</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.343</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6717,28 +6717,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.39</v>
+        <v>10.66</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>0.0042</v>
+        <v>0.0329</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1270200</v>
+        <v>1368400</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="H140" t="n">
-        <v>43.29</v>
+        <v>58.02</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.448</v>
+        <v>10.414</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.379</v>
+        <v>9.731</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6762,39 +6762,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.74</v>
+        <v>0.435</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>0.035</v>
+        <v>0.0116</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1259200</v>
+        <v>1348900</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H141" t="n">
-        <v>52.39</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.24</v>
+      </c>
+      <c r="I141" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.741</v>
+        <v>0.388</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.673</v>
+        <v>0.359</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6807,39 +6807,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E142" s="9" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.38</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1217500</v>
+        <v>1321600</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="H142" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I142" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.71</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.259</v>
+        <v>2.447</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.279</v>
+        <v>2.379</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6852,28 +6852,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.305</v>
+        <v>0.745</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>0.0339</v>
+        <v>0.042</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1211700</v>
+        <v>1259400</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H143" t="n">
-        <v>42.53</v>
+        <v>53.15</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.318</v>
+        <v>0.742</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.338</v>
+        <v>0.673</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6897,39 +6897,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.93</v>
+        <v>13</v>
       </c>
       <c r="E144" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.0015</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1209300</v>
+        <v>1236900</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.76</v>
+        <v>0.14</v>
       </c>
       <c r="H144" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.917</v>
+        <v>13.019</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.87</v>
+        <v>13.443</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6942,39 +6942,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-0.006</v>
+        <v>1.29</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1200800</v>
+        <v>1236600</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="H145" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.848</v>
+        <v>1.259</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.862</v>
+        <v>1.279</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6987,28 +6987,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>7.33</v>
+        <v>0.305</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>0.0209</v>
+        <v>0.0339</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1188200</v>
+        <v>1231700</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H146" t="n">
-        <v>52.03</v>
+        <v>42.53</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>7.36</v>
+        <v>0.318</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>6.882</v>
+        <v>0.338</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7032,39 +7032,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.44</v>
+        <v>0.93</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0333</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1182600</v>
+        <v>1209300</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.21</v>
+        <v>0.76</v>
       </c>
       <c r="H147" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.32</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.388</v>
+        <v>0.917</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.359</v>
+        <v>0.87</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7077,28 +7077,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.265</v>
+        <v>7.33</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>0.0392</v>
+        <v>0.0209</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1173500</v>
+        <v>1201200</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="H148" t="n">
-        <v>44.4</v>
+        <v>52.03</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.275</v>
+        <v>7.36</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.296</v>
+        <v>6.882</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7122,28 +7122,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E149" s="9" t="n">
-        <v>0.0476</v>
+        <v>0.825</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1161200</v>
+        <v>1201100</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="H149" t="n">
-        <v>77.73999999999999</v>
+        <v>36.21</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.269</v>
+        <v>0.848</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.217</v>
+        <v>0.862</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7167,39 +7167,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E150" s="9" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1158500</v>
+        <v>1194700</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H150" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I150" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>13.017</v>
+        <v>0.275</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>13.443</v>
+        <v>0.296</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7212,28 +7212,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.765</v>
+        <v>0.33</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0476</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1132600</v>
+        <v>1181200</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.2</v>
+        <v>0.85</v>
       </c>
       <c r="H151" t="n">
-        <v>53.42</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.764</v>
+        <v>0.269</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,19 +7266,19 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>0.0304</v>
+        <v>0.027</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1128300</v>
+        <v>1175100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H152" t="n">
-        <v>53.27</v>
+        <v>52.85</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>3.027</v>
+        <v>3.026</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>2.851</v>
@@ -7317,10 +7317,10 @@
         <v>0.004699999999999999</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1123900</v>
+        <v>1169100</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="H153" t="n">
         <v>57.18</v>
@@ -7347,28 +7347,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.24</v>
+        <v>0.765</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.0435</v>
+        <v>0.02</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1072300</v>
+        <v>1153100</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
       <c r="H154" t="n">
-        <v>46.72</v>
+        <v>53.42</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.247</v>
+        <v>0.764</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.256</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7392,39 +7392,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>-0.0208</v>
+        <v>0.58</v>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>0.0265</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1049300</v>
+        <v>1120500</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="H155" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I155" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.24</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.239</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.243</v>
+        <v>0.513</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7437,28 +7437,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.75</v>
+        <v>0.24</v>
       </c>
       <c r="E156" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1040800</v>
+        <v>1086700</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>17.07</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>55.72</v>
+        <v>50.37</v>
       </c>
       <c r="I156" s="10" t="inlineStr">
         <is>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.735</v>
+        <v>0.24</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.741</v>
+        <v>0.243</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7482,28 +7482,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>-0.0175</v>
+        <v>0.24</v>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1032100</v>
+        <v>1072300</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H157" t="n">
-        <v>37.98</v>
+        <v>46.72</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>4.632</v>
+        <v>0.247</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>4.639</v>
+        <v>0.256</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7527,28 +7527,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1026200</v>
+        <v>1048000</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H158" t="n">
-        <v>41.54</v>
+        <v>54.43</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.272</v>
+        <v>0.778</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.276</v>
+        <v>0.768</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7572,28 +7572,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PWF</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E159" s="9" t="n">
-        <v>0.028</v>
+        <v>0.75</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1021000</v>
+        <v>1040800</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.89</v>
+        <v>17.07</v>
       </c>
       <c r="H159" t="n">
-        <v>40.11</v>
+        <v>55.72</v>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.569</v>
+        <v>0.735</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0.613</v>
+        <v>0.741</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7617,28 +7617,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E160" s="9" t="n">
-        <v>0.0327</v>
+        <v>4.5</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>1019400</v>
+        <v>1037600</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="H160" t="n">
-        <v>53.5</v>
+        <v>37.98</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.777</v>
+        <v>4.632</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0.768</v>
+        <v>4.639</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7662,39 +7662,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E161" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1010600</v>
+        <v>1026200</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1.43</v>
+        <v>0.92</v>
       </c>
       <c r="H161" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I161" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.54</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.002</v>
+        <v>0.272</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.983</v>
+        <v>0.276</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7707,39 +7707,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1.3</v>
+        <v>0.55</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1006600</v>
+        <v>1022700</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.42</v>
+        <v>0.89</v>
       </c>
       <c r="H162" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.11</v>
+      </c>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1.331</v>
+        <v>0.569</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1.279</v>
+        <v>0.613</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7752,28 +7752,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>0.029</v>
+        <v>0.04</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>986300</v>
+        <v>1015400</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H163" t="n">
-        <v>52.91</v>
+        <v>47.66</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2.115</v>
+        <v>1.331</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.989</v>
+        <v>1.279</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7797,39 +7797,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.575</v>
+        <v>1.02</v>
       </c>
       <c r="E164" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>948100</v>
+        <v>1010600</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.18</v>
+        <v>1.43</v>
       </c>
       <c r="H164" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.002</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.513</v>
+        <v>0.983</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7842,39 +7842,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.62</v>
+        <v>2.13</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>946100</v>
+        <v>990400</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>12.44</v>
+        <v>0.39</v>
       </c>
       <c r="H165" t="n">
-        <v>75.11</v>
-      </c>
-      <c r="I165" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.91</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.546</v>
+        <v>2.115</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.542</v>
+        <v>1.989</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7887,39 +7887,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.62</v>
+      </c>
+      <c r="E166" s="9" t="n">
+        <v>0.05980000000000001</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>945100</v>
+        <v>954800</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.17</v>
+        <v>12.56</v>
       </c>
       <c r="H166" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.11</v>
+      </c>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.546</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.467</v>
+        <v>0.542</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7932,28 +7932,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>924500</v>
+        <v>952500</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H167" t="n">
-        <v>45.79</v>
+        <v>50.63</v>
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
@@ -7961,10 +7961,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>4.299</v>
+        <v>1.048</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>4.334</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7977,28 +7977,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E168" s="9" t="n">
-        <v>0.0404</v>
+        <v>0.62</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>832700</v>
+        <v>951800</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H168" t="n">
-        <v>50.63</v>
+        <v>61.66</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>1.048</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.466</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8022,28 +8022,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.875</v>
+        <v>4.2</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>827800</v>
+        <v>930200</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H169" t="n">
-        <v>36.65</v>
+        <v>45.79</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.903</v>
+        <v>4.299</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.956</v>
+        <v>4.334</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8067,28 +8067,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.68</v>
+        <v>0.875</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>0.006</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>826300</v>
+        <v>910400</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H170" t="n">
-        <v>41.09</v>
+        <v>36.65</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.734</v>
+        <v>0.903</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.769</v>
+        <v>0.956</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8112,28 +8112,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>2.72</v>
+        <v>1.2</v>
       </c>
       <c r="E171" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>815500</v>
+        <v>864900</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="H171" t="n">
-        <v>43.88</v>
+        <v>49.36</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>2.756</v>
+        <v>1.245</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>2.765</v>
+        <v>1.059</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8157,28 +8157,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.2</v>
+        <v>2.72</v>
       </c>
       <c r="E172" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>807500</v>
+        <v>835900</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H172" t="n">
-        <v>49.36</v>
+        <v>43.88</v>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>1.245</v>
+        <v>2.756</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>1.059</v>
+        <v>2.765</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8202,39 +8202,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>7.5</v>
+        <v>1.67</v>
       </c>
       <c r="E173" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>745100</v>
+        <v>827400</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H173" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="I173" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.49</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>7.587</v>
+        <v>1.734</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>7.78</v>
+        <v>1.769</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
         <v>-0.0124</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>732800</v>
+        <v>775900</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H174" t="n">
         <v>74.43000000000001</v>
@@ -8292,39 +8292,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E175" s="9" t="n">
-        <v>0.0547</v>
+        <v>7.5</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>709900</v>
+        <v>756200</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.98</v>
+        <v>0.25</v>
       </c>
       <c r="H175" t="n">
-        <v>42.44</v>
-      </c>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.72</v>
+      </c>
+      <c r="I175" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.21</v>
+        <v>7.587</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.233</v>
+        <v>7.78</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8337,28 +8337,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.71</v>
+      </c>
+      <c r="E176" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>709600</v>
+        <v>740000</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H176" t="n">
-        <v>35.15</v>
+        <v>35.52</v>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.631</v>
+        <v>1.78</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.631</v>
+        <v>1.895</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8382,28 +8382,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>-0.0054</v>
+        <v>1.17</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>709100</v>
+        <v>730200</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.37</v>
+        <v>1.2</v>
       </c>
       <c r="H177" t="n">
-        <v>33.35</v>
+        <v>38.55</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.949</v>
+        <v>1.189</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1.005</v>
+        <v>1.209</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8427,28 +8427,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E178" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E178" s="9" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>708900</v>
+        <v>710000</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="H178" t="n">
-        <v>35.52</v>
+        <v>40.72</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1.78</v>
+        <v>2.209</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1.895</v>
+        <v>2.233</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8472,28 +8472,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.51</v>
+        <v>0.925</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>687300</v>
+        <v>709600</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="H179" t="n">
-        <v>46.48</v>
+        <v>36.72</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.524</v>
+        <v>0.95</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0.506</v>
+        <v>1.005</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8517,28 +8517,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E180" s="9" t="n">
-        <v>0.0288</v>
+        <v>0.625</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>675200</v>
+        <v>709600</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.27</v>
+        <v>0.62</v>
       </c>
       <c r="H180" t="n">
-        <v>35.26</v>
+        <v>35.15</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8546,10 +8546,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1.212</v>
+        <v>0.631</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1.297</v>
+        <v>0.631</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8562,28 +8562,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MFCB</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>-0.0036</v>
+        <v>0.51</v>
+      </c>
+      <c r="E181" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>673900</v>
+        <v>687300</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H181" t="n">
-        <v>39.22</v>
+        <v>46.48</v>
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>2.859</v>
+        <v>0.524</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>2.859</v>
+        <v>0.506</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8607,39 +8607,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="E182" s="9" t="n">
-        <v>0.0034</v>
+        <v>0.0288</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>671000</v>
+        <v>682200</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9</v>
+        <v>0.28</v>
       </c>
       <c r="H182" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I182" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.26</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1.509</v>
+        <v>1.212</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>1.501</v>
+        <v>1.297</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8652,39 +8652,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MFCB</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>0.0164</v>
+        <v>2.75</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>656100</v>
+        <v>674900</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.11</v>
+        <v>0.66</v>
       </c>
       <c r="H183" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="I183" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.22</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>4.352</v>
+        <v>2.859</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>4.432</v>
+        <v>2.859</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8697,28 +8697,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>-0.0484</v>
+        <v>1.49</v>
+      </c>
+      <c r="E184" s="9" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>652800</v>
+        <v>671000</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="H184" t="n">
-        <v>61.25</v>
+        <v>44.8</v>
       </c>
       <c r="I184" s="10" t="inlineStr">
         <is>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.57</v>
+        <v>1.509</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>0.525</v>
+        <v>1.501</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8742,28 +8742,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>4.32</v>
+      </c>
+      <c r="E185" s="9" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>631700</v>
+        <v>670100</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H185" t="n">
-        <v>44.51</v>
+        <v>47.7</v>
       </c>
       <c r="I185" s="10" t="inlineStr">
         <is>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>2.565</v>
+        <v>4.351</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>2.695</v>
+        <v>4.432</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8787,28 +8787,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.0484</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>622100</v>
+        <v>653500</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.47</v>
+        <v>0.78</v>
       </c>
       <c r="H186" t="n">
-        <v>41.52</v>
+        <v>61.25</v>
       </c>
       <c r="I186" s="10" t="inlineStr">
         <is>
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>1.093</v>
+        <v>0.57</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>1.136</v>
+        <v>0.525</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8832,28 +8832,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>0.795</v>
+        <v>2.55</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>-0.0185</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>616200</v>
+        <v>642600</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H187" t="n">
-        <v>33.71</v>
+        <v>44.51</v>
       </c>
       <c r="I187" s="10" t="inlineStr">
         <is>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.842</v>
+        <v>2.565</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>0.904</v>
+        <v>2.695</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8877,39 +8877,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E188" s="8" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E188" s="9" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>598300</v>
+        <v>638400</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H188" t="n">
-        <v>50.62</v>
-      </c>
-      <c r="I188" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.98</v>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.639</v>
+        <v>1.16</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>0.612</v>
+        <v>1.096</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="7" t="inlineStr"/>
@@ -8922,39 +8922,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>3.3</v>
+        <v>1.07</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>596000</v>
+        <v>627200</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H189" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="I189" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.52</v>
+      </c>
+      <c r="I189" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>3.424</v>
+        <v>1.093</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>3.16</v>
+        <v>1.136</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
@@ -8967,39 +8967,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>3.16</v>
+        <v>0.8</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>-0.0063</v>
+        <v>-0.0123</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>595600</v>
+        <v>621300</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H190" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I190" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.6</v>
+      </c>
+      <c r="I190" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>3.177</v>
+        <v>0.843</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>2.858</v>
+        <v>0.904</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
@@ -9012,39 +9012,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E191" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.63</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>540700</v>
+        <v>618300</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H191" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.92</v>
+      </c>
+      <c r="I191" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>1.16</v>
+        <v>0.638</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>1.096</v>
+        <v>0.612</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="7" t="inlineStr"/>
@@ -9057,28 +9057,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>540300</v>
+        <v>609600</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H192" t="n">
-        <v>33.95</v>
+        <v>52.85</v>
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>1.74</v>
+        <v>3.176</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>1.891</v>
+        <v>2.857</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="7" t="inlineStr"/>
@@ -9102,28 +9102,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E193" s="9" t="n">
-        <v>0.0364</v>
+        <v>3.29</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>534100</v>
+        <v>606500</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="H193" t="n">
-        <v>55.04</v>
+        <v>44.06</v>
       </c>
       <c r="I193" s="6" t="inlineStr">
         <is>
@@ -9131,10 +9131,10 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>2.528</v>
+        <v>3.423</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>2.236</v>
+        <v>3.16</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
@@ -9147,28 +9147,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>3.08</v>
+        <v>2.07</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>0.0033</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>513300</v>
+        <v>571800</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H194" t="n">
-        <v>39.51</v>
+        <v>43.16</v>
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>3.154</v>
+        <v>2.128</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>3.336</v>
+        <v>2.285</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
@@ -9192,28 +9192,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E195" s="9" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.65</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>508700</v>
+        <v>540400</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="H195" t="n">
-        <v>40.67</v>
+        <v>32.05</v>
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
@@ -9221,16 +9221,196 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.546</v>
+        <v>1.738</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>0.574</v>
+        <v>1.891</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="7" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E196" s="9" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H196" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E197" s="9" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>537800</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H197" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="7" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E198" s="9" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>521700</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H198" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>3.154</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="7" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>512600</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H199" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>1.766</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M195"/>
+  <autoFilter ref="A1:M199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>